--- a/jogos_2026-07-11.xlsx
+++ b/jogos_2026-07-11.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>APIA Leichhardt Tigers</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sydney II</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>APIA Leichhardt Tigers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Sydney II</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G47" t="n">

--- a/jogos_2026-07-11.xlsx
+++ b/jogos_2026-07-11.xlsx
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G47" t="n">

--- a/jogos_2026-07-11.xlsx
+++ b/jogos_2026-07-11.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>APIA Leichhardt Tigers</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Sydney II</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>APIA Leichhardt Tigers</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sydney II</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G47" t="n">

--- a/jogos_2026-07-11.xlsx
+++ b/jogos_2026-07-11.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>APIA Leichhardt Tigers</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sydney II</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>APIA Leichhardt Tigers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Sydney II</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>7.49</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,10 +6290,10 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.86</v>
+        <v>1.64</v>
       </c>
       <c r="O37" t="n">
-        <v>3.71</v>
+        <v>3.85</v>
       </c>
       <c r="P37" t="n">
         <v>4.15</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G46" t="n">

--- a/jogos_2026-07-11.xlsx
+++ b/jogos_2026-07-11.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.23</v>
+        <v>2.02</v>
       </c>
       <c r="O12" t="n">
-        <v>3.18</v>
+        <v>3.22</v>
       </c>
       <c r="P12" t="n">
-        <v>2.97</v>
+        <v>3.41</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>7.49</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>7.49</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,10 +6290,10 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.64</v>
+        <v>1.86</v>
       </c>
       <c r="O37" t="n">
-        <v>3.85</v>
+        <v>3.71</v>
       </c>
       <c r="P37" t="n">
         <v>4.15</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,10 +6449,10 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1.86</v>
+        <v>1.64</v>
       </c>
       <c r="O38" t="n">
-        <v>3.71</v>
+        <v>3.85</v>
       </c>
       <c r="P38" t="n">
         <v>4.15</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G47" t="n">

--- a/jogos_2026-07-11.xlsx
+++ b/jogos_2026-07-11.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>7.49</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>7.49</v>
+        <v>2.02</v>
       </c>
       <c r="O14" t="n">
-        <v>4.55</v>
+        <v>3.22</v>
       </c>
       <c r="P14" t="n">
-        <v>1.34</v>
+        <v>3.41</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G47" t="n">

--- a/jogos_2026-07-11.xlsx
+++ b/jogos_2026-07-11.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>7.49</v>
+        <v>2.05</v>
       </c>
       <c r="O9" t="n">
-        <v>4.55</v>
+        <v>3.2</v>
       </c>
       <c r="P9" t="n">
-        <v>1.34</v>
+        <v>3.35</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.23</v>
+        <v>2.02</v>
       </c>
       <c r="O11" t="n">
-        <v>3.18</v>
+        <v>3.22</v>
       </c>
       <c r="P11" t="n">
-        <v>2.97</v>
+        <v>3.41</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.02</v>
+        <v>2.23</v>
       </c>
       <c r="O14" t="n">
-        <v>3.22</v>
+        <v>3.18</v>
       </c>
       <c r="P14" t="n">
-        <v>3.41</v>
+        <v>2.97</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.05</v>
+        <v>7.49</v>
       </c>
       <c r="O15" t="n">
-        <v>3.2</v>
+        <v>4.55</v>
       </c>
       <c r="P15" t="n">
-        <v>3.35</v>
+        <v>1.34</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G47" t="n">

--- a/jogos_2026-07-11.xlsx
+++ b/jogos_2026-07-11.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="O9" t="n">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="P9" t="n">
-        <v>3.35</v>
+        <v>3.41</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>7.49</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.23</v>
+        <v>2.05</v>
       </c>
       <c r="O14" t="n">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="P14" t="n">
-        <v>2.97</v>
+        <v>3.35</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>7.49</v>
+        <v>2.23</v>
       </c>
       <c r="O15" t="n">
-        <v>4.55</v>
+        <v>3.18</v>
       </c>
       <c r="P15" t="n">
-        <v>1.34</v>
+        <v>2.97</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G47" t="n">

--- a/jogos_2026-07-11.xlsx
+++ b/jogos_2026-07-11.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>APIA Leichhardt Tigers</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Sydney II</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>APIA Leichhardt Tigers</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sydney II</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.02</v>
+        <v>7.49</v>
       </c>
       <c r="O9" t="n">
-        <v>3.22</v>
+        <v>4.55</v>
       </c>
       <c r="P9" t="n">
-        <v>3.41</v>
+        <v>1.34</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>7.49</v>
+        <v>2.23</v>
       </c>
       <c r="O13" t="n">
-        <v>4.55</v>
+        <v>3.18</v>
       </c>
       <c r="P13" t="n">
-        <v>1.34</v>
+        <v>2.97</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,10 +6290,10 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.86</v>
+        <v>1.64</v>
       </c>
       <c r="O37" t="n">
-        <v>3.71</v>
+        <v>3.85</v>
       </c>
       <c r="P37" t="n">
         <v>4.15</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,10 +6449,10 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1.64</v>
+        <v>1.86</v>
       </c>
       <c r="O38" t="n">
-        <v>3.85</v>
+        <v>3.71</v>
       </c>
       <c r="P38" t="n">
         <v>4.15</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -8357,13 +8357,13 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -8396,10 +8396,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -8873,10 +8873,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>

--- a/jogos_2026-07-11.xlsx
+++ b/jogos_2026-07-11.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>7.49</v>
+        <v>2.05</v>
       </c>
       <c r="O9" t="n">
-        <v>4.55</v>
+        <v>3.2</v>
       </c>
       <c r="P9" t="n">
-        <v>1.34</v>
+        <v>3.35</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.02</v>
+        <v>7.49</v>
       </c>
       <c r="O12" t="n">
-        <v>3.22</v>
+        <v>4.55</v>
       </c>
       <c r="P12" t="n">
-        <v>3.41</v>
+        <v>1.34</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,10 +6290,10 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.64</v>
+        <v>1.86</v>
       </c>
       <c r="O37" t="n">
-        <v>3.85</v>
+        <v>3.71</v>
       </c>
       <c r="P37" t="n">
         <v>4.15</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G47" t="n">

--- a/jogos_2026-07-11.xlsx
+++ b/jogos_2026-07-11.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>7.49</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>7.49</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,10 +6290,10 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.86</v>
+        <v>1.64</v>
       </c>
       <c r="O37" t="n">
-        <v>3.71</v>
+        <v>3.85</v>
       </c>
       <c r="P37" t="n">
         <v>4.15</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G47" t="n">

--- a/jogos_2026-07-11.xlsx
+++ b/jogos_2026-07-11.xlsx
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>7.49</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.23</v>
+        <v>2.02</v>
       </c>
       <c r="O13" t="n">
-        <v>3.18</v>
+        <v>3.22</v>
       </c>
       <c r="P13" t="n">
-        <v>2.97</v>
+        <v>3.41</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>7.49</v>
+        <v>2.23</v>
       </c>
       <c r="O14" t="n">
-        <v>4.55</v>
+        <v>3.18</v>
       </c>
       <c r="P14" t="n">
-        <v>1.34</v>
+        <v>2.97</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,10 +6449,10 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1.86</v>
+        <v>1.64</v>
       </c>
       <c r="O38" t="n">
-        <v>3.71</v>
+        <v>3.85</v>
       </c>
       <c r="P38" t="n">
         <v>4.15</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G47" t="n">

--- a/jogos_2026-07-11.xlsx
+++ b/jogos_2026-07-11.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>7.49</v>
+        <v>2.23</v>
       </c>
       <c r="O9" t="n">
-        <v>4.55</v>
+        <v>3.18</v>
       </c>
       <c r="P9" t="n">
-        <v>1.34</v>
+        <v>2.97</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.05</v>
+        <v>7.49</v>
       </c>
       <c r="O10" t="n">
-        <v>3.2</v>
+        <v>4.55</v>
       </c>
       <c r="P10" t="n">
-        <v>3.35</v>
+        <v>1.34</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>6.07</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>3.18</v>
+        <v>1.59</v>
       </c>
       <c r="O20" t="n">
-        <v>3.48</v>
+        <v>4.46</v>
       </c>
       <c r="P20" t="n">
-        <v>2.25</v>
+        <v>5.2</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>4.02</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4109,10 +4109,10 @@
         <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE23" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>2.81</v>
+        <v>1.45</v>
       </c>
       <c r="O26" t="n">
-        <v>3.54</v>
+        <v>4.64</v>
       </c>
       <c r="P26" t="n">
-        <v>2.45</v>
+        <v>6.95</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5057,10 +5057,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,10 +6131,10 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1.86</v>
+        <v>1.64</v>
       </c>
       <c r="O36" t="n">
-        <v>3.71</v>
+        <v>3.85</v>
       </c>
       <c r="P36" t="n">
         <v>4.15</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,10 +6449,10 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1.64</v>
+        <v>1.86</v>
       </c>
       <c r="O38" t="n">
-        <v>3.85</v>
+        <v>3.71</v>
       </c>
       <c r="P38" t="n">
         <v>4.15</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G47" t="n">

--- a/jogos_2026-07-11.xlsx
+++ b/jogos_2026-07-11.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>APIA Leichhardt Tigers</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sydney II</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>APIA Leichhardt Tigers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Sydney II</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.23</v>
+        <v>2.74</v>
       </c>
       <c r="O9" t="n">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="P9" t="n">
-        <v>2.97</v>
+        <v>2.47</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>7.49</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.05</v>
+        <v>6.07</v>
       </c>
       <c r="O11" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="P11" t="n">
-        <v>3.35</v>
+        <v>1.58</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.74</v>
+        <v>2.23</v>
       </c>
       <c r="O12" t="n">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="P12" t="n">
-        <v>2.47</v>
+        <v>2.97</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.02</v>
+        <v>7.49</v>
       </c>
       <c r="O13" t="n">
-        <v>3.22</v>
+        <v>4.55</v>
       </c>
       <c r="P13" t="n">
-        <v>3.41</v>
+        <v>1.34</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>6.07</v>
+        <v>2.02</v>
       </c>
       <c r="O15" t="n">
-        <v>3.7</v>
+        <v>3.22</v>
       </c>
       <c r="P15" t="n">
-        <v>1.58</v>
+        <v>3.41</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>3.18</v>
+        <v>1.59</v>
       </c>
       <c r="O19" t="n">
-        <v>3.48</v>
+        <v>4.46</v>
       </c>
       <c r="P19" t="n">
-        <v>2.25</v>
+        <v>5.2</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.59</v>
+        <v>3.18</v>
       </c>
       <c r="O20" t="n">
-        <v>4.46</v>
+        <v>3.48</v>
       </c>
       <c r="P20" t="n">
-        <v>5.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.81</v>
+        <v>1.45</v>
       </c>
       <c r="O25" t="n">
-        <v>3.54</v>
+        <v>4.64</v>
       </c>
       <c r="P25" t="n">
-        <v>2.45</v>
+        <v>6.95</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.45</v>
+        <v>2.81</v>
       </c>
       <c r="O26" t="n">
-        <v>4.64</v>
+        <v>3.54</v>
       </c>
       <c r="P26" t="n">
-        <v>6.95</v>
+        <v>2.45</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4739,10 +4739,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5057,10 +5057,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G47" t="n">

--- a/jogos_2026-07-11.xlsx
+++ b/jogos_2026-07-11.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>APIA Leichhardt Tigers</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Sydney II</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>APIA Leichhardt Tigers</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sydney II</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.23</v>
+        <v>7.49</v>
       </c>
       <c r="O12" t="n">
-        <v>3.18</v>
+        <v>4.55</v>
       </c>
       <c r="P12" t="n">
-        <v>2.97</v>
+        <v>1.34</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>7.49</v>
+        <v>2.02</v>
       </c>
       <c r="O13" t="n">
-        <v>4.55</v>
+        <v>3.22</v>
       </c>
       <c r="P13" t="n">
-        <v>1.34</v>
+        <v>3.41</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.05</v>
+        <v>2.23</v>
       </c>
       <c r="O14" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="P14" t="n">
-        <v>3.35</v>
+        <v>2.97</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="O15" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="P15" t="n">
-        <v>3.41</v>
+        <v>3.35</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>4.46</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.59</v>
+        <v>3.18</v>
       </c>
       <c r="O19" t="n">
-        <v>4.46</v>
+        <v>3.48</v>
       </c>
       <c r="P19" t="n">
-        <v>5.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1.45</v>
+        <v>2.81</v>
       </c>
       <c r="O25" t="n">
-        <v>4.64</v>
+        <v>3.54</v>
       </c>
       <c r="P25" t="n">
-        <v>6.95</v>
+        <v>2.45</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>2.81</v>
+        <v>1.45</v>
       </c>
       <c r="O26" t="n">
-        <v>3.54</v>
+        <v>4.64</v>
       </c>
       <c r="P26" t="n">
-        <v>2.45</v>
+        <v>6.95</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G47" t="n">

--- a/jogos_2026-07-11.xlsx
+++ b/jogos_2026-07-11.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>APIA Leichhardt Tigers</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sydney II</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>APIA Leichhardt Tigers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Sydney II</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.02</v>
+        <v>2.74</v>
       </c>
       <c r="O13" t="n">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="P13" t="n">
-        <v>3.41</v>
+        <v>2.47</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.97</v>
+        <v>1.88</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.23</v>
+        <v>2.05</v>
       </c>
       <c r="O14" t="n">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="P14" t="n">
-        <v>2.97</v>
+        <v>3.35</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.05</v>
+        <v>2.23</v>
       </c>
       <c r="O15" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="P15" t="n">
-        <v>3.35</v>
+        <v>2.97</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.81</v>
+        <v>1.45</v>
       </c>
       <c r="O25" t="n">
-        <v>3.54</v>
+        <v>4.64</v>
       </c>
       <c r="P25" t="n">
-        <v>2.45</v>
+        <v>6.95</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.45</v>
+        <v>2.81</v>
       </c>
       <c r="O26" t="n">
-        <v>4.64</v>
+        <v>3.54</v>
       </c>
       <c r="P26" t="n">
-        <v>6.95</v>
+        <v>2.45</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4739,10 +4739,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4898,10 +4898,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G47" t="n">

--- a/jogos_2026-07-11.xlsx
+++ b/jogos_2026-07-11.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>APIA Leichhardt Tigers</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Sydney II</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>APIA Leichhardt Tigers</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sydney II</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.02</v>
+        <v>2.74</v>
       </c>
       <c r="O10" t="n">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="P10" t="n">
-        <v>3.41</v>
+        <v>2.47</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.97</v>
+        <v>1.88</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>6.07</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>7.49</v>
+        <v>6.07</v>
       </c>
       <c r="O12" t="n">
-        <v>4.55</v>
+        <v>3.7</v>
       </c>
       <c r="P12" t="n">
-        <v>1.34</v>
+        <v>1.58</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.74</v>
+        <v>7.49</v>
       </c>
       <c r="O13" t="n">
-        <v>3.3</v>
+        <v>4.55</v>
       </c>
       <c r="P13" t="n">
-        <v>2.47</v>
+        <v>1.34</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="O14" t="n">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="P14" t="n">
-        <v>3.35</v>
+        <v>3.41</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.23</v>
+        <v>2.05</v>
       </c>
       <c r="O15" t="n">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="P15" t="n">
-        <v>2.97</v>
+        <v>3.35</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>4.46</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>4.46</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4739,10 +4739,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4898,10 +4898,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>3.5</v>
+        <v>1.74</v>
       </c>
       <c r="O33" t="n">
-        <v>3.87</v>
+        <v>3.78</v>
       </c>
       <c r="P33" t="n">
-        <v>1.99</v>
+        <v>3.84</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,10 +6131,10 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1.64</v>
+        <v>1.86</v>
       </c>
       <c r="O36" t="n">
-        <v>3.85</v>
+        <v>3.71</v>
       </c>
       <c r="P36" t="n">
         <v>4.15</v>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G47" t="n">

--- a/jogos_2026-07-11.xlsx
+++ b/jogos_2026-07-11.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>APIA Leichhardt Tigers</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sydney II</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>APIA Leichhardt Tigers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Sydney II</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.23</v>
+        <v>7.49</v>
       </c>
       <c r="O9" t="n">
-        <v>3.18</v>
+        <v>4.55</v>
       </c>
       <c r="P9" t="n">
-        <v>2.97</v>
+        <v>1.34</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.74</v>
+        <v>6.07</v>
       </c>
       <c r="O10" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="P10" t="n">
-        <v>2.47</v>
+        <v>1.58</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>6.07</v>
+        <v>2.05</v>
       </c>
       <c r="O12" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="P12" t="n">
-        <v>1.58</v>
+        <v>3.35</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>7.49</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.02</v>
+        <v>2.74</v>
       </c>
       <c r="O14" t="n">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="P14" t="n">
-        <v>3.41</v>
+        <v>2.47</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.97</v>
+        <v>1.88</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="O15" t="n">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="P15" t="n">
-        <v>3.35</v>
+        <v>3.41</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>3.5</v>
+        <v>1.74</v>
       </c>
       <c r="O30" t="n">
-        <v>3.87</v>
+        <v>3.78</v>
       </c>
       <c r="P30" t="n">
-        <v>1.99</v>
+        <v>3.84</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G47" t="n">

--- a/jogos_2026-07-11.xlsx
+++ b/jogos_2026-07-11.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>7.49</v>
+        <v>2.02</v>
       </c>
       <c r="O9" t="n">
-        <v>4.55</v>
+        <v>3.22</v>
       </c>
       <c r="P9" t="n">
-        <v>1.34</v>
+        <v>3.41</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.23</v>
+        <v>2.05</v>
       </c>
       <c r="O11" t="n">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="P11" t="n">
-        <v>2.97</v>
+        <v>3.35</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.05</v>
+        <v>7.49</v>
       </c>
       <c r="O12" t="n">
-        <v>3.2</v>
+        <v>4.55</v>
       </c>
       <c r="P12" t="n">
-        <v>3.35</v>
+        <v>1.34</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.74</v>
+        <v>2.23</v>
       </c>
       <c r="O14" t="n">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="P14" t="n">
-        <v>2.47</v>
+        <v>2.97</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>4.46</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>4.46</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G47" t="n">

--- a/jogos_2026-07-11.xlsx
+++ b/jogos_2026-07-11.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>APIA Leichhardt Tigers</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Sydney II</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>APIA Leichhardt Tigers</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sydney II</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.02</v>
+        <v>2.23</v>
       </c>
       <c r="O9" t="n">
-        <v>3.22</v>
+        <v>3.18</v>
       </c>
       <c r="P9" t="n">
-        <v>3.41</v>
+        <v>2.97</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>6.07</v>
+        <v>2.02</v>
       </c>
       <c r="O10" t="n">
-        <v>3.7</v>
+        <v>3.22</v>
       </c>
       <c r="P10" t="n">
-        <v>1.58</v>
+        <v>3.41</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.05</v>
+        <v>7.49</v>
       </c>
       <c r="O11" t="n">
-        <v>3.2</v>
+        <v>4.55</v>
       </c>
       <c r="P11" t="n">
-        <v>3.35</v>
+        <v>1.34</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>7.49</v>
+        <v>2.05</v>
       </c>
       <c r="O12" t="n">
-        <v>4.55</v>
+        <v>3.2</v>
       </c>
       <c r="P12" t="n">
-        <v>1.34</v>
+        <v>3.35</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.74</v>
+        <v>6.07</v>
       </c>
       <c r="O13" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="P13" t="n">
-        <v>2.47</v>
+        <v>1.58</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.23</v>
+        <v>2.74</v>
       </c>
       <c r="O14" t="n">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="P14" t="n">
-        <v>2.97</v>
+        <v>2.47</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>4.46</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>4.46</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>4.02</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4109,10 +4109,10 @@
         <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>4.02</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4268,10 +4268,10 @@
         <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4739,10 +4739,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5057,10 +5057,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G47" t="n">

--- a/jogos_2026-07-11.xlsx
+++ b/jogos_2026-07-11.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.23</v>
+        <v>6.07</v>
       </c>
       <c r="O9" t="n">
-        <v>3.18</v>
+        <v>3.7</v>
       </c>
       <c r="P9" t="n">
-        <v>2.97</v>
+        <v>1.58</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.02</v>
+        <v>7.49</v>
       </c>
       <c r="O10" t="n">
-        <v>3.22</v>
+        <v>4.55</v>
       </c>
       <c r="P10" t="n">
-        <v>3.41</v>
+        <v>1.34</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>7.49</v>
+        <v>2.02</v>
       </c>
       <c r="O11" t="n">
-        <v>4.55</v>
+        <v>3.22</v>
       </c>
       <c r="P11" t="n">
-        <v>1.34</v>
+        <v>3.41</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>6.07</v>
+        <v>2.74</v>
       </c>
       <c r="O13" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="P13" t="n">
-        <v>1.58</v>
+        <v>2.47</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.74</v>
+        <v>2.05</v>
       </c>
       <c r="O14" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P14" t="n">
-        <v>2.47</v>
+        <v>3.35</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.59</v>
+        <v>3.18</v>
       </c>
       <c r="O17" t="n">
-        <v>4.46</v>
+        <v>3.48</v>
       </c>
       <c r="P17" t="n">
-        <v>5.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>4.46</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>4.02</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4109,10 +4109,10 @@
         <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>4.02</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4268,10 +4268,10 @@
         <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>3.5</v>
+        <v>1.74</v>
       </c>
       <c r="O30" t="n">
-        <v>3.87</v>
+        <v>3.78</v>
       </c>
       <c r="P30" t="n">
-        <v>1.99</v>
+        <v>3.84</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>1.74</v>
+        <v>3.5</v>
       </c>
       <c r="O32" t="n">
-        <v>3.78</v>
+        <v>3.87</v>
       </c>
       <c r="P32" t="n">
-        <v>3.84</v>
+        <v>1.99</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G47" t="n">

--- a/jogos_2026-07-11.xlsx
+++ b/jogos_2026-07-11.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1847,55 +1847,55 @@
         <v>1.58</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>5.61</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>7.49</v>
+        <v>2.23</v>
       </c>
       <c r="O10" t="n">
-        <v>4.55</v>
+        <v>3.18</v>
       </c>
       <c r="P10" t="n">
-        <v>1.34</v>
+        <v>2.97</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2165,34 +2165,34 @@
         <v>3.41</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA11" t="n">
         <v>1.97</v>
@@ -2201,19 +2201,19 @@
         <v>1.73</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.74</v>
+        <v>7.49</v>
       </c>
       <c r="O13" t="n">
-        <v>3.3</v>
+        <v>4.55</v>
       </c>
       <c r="P13" t="n">
-        <v>2.47</v>
+        <v>1.34</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>6.95</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.88</v>
+        <v>1.7</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.84</v>
+        <v>2.05</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="O14" t="n">
-        <v>3.2</v>
+        <v>3.32</v>
       </c>
       <c r="P14" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.23</v>
+        <v>2.74</v>
       </c>
       <c r="O15" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AC15" t="n">
         <v>3.18</v>
       </c>
-      <c r="P15" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>0</v>
-      </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>4.46</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>3.18</v>
+        <v>1.52</v>
       </c>
       <c r="O17" t="n">
-        <v>3.48</v>
+        <v>4.2</v>
       </c>
       <c r="P17" t="n">
-        <v>2.25</v>
+        <v>5</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.59</v>
+        <v>3.18</v>
       </c>
       <c r="O19" t="n">
-        <v>4.46</v>
+        <v>3.48</v>
       </c>
       <c r="P19" t="n">
-        <v>5.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3914,55 +3914,55 @@
         <v>2.39</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="R23" t="n">
         <v>2.31</v>
       </c>
-      <c r="O23" t="n">
-        <v>4.02</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>4.54</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.84</v>
+        <v>3.22</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.87</v>
+        <v>1.38</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>4.02</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>11.8</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4391,55 +4391,55 @@
         <v>6.95</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4550,55 +4550,55 @@
         <v>2.45</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4700,64 +4700,64 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,64 +4859,64 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>2.19</v>
+        <v>2.09</v>
       </c>
       <c r="O29" t="n">
-        <v>3.56</v>
+        <v>3.22</v>
       </c>
       <c r="P29" t="n">
-        <v>3.03</v>
+        <v>3.62</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5057,10 +5057,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,64 +5177,64 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1.74</v>
+        <v>3.22</v>
       </c>
       <c r="O30" t="n">
-        <v>3.78</v>
+        <v>2.91</v>
       </c>
       <c r="P30" t="n">
-        <v>3.84</v>
+        <v>2.44</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,64 +5495,64 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>3.5</v>
+        <v>1.74</v>
       </c>
       <c r="O32" t="n">
-        <v>3.87</v>
+        <v>3.78</v>
       </c>
       <c r="P32" t="n">
-        <v>1.99</v>
+        <v>3.84</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK32" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,64 +5654,64 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -5813,64 +5813,64 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -5981,55 +5981,55 @@
         <v>1.47</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>5.48</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6042,10 +6042,10 @@
         </is>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK35" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,64 +6131,64 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1.86</v>
+        <v>1.64</v>
       </c>
       <c r="O36" t="n">
-        <v>3.71</v>
+        <v>3.85</v>
       </c>
       <c r="P36" t="n">
         <v>4.15</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK36" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,64 +6449,64 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -7913,10 +7913,10 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA47" t="n">
         <v>0</v>

--- a/jogos_2026-07-11.xlsx
+++ b/jogos_2026-07-11.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>APIA Leichhardt Tigers</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sydney II</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.27</v>
+        <v>1.66</v>
       </c>
       <c r="O5" t="n">
-        <v>5.1</v>
+        <v>3.65</v>
       </c>
       <c r="P5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>APIA Leichhardt Tigers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Sydney II</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.66</v>
+        <v>1.27</v>
       </c>
       <c r="O6" t="n">
-        <v>3.65</v>
+        <v>5.1</v>
       </c>
       <c r="P6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,65 +1838,65 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>6.07</v>
+        <v>2.74</v>
       </c>
       <c r="O9" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="P9" t="n">
-        <v>1.58</v>
+        <v>2.47</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.61</v>
+        <v>3.2</v>
       </c>
       <c r="R9" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG9" t="n">
         <v>2.1</v>
       </c>
-      <c r="S9" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="U9" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AH9" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.11</v>
+        <v>1.4</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.23</v>
+        <v>2</v>
       </c>
       <c r="O10" t="n">
-        <v>3.18</v>
+        <v>3.32</v>
       </c>
       <c r="P10" t="n">
-        <v>2.97</v>
+        <v>3.65</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.99</v>
+        <v>2.15</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,31 +2315,31 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.05</v>
+        <v>6.07</v>
       </c>
       <c r="O12" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="P12" t="n">
-        <v>3.35</v>
+        <v>1.58</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.51</v>
+        <v>5.61</v>
       </c>
       <c r="R12" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S12" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="T12" t="n">
-        <v>2.75</v>
+        <v>2.53</v>
       </c>
       <c r="U12" t="n">
-        <v>2.9</v>
+        <v>3.22</v>
       </c>
       <c r="V12" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W12" t="n">
         <v>1.06</v>
@@ -2348,31 +2348,31 @@
         <v>1.06</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z12" t="n">
-        <v>3</v>
+        <v>2.72</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.84</v>
+        <v>2.25</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.75</v>
+        <v>1.11</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,80 +2474,80 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>7.49</v>
+        <v>2.05</v>
       </c>
       <c r="O13" t="n">
-        <v>4.55</v>
+        <v>3.2</v>
       </c>
       <c r="P13" t="n">
-        <v>1.34</v>
+        <v>3.35</v>
       </c>
       <c r="Q13" t="n">
-        <v>6.95</v>
+        <v>2.51</v>
       </c>
       <c r="R13" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="S13" t="n">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="T13" t="n">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="U13" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="V13" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="W13" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X13" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AD13" t="n">
         <v>1.22</v>
       </c>
-      <c r="Z13" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AE13" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.95</v>
+        <v>1.84</v>
       </c>
       <c r="AG13" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AK13" t="n">
         <v>1.75</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1.03</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2</v>
+        <v>2.23</v>
       </c>
       <c r="O14" t="n">
-        <v>3.32</v>
+        <v>3.18</v>
       </c>
       <c r="P14" t="n">
-        <v>3.65</v>
+        <v>2.97</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.15</v>
+        <v>1.99</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.74</v>
+        <v>7.49</v>
       </c>
       <c r="O15" t="n">
-        <v>3.3</v>
+        <v>4.55</v>
       </c>
       <c r="P15" t="n">
-        <v>2.47</v>
+        <v>1.34</v>
       </c>
       <c r="Q15" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="T15" t="n">
         <v>3.2</v>
       </c>
-      <c r="R15" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.81</v>
-      </c>
       <c r="U15" t="n">
-        <v>2.81</v>
+        <v>2.5</v>
       </c>
       <c r="V15" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="W15" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X15" t="n">
         <v>1.03</v>
       </c>
-      <c r="X15" t="n">
-        <v>1.01</v>
-      </c>
       <c r="Y15" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.88</v>
+        <v>1.7</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.84</v>
+        <v>2.05</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.18</v>
+        <v>2.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.4</v>
+        <v>1.03</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.59</v>
+        <v>2.15</v>
       </c>
       <c r="O16" t="n">
-        <v>4.46</v>
+        <v>3.2</v>
       </c>
       <c r="P16" t="n">
-        <v>5.2</v>
+        <v>3.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.15</v>
+        <v>1.52</v>
       </c>
       <c r="O18" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="P18" t="n">
-        <v>3.1</v>
+        <v>5</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>4.46</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.36</v>
+        <v>2.53</v>
       </c>
       <c r="O21" t="n">
-        <v>4.3</v>
+        <v>3.38</v>
       </c>
       <c r="P21" t="n">
-        <v>7.5</v>
+        <v>2.39</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.53</v>
+        <v>1.36</v>
       </c>
       <c r="O22" t="n">
-        <v>3.38</v>
+        <v>4.3</v>
       </c>
       <c r="P22" t="n">
-        <v>2.39</v>
+        <v>7.5</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,64 +4700,64 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>2.61</v>
+        <v>2.09</v>
       </c>
       <c r="O27" t="n">
-        <v>2.86</v>
+        <v>3.22</v>
       </c>
       <c r="P27" t="n">
-        <v>3.01</v>
+        <v>3.62</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,64 +5018,64 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>2.09</v>
+        <v>2.61</v>
       </c>
       <c r="O29" t="n">
-        <v>3.22</v>
+        <v>2.86</v>
       </c>
       <c r="P29" t="n">
-        <v>3.62</v>
+        <v>3.01</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,64 +5177,64 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>3.22</v>
+        <v>1.89</v>
       </c>
       <c r="O30" t="n">
-        <v>2.91</v>
+        <v>2.95</v>
       </c>
       <c r="P30" t="n">
-        <v>2.44</v>
+        <v>4.1</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,64 +5336,64 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1.89</v>
+        <v>1.74</v>
       </c>
       <c r="O31" t="n">
-        <v>2.95</v>
+        <v>3.78</v>
       </c>
       <c r="P31" t="n">
-        <v>4.1</v>
+        <v>3.84</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,64 +5495,64 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>1.74</v>
+        <v>3.22</v>
       </c>
       <c r="O32" t="n">
-        <v>3.78</v>
+        <v>2.91</v>
       </c>
       <c r="P32" t="n">
-        <v>3.84</v>
+        <v>2.44</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.25</v>
+        <v>3.8</v>
       </c>
       <c r="R32" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="S32" t="n">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="T32" t="n">
-        <v>3.75</v>
+        <v>2.63</v>
       </c>
       <c r="U32" t="n">
-        <v>2.02</v>
+        <v>3.2</v>
       </c>
       <c r="V32" t="n">
-        <v>1.68</v>
+        <v>1.3</v>
       </c>
       <c r="W32" t="n">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="X32" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.09</v>
+        <v>1.37</v>
       </c>
       <c r="Z32" t="n">
-        <v>5.25</v>
+        <v>2.85</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.44</v>
+        <v>2.16</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.6</v>
+        <v>1.62</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.02</v>
+        <v>3.9</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.65</v>
+        <v>1.21</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.27</v>
+        <v>1.03</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.44</v>
+        <v>1.82</v>
       </c>
       <c r="AG32" t="n">
-        <v>2.63</v>
+        <v>1.78</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.9</v>
+        <v>1.36</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,43 +6131,43 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1.64</v>
+        <v>1.86</v>
       </c>
       <c r="O36" t="n">
-        <v>3.85</v>
+        <v>3.71</v>
       </c>
       <c r="P36" t="n">
         <v>4.15</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.09</v>
+        <v>2.25</v>
       </c>
       <c r="R36" t="n">
         <v>2.3</v>
       </c>
       <c r="S36" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T36" t="n">
-        <v>3.3</v>
+        <v>3.04</v>
       </c>
       <c r="U36" t="n">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="V36" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="W36" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X36" t="n">
         <v>1.04</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z36" t="n">
-        <v>3.95</v>
+        <v>4.14</v>
       </c>
       <c r="AA36" t="n">
         <v>1.76</v>
@@ -6176,19 +6176,19 @@
         <v>2.08</v>
       </c>
       <c r="AC36" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG36" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK36" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,43 +6449,43 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1.86</v>
+        <v>1.64</v>
       </c>
       <c r="O38" t="n">
-        <v>3.71</v>
+        <v>3.85</v>
       </c>
       <c r="P38" t="n">
         <v>4.15</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.25</v>
+        <v>2.09</v>
       </c>
       <c r="R38" t="n">
         <v>2.3</v>
       </c>
       <c r="S38" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T38" t="n">
-        <v>3.04</v>
+        <v>3.3</v>
       </c>
       <c r="U38" t="n">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="V38" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="W38" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X38" t="n">
         <v>1.04</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z38" t="n">
-        <v>4.14</v>
+        <v>3.95</v>
       </c>
       <c r="AA38" t="n">
         <v>1.76</v>
@@ -6494,19 +6494,19 @@
         <v>2.08</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG38" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK38" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7595,10 +7595,10 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA45" t="n">
         <v>0</v>
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -7913,10 +7913,10 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
         <v>0</v>

--- a/jogos_2026-07-11.xlsx
+++ b/jogos_2026-07-11.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.14</v>
+        <v>2.75</v>
       </c>
       <c r="O4" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P4" t="n">
-        <v>2.85</v>
+        <v>2.17</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>APIA Leichhardt Tigers</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Sydney II</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.66</v>
+        <v>1.27</v>
       </c>
       <c r="O5" t="n">
-        <v>3.65</v>
+        <v>5.1</v>
       </c>
       <c r="P5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>APIA Leichhardt Tigers</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sydney II</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.27</v>
+        <v>1.66</v>
       </c>
       <c r="O6" t="n">
-        <v>5.1</v>
+        <v>3.65</v>
       </c>
       <c r="P6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.74</v>
+        <v>2.05</v>
       </c>
       <c r="O9" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P9" t="n">
-        <v>2.47</v>
+        <v>3.35</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.2</v>
+        <v>2.51</v>
       </c>
       <c r="R9" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="S9" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="T9" t="n">
-        <v>2.81</v>
+        <v>2.75</v>
       </c>
       <c r="U9" t="n">
-        <v>2.81</v>
+        <v>2.9</v>
       </c>
       <c r="V9" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="W9" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.88</v>
+        <v>2.05</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.84</v>
+        <v>1.67</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.18</v>
+        <v>3.8</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AE9" t="n">
         <v>1.06</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.67</v>
+        <v>1.84</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.4</v>
+        <v>1.75</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2</v>
+        <v>2.23</v>
       </c>
       <c r="O10" t="n">
-        <v>3.32</v>
+        <v>3.18</v>
       </c>
       <c r="P10" t="n">
-        <v>3.65</v>
+        <v>2.97</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.15</v>
+        <v>1.99</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.02</v>
+        <v>6.07</v>
       </c>
       <c r="O11" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>5.61</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="U11" t="n">
         <v>3.22</v>
       </c>
-      <c r="P11" t="n">
-        <v>3.41</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="R11" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2.88</v>
-      </c>
       <c r="V11" t="n">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="W11" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X11" t="n">
         <v>1.06</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.2</v>
+        <v>2.72</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.97</v>
+        <v>2.15</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.95</v>
+        <v>1.57</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.77</v>
+        <v>1.11</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>6.07</v>
+        <v>7.49</v>
       </c>
       <c r="O12" t="n">
-        <v>3.7</v>
+        <v>4.55</v>
       </c>
       <c r="P12" t="n">
-        <v>1.58</v>
+        <v>1.34</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.61</v>
+        <v>6.95</v>
       </c>
       <c r="R12" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="S12" t="n">
-        <v>1.46</v>
+        <v>1.32</v>
       </c>
       <c r="T12" t="n">
-        <v>2.53</v>
+        <v>3.2</v>
       </c>
       <c r="U12" t="n">
-        <v>3.22</v>
+        <v>2.5</v>
       </c>
       <c r="V12" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="W12" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X12" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD12" t="n">
         <v>1.36</v>
       </c>
-      <c r="Z12" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AE12" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="O13" t="n">
-        <v>3.2</v>
+        <v>3.32</v>
       </c>
       <c r="P13" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,80 +2633,80 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.23</v>
+        <v>2.74</v>
       </c>
       <c r="O14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R14" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AC14" t="n">
         <v>3.18</v>
       </c>
-      <c r="P14" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="R14" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U14" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="V14" t="n">
+      <c r="AD14" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ14" t="n">
         <v>1.33</v>
       </c>
-      <c r="W14" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AK14" t="n">
-        <v>1.54</v>
+        <v>1.4</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,65 +2792,65 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>7.49</v>
+        <v>2.02</v>
       </c>
       <c r="O15" t="n">
-        <v>4.55</v>
+        <v>3.22</v>
       </c>
       <c r="P15" t="n">
-        <v>1.34</v>
+        <v>3.41</v>
       </c>
       <c r="Q15" t="n">
-        <v>6.95</v>
+        <v>2.3</v>
       </c>
       <c r="R15" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="S15" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="T15" t="n">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="U15" t="n">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="V15" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="W15" t="n">
         <v>1.07</v>
       </c>
       <c r="X15" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="Z15" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.7</v>
+        <v>1.97</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.05</v>
+        <v>1.73</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.4</v>
+        <v>3.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF15" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG15" t="n">
         <v>1.95</v>
       </c>
-      <c r="AG15" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AH15" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.03</v>
+        <v>1.77</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.15</v>
+        <v>3.18</v>
       </c>
       <c r="O16" t="n">
-        <v>3.2</v>
+        <v>3.48</v>
       </c>
       <c r="P16" t="n">
-        <v>3.1</v>
+        <v>2.25</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.52</v>
+        <v>2.15</v>
       </c>
       <c r="O18" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="P18" t="n">
-        <v>5</v>
+        <v>3.1</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>3.18</v>
+        <v>1.52</v>
       </c>
       <c r="O19" t="n">
-        <v>3.48</v>
+        <v>4.2</v>
       </c>
       <c r="P19" t="n">
-        <v>2.25</v>
+        <v>5</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.53</v>
+        <v>1.36</v>
       </c>
       <c r="O21" t="n">
-        <v>3.38</v>
+        <v>4.3</v>
       </c>
       <c r="P21" t="n">
-        <v>2.39</v>
+        <v>7.5</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.36</v>
+        <v>2.53</v>
       </c>
       <c r="O22" t="n">
-        <v>4.3</v>
+        <v>3.38</v>
       </c>
       <c r="P22" t="n">
-        <v>7.5</v>
+        <v>2.39</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,64 +4700,64 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>2.09</v>
+        <v>2.61</v>
       </c>
       <c r="O27" t="n">
-        <v>3.22</v>
+        <v>2.86</v>
       </c>
       <c r="P27" t="n">
-        <v>3.62</v>
+        <v>3.01</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,64 +5018,64 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>2.61</v>
+        <v>2.09</v>
       </c>
       <c r="O29" t="n">
-        <v>2.86</v>
+        <v>3.22</v>
       </c>
       <c r="P29" t="n">
-        <v>3.01</v>
+        <v>3.62</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="AJ29" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,64 +5336,64 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1.74</v>
+        <v>3.22</v>
       </c>
       <c r="O31" t="n">
-        <v>3.78</v>
+        <v>2.91</v>
       </c>
       <c r="P31" t="n">
-        <v>3.84</v>
+        <v>2.44</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.25</v>
+        <v>3.8</v>
       </c>
       <c r="R31" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="S31" t="n">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="T31" t="n">
-        <v>3.75</v>
+        <v>2.63</v>
       </c>
       <c r="U31" t="n">
-        <v>2.02</v>
+        <v>3.2</v>
       </c>
       <c r="V31" t="n">
-        <v>1.68</v>
+        <v>1.3</v>
       </c>
       <c r="W31" t="n">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="X31" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.09</v>
+        <v>1.37</v>
       </c>
       <c r="Z31" t="n">
-        <v>5.25</v>
+        <v>2.85</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.44</v>
+        <v>2.16</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.6</v>
+        <v>1.62</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.02</v>
+        <v>3.9</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.65</v>
+        <v>1.21</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.27</v>
+        <v>1.03</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.44</v>
+        <v>1.82</v>
       </c>
       <c r="AG31" t="n">
-        <v>2.63</v>
+        <v>1.78</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="AJ31" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.9</v>
+        <v>1.36</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,80 +5495,80 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>3.22</v>
+        <v>1.74</v>
       </c>
       <c r="O32" t="n">
-        <v>2.91</v>
+        <v>3.78</v>
       </c>
       <c r="P32" t="n">
-        <v>2.44</v>
+        <v>3.84</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.8</v>
+        <v>2.25</v>
       </c>
       <c r="R32" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="S32" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ32" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AK32" t="n">
         <v>1.9</v>
-      </c>
-      <c r="S32" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U32" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X32" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ32" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>1.36</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,64 +6290,64 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK37" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,64 +6449,64 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK38" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6800,10 +6800,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7595,10 +7595,10 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
         <v>0</v>
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G47" t="n">

--- a/jogos_2026-07-11.xlsx
+++ b/jogos_2026-07-11.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.75</v>
+        <v>2.14</v>
       </c>
       <c r="O4" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P4" t="n">
-        <v>2.17</v>
+        <v>2.85</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>APIA Leichhardt Tigers</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sydney II</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.27</v>
+        <v>1.66</v>
       </c>
       <c r="O5" t="n">
-        <v>5.1</v>
+        <v>3.65</v>
       </c>
       <c r="P5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>APIA Leichhardt Tigers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Sydney II</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.66</v>
+        <v>1.27</v>
       </c>
       <c r="O6" t="n">
-        <v>3.65</v>
+        <v>5.1</v>
       </c>
       <c r="P6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.05</v>
+        <v>2.74</v>
       </c>
       <c r="O9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="Q9" t="n">
         <v>3.2</v>
       </c>
-      <c r="P9" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2.51</v>
-      </c>
       <c r="R9" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="S9" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="T9" t="n">
-        <v>2.75</v>
+        <v>2.81</v>
       </c>
       <c r="U9" t="n">
-        <v>2.9</v>
+        <v>2.81</v>
       </c>
       <c r="V9" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="W9" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X9" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="Z9" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.05</v>
+        <v>1.88</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.67</v>
+        <v>1.84</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.8</v>
+        <v>3.18</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AE9" t="n">
         <v>1.06</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.84</v>
+        <v>1.67</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.23</v>
+        <v>2.02</v>
       </c>
       <c r="O10" t="n">
-        <v>3.18</v>
+        <v>3.22</v>
       </c>
       <c r="P10" t="n">
-        <v>2.97</v>
+        <v>3.41</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.86</v>
+        <v>2.3</v>
       </c>
       <c r="R10" t="n">
-        <v>2.03</v>
+        <v>2.2</v>
       </c>
       <c r="S10" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T10" t="n">
-        <v>2.63</v>
+        <v>2.88</v>
       </c>
       <c r="U10" t="n">
-        <v>2.91</v>
+        <v>2.88</v>
       </c>
       <c r="V10" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="W10" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X10" t="n">
         <v>1.06</v>
       </c>
-      <c r="X10" t="n">
-        <v>1.04</v>
-      </c>
       <c r="Y10" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.64</v>
+        <v>3.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.54</v>
+        <v>1.77</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>6.07</v>
+        <v>2</v>
       </c>
       <c r="O11" t="n">
-        <v>3.7</v>
+        <v>3.32</v>
       </c>
       <c r="P11" t="n">
-        <v>1.58</v>
+        <v>3.65</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.61</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
         <v>2.15</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2</v>
+        <v>6.07</v>
       </c>
       <c r="O13" t="n">
-        <v>3.32</v>
+        <v>3.7</v>
       </c>
       <c r="P13" t="n">
-        <v>3.65</v>
+        <v>1.58</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>5.61</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AA13" t="n">
         <v>2.15</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.74</v>
+        <v>2.23</v>
       </c>
       <c r="O14" t="n">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="P14" t="n">
-        <v>2.47</v>
+        <v>2.97</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.2</v>
+        <v>2.86</v>
       </c>
       <c r="R14" t="n">
-        <v>2.15</v>
+        <v>2.03</v>
       </c>
       <c r="S14" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="T14" t="n">
-        <v>2.81</v>
+        <v>2.63</v>
       </c>
       <c r="U14" t="n">
-        <v>2.81</v>
+        <v>2.91</v>
       </c>
       <c r="V14" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="W14" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.3</v>
+        <v>3.19</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.88</v>
+        <v>1.99</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.84</v>
+        <v>1.71</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.18</v>
+        <v>3.64</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.67</v>
+        <v>1.79</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.4</v>
+        <v>1.54</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="O15" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="P15" t="n">
-        <v>3.41</v>
+        <v>3.35</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.3</v>
+        <v>2.51</v>
       </c>
       <c r="R15" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="S15" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="T15" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="U15" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="V15" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="W15" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X15" t="n">
         <v>1.06</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2865,7 +2865,7 @@
         <v>1.3</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>3.18</v>
+        <v>1.59</v>
       </c>
       <c r="O16" t="n">
-        <v>3.48</v>
+        <v>4.46</v>
       </c>
       <c r="P16" t="n">
-        <v>2.25</v>
+        <v>5.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.4</v>
+        <v>1.97</v>
       </c>
       <c r="R16" t="n">
-        <v>2.3</v>
+        <v>2.49</v>
       </c>
       <c r="S16" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="T16" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="U16" t="n">
-        <v>2.5</v>
+        <v>2.13</v>
       </c>
       <c r="V16" t="n">
-        <v>1.46</v>
+        <v>1.67</v>
       </c>
       <c r="W16" t="n">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="X16" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="Z16" t="n">
         <v>5.1</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.73</v>
+        <v>1.44</v>
       </c>
       <c r="AB16" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.8</v>
+        <v>2.16</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.4</v>
+        <v>1.69</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.35</v>
+        <v>2.4</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>4.46</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>4.02</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.96</v>
+        <v>2.74</v>
       </c>
       <c r="R23" t="n">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
       <c r="S23" t="n">
-        <v>1.35</v>
+        <v>1.14</v>
       </c>
       <c r="T23" t="n">
-        <v>2.9</v>
+        <v>4.8</v>
       </c>
       <c r="U23" t="n">
-        <v>2.54</v>
+        <v>2</v>
       </c>
       <c r="V23" t="n">
-        <v>1.44</v>
+        <v>1.76</v>
       </c>
       <c r="W23" t="n">
-        <v>1.07</v>
+        <v>1.17</v>
       </c>
       <c r="X23" t="n">
         <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.24</v>
+        <v>1.11</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.54</v>
+        <v>11.8</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.82</v>
+        <v>1.36</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.01</v>
+        <v>3.36</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.22</v>
+        <v>1.84</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.38</v>
+        <v>1.87</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.14</v>
+        <v>1.32</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.61</v>
+        <v>1.33</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.18</v>
+        <v>3.1</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="R24" t="n">
         <v>2.31</v>
       </c>
-      <c r="O24" t="n">
-        <v>4.02</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="R24" t="n">
-        <v>2.38</v>
-      </c>
       <c r="S24" t="n">
-        <v>1.14</v>
+        <v>1.35</v>
       </c>
       <c r="T24" t="n">
-        <v>4.8</v>
+        <v>2.9</v>
       </c>
       <c r="U24" t="n">
-        <v>2</v>
+        <v>2.54</v>
       </c>
       <c r="V24" t="n">
-        <v>1.76</v>
+        <v>1.44</v>
       </c>
       <c r="W24" t="n">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="X24" t="n">
         <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.11</v>
+        <v>1.24</v>
       </c>
       <c r="Z24" t="n">
-        <v>11.8</v>
+        <v>4.54</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.36</v>
+        <v>1.82</v>
       </c>
       <c r="AB24" t="n">
-        <v>3.36</v>
+        <v>2.01</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.84</v>
+        <v>3.22</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.87</v>
+        <v>1.38</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.32</v>
+        <v>1.14</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.33</v>
+        <v>1.61</v>
       </c>
       <c r="AG24" t="n">
-        <v>3.1</v>
+        <v>2.18</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,64 +4700,64 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>2.61</v>
+        <v>2.19</v>
       </c>
       <c r="O27" t="n">
-        <v>2.86</v>
+        <v>3.56</v>
       </c>
       <c r="P27" t="n">
-        <v>3.01</v>
+        <v>3.03</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="R27" t="n">
-        <v>2.12</v>
+        <v>2.27</v>
       </c>
       <c r="S27" t="n">
-        <v>1.46</v>
+        <v>1.31</v>
       </c>
       <c r="T27" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="U27" t="n">
-        <v>3.1</v>
+        <v>2.53</v>
       </c>
       <c r="V27" t="n">
-        <v>1.31</v>
+        <v>1.45</v>
       </c>
       <c r="W27" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X27" t="n">
         <v>1.05</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.37</v>
+        <v>1.24</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.8</v>
+        <v>3.95</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.24</v>
+        <v>1.72</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.62</v>
+        <v>1.98</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.8</v>
+        <v>2.97</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.21</v>
+        <v>1.38</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.92</v>
+        <v>1.63</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.83</v>
+        <v>2.14</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,64 +4859,64 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>2.19</v>
+        <v>2.09</v>
       </c>
       <c r="O28" t="n">
-        <v>3.56</v>
+        <v>3.22</v>
       </c>
       <c r="P28" t="n">
-        <v>3.03</v>
+        <v>3.62</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="AJ28" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,64 +5018,64 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>2.09</v>
+        <v>2.61</v>
       </c>
       <c r="O29" t="n">
-        <v>3.22</v>
+        <v>2.86</v>
       </c>
       <c r="P29" t="n">
-        <v>3.62</v>
+        <v>3.01</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,64 +5336,64 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>3.22</v>
+        <v>3.5</v>
       </c>
       <c r="O31" t="n">
-        <v>2.91</v>
+        <v>3.87</v>
       </c>
       <c r="P31" t="n">
-        <v>2.44</v>
+        <v>1.99</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="R31" t="n">
-        <v>1.9</v>
+        <v>2.45</v>
       </c>
       <c r="S31" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF31" t="n">
         <v>1.44</v>
       </c>
-      <c r="T31" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U31" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X31" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>1.82</v>
-      </c>
       <c r="AG31" t="n">
-        <v>1.78</v>
+        <v>2.5</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="AJ31" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,64 +5495,64 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>1.74</v>
+        <v>3.22</v>
       </c>
       <c r="O32" t="n">
-        <v>3.78</v>
+        <v>2.91</v>
       </c>
       <c r="P32" t="n">
-        <v>3.84</v>
+        <v>2.44</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.25</v>
+        <v>3.8</v>
       </c>
       <c r="R32" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="S32" t="n">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="T32" t="n">
-        <v>3.75</v>
+        <v>2.63</v>
       </c>
       <c r="U32" t="n">
-        <v>2.02</v>
+        <v>3.2</v>
       </c>
       <c r="V32" t="n">
-        <v>1.68</v>
+        <v>1.3</v>
       </c>
       <c r="W32" t="n">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="X32" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.09</v>
+        <v>1.37</v>
       </c>
       <c r="Z32" t="n">
-        <v>5.25</v>
+        <v>2.85</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.44</v>
+        <v>2.16</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.6</v>
+        <v>1.62</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.02</v>
+        <v>3.9</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.65</v>
+        <v>1.21</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.27</v>
+        <v>1.03</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.44</v>
+        <v>1.82</v>
       </c>
       <c r="AG32" t="n">
-        <v>2.63</v>
+        <v>1.78</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.9</v>
+        <v>1.36</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,64 +5654,64 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>3.5</v>
+        <v>1.74</v>
       </c>
       <c r="O33" t="n">
-        <v>3.87</v>
+        <v>3.78</v>
       </c>
       <c r="P33" t="n">
-        <v>1.99</v>
+        <v>3.84</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.3</v>
+        <v>2.25</v>
       </c>
       <c r="R33" t="n">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="S33" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="T33" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="U33" t="n">
-        <v>2.25</v>
+        <v>2.02</v>
       </c>
       <c r="V33" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="W33" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="Z33" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.25</v>
+        <v>2.02</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AF33" t="n">
         <v>1.44</v>
       </c>
       <c r="AG33" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>1.7</v>
+        <v>1.18</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.35</v>
+        <v>1.9</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,43 +6131,43 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1.86</v>
+        <v>1.64</v>
       </c>
       <c r="O36" t="n">
-        <v>3.71</v>
+        <v>3.85</v>
       </c>
       <c r="P36" t="n">
         <v>4.15</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.25</v>
+        <v>2.09</v>
       </c>
       <c r="R36" t="n">
         <v>2.3</v>
       </c>
       <c r="S36" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T36" t="n">
-        <v>3.04</v>
+        <v>3.3</v>
       </c>
       <c r="U36" t="n">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="V36" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="W36" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X36" t="n">
         <v>1.04</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z36" t="n">
-        <v>4.14</v>
+        <v>3.95</v>
       </c>
       <c r="AA36" t="n">
         <v>1.76</v>
@@ -6176,19 +6176,19 @@
         <v>2.08</v>
       </c>
       <c r="AC36" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG36" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK36" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,43 +6290,43 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.64</v>
+        <v>1.86</v>
       </c>
       <c r="O37" t="n">
-        <v>3.85</v>
+        <v>3.71</v>
       </c>
       <c r="P37" t="n">
         <v>4.15</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.09</v>
+        <v>2.25</v>
       </c>
       <c r="R37" t="n">
         <v>2.3</v>
       </c>
       <c r="S37" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T37" t="n">
-        <v>3.3</v>
+        <v>3.04</v>
       </c>
       <c r="U37" t="n">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="V37" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="W37" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X37" t="n">
         <v>1.04</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z37" t="n">
-        <v>3.95</v>
+        <v>4.14</v>
       </c>
       <c r="AA37" t="n">
         <v>1.76</v>
@@ -6335,19 +6335,19 @@
         <v>2.08</v>
       </c>
       <c r="AC37" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG37" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK37" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6800,10 +6800,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7436,10 +7436,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G47" t="n">

--- a/jogos_2026-07-11.xlsx
+++ b/jogos_2026-07-11.xlsx
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>APIA Leichhardt Tigers</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Sydney II</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.66</v>
+        <v>1.27</v>
       </c>
       <c r="O5" t="n">
-        <v>3.65</v>
+        <v>5.1</v>
       </c>
       <c r="P5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>APIA Leichhardt Tigers</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sydney II</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.27</v>
+        <v>1.66</v>
       </c>
       <c r="O6" t="n">
-        <v>5.1</v>
+        <v>3.65</v>
       </c>
       <c r="P6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.74</v>
+        <v>2.02</v>
       </c>
       <c r="O9" t="n">
-        <v>3.3</v>
+        <v>3.22</v>
       </c>
       <c r="P9" t="n">
-        <v>2.47</v>
+        <v>3.41</v>
       </c>
       <c r="Q9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z9" t="n">
         <v>3.2</v>
       </c>
-      <c r="R9" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y9" t="n">
+      <c r="AA9" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD9" t="n">
         <v>1.25</v>
       </c>
-      <c r="Z9" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AE9" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.4</v>
+        <v>1.77</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.02</v>
+        <v>2.74</v>
       </c>
       <c r="O10" t="n">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="P10" t="n">
-        <v>3.41</v>
+        <v>2.47</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="R10" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S10" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T10" t="n">
-        <v>2.88</v>
+        <v>2.81</v>
       </c>
       <c r="U10" t="n">
-        <v>2.88</v>
+        <v>2.81</v>
       </c>
       <c r="V10" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W10" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AE10" t="n">
         <v>1.06</v>
       </c>
-      <c r="Y10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AF10" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.77</v>
+        <v>1.4</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2</v>
+        <v>2.23</v>
       </c>
       <c r="O11" t="n">
-        <v>3.32</v>
+        <v>3.18</v>
       </c>
       <c r="P11" t="n">
-        <v>3.65</v>
+        <v>2.97</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.15</v>
+        <v>1.99</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,80 +2315,80 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>7.49</v>
+        <v>6.07</v>
       </c>
       <c r="O12" t="n">
-        <v>4.55</v>
+        <v>3.7</v>
       </c>
       <c r="P12" t="n">
-        <v>1.34</v>
+        <v>1.58</v>
       </c>
       <c r="Q12" t="n">
-        <v>6.95</v>
+        <v>5.61</v>
       </c>
       <c r="R12" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="S12" t="n">
-        <v>1.32</v>
+        <v>1.46</v>
       </c>
       <c r="T12" t="n">
-        <v>3.2</v>
+        <v>2.53</v>
       </c>
       <c r="U12" t="n">
-        <v>2.5</v>
+        <v>3.22</v>
       </c>
       <c r="V12" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="W12" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X12" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="Z12" t="n">
-        <v>4</v>
+        <v>2.72</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.7</v>
+        <v>2.15</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.05</v>
+        <v>1.61</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.4</v>
+        <v>4.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="AE12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AK12" t="n">
         <v>1.11</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>1.03</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>6.07</v>
+        <v>7.49</v>
       </c>
       <c r="O13" t="n">
-        <v>3.7</v>
+        <v>4.55</v>
       </c>
       <c r="P13" t="n">
-        <v>1.58</v>
+        <v>1.34</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.61</v>
+        <v>6.95</v>
       </c>
       <c r="R13" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="S13" t="n">
-        <v>1.46</v>
+        <v>1.32</v>
       </c>
       <c r="T13" t="n">
-        <v>2.53</v>
+        <v>3.2</v>
       </c>
       <c r="U13" t="n">
-        <v>3.22</v>
+        <v>2.5</v>
       </c>
       <c r="V13" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="W13" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X13" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD13" t="n">
         <v>1.36</v>
       </c>
-      <c r="Z13" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AE13" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,28 +2633,28 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.23</v>
+        <v>2.05</v>
       </c>
       <c r="O14" t="n">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="P14" t="n">
-        <v>2.97</v>
+        <v>3.35</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.86</v>
+        <v>2.51</v>
       </c>
       <c r="R14" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="S14" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="T14" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="U14" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="V14" t="n">
         <v>1.33</v>
@@ -2663,34 +2663,34 @@
         <v>1.06</v>
       </c>
       <c r="X14" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y14" t="n">
         <v>1.33</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.19</v>
+        <v>3</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.64</v>
+        <v>3.8</v>
       </c>
       <c r="AD14" t="n">
         <v>1.22</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.54</v>
+        <v>1.75</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="O15" t="n">
-        <v>3.2</v>
+        <v>3.32</v>
       </c>
       <c r="P15" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.59</v>
+        <v>3.18</v>
       </c>
       <c r="O16" t="n">
-        <v>4.46</v>
+        <v>3.48</v>
       </c>
       <c r="P16" t="n">
-        <v>5.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.97</v>
+        <v>3.4</v>
       </c>
       <c r="R16" t="n">
-        <v>2.49</v>
+        <v>2.3</v>
       </c>
       <c r="S16" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="T16" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="U16" t="n">
-        <v>2.13</v>
+        <v>2.5</v>
       </c>
       <c r="V16" t="n">
-        <v>1.67</v>
+        <v>1.46</v>
       </c>
       <c r="W16" t="n">
-        <v>1.16</v>
+        <v>1.06</v>
       </c>
       <c r="X16" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="Z16" t="n">
         <v>5.1</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.44</v>
+        <v>1.73</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.16</v>
+        <v>2.8</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.69</v>
+        <v>1.4</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.4</v>
+        <v>1.35</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>3.18</v>
+        <v>1.59</v>
       </c>
       <c r="O17" t="n">
-        <v>3.48</v>
+        <v>4.46</v>
       </c>
       <c r="P17" t="n">
-        <v>2.25</v>
+        <v>5.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.4</v>
+        <v>1.97</v>
       </c>
       <c r="R17" t="n">
-        <v>2.3</v>
+        <v>2.49</v>
       </c>
       <c r="S17" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="T17" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="U17" t="n">
-        <v>2.5</v>
+        <v>2.13</v>
       </c>
       <c r="V17" t="n">
-        <v>1.46</v>
+        <v>1.67</v>
       </c>
       <c r="W17" t="n">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="X17" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="Z17" t="n">
         <v>5.1</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.73</v>
+        <v>1.44</v>
       </c>
       <c r="AB17" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.8</v>
+        <v>2.16</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.4</v>
+        <v>1.69</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.35</v>
+        <v>2.4</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.36</v>
+        <v>2.53</v>
       </c>
       <c r="O21" t="n">
-        <v>4.3</v>
+        <v>3.38</v>
       </c>
       <c r="P21" t="n">
-        <v>7.5</v>
+        <v>2.39</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.53</v>
+        <v>1.36</v>
       </c>
       <c r="O22" t="n">
-        <v>3.38</v>
+        <v>4.3</v>
       </c>
       <c r="P22" t="n">
-        <v>2.39</v>
+        <v>7.5</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="R23" t="n">
         <v>2.31</v>
       </c>
-      <c r="O23" t="n">
-        <v>4.02</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="R23" t="n">
-        <v>2.38</v>
-      </c>
       <c r="S23" t="n">
-        <v>1.14</v>
+        <v>1.35</v>
       </c>
       <c r="T23" t="n">
-        <v>4.8</v>
+        <v>2.9</v>
       </c>
       <c r="U23" t="n">
-        <v>2</v>
+        <v>2.54</v>
       </c>
       <c r="V23" t="n">
-        <v>1.76</v>
+        <v>1.44</v>
       </c>
       <c r="W23" t="n">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="X23" t="n">
         <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.11</v>
+        <v>1.24</v>
       </c>
       <c r="Z23" t="n">
-        <v>11.8</v>
+        <v>4.54</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.36</v>
+        <v>1.82</v>
       </c>
       <c r="AB23" t="n">
-        <v>3.36</v>
+        <v>2.01</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.84</v>
+        <v>3.22</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.87</v>
+        <v>1.38</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.32</v>
+        <v>1.14</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.33</v>
+        <v>1.61</v>
       </c>
       <c r="AG23" t="n">
-        <v>3.1</v>
+        <v>2.18</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>4.02</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.96</v>
+        <v>2.74</v>
       </c>
       <c r="R24" t="n">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
       <c r="S24" t="n">
-        <v>1.35</v>
+        <v>1.14</v>
       </c>
       <c r="T24" t="n">
-        <v>2.9</v>
+        <v>4.8</v>
       </c>
       <c r="U24" t="n">
-        <v>2.54</v>
+        <v>2</v>
       </c>
       <c r="V24" t="n">
-        <v>1.44</v>
+        <v>1.76</v>
       </c>
       <c r="W24" t="n">
-        <v>1.07</v>
+        <v>1.17</v>
       </c>
       <c r="X24" t="n">
         <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.24</v>
+        <v>1.11</v>
       </c>
       <c r="Z24" t="n">
-        <v>4.54</v>
+        <v>11.8</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.82</v>
+        <v>1.36</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.01</v>
+        <v>3.36</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.22</v>
+        <v>1.84</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.38</v>
+        <v>1.87</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.14</v>
+        <v>1.32</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.61</v>
+        <v>1.33</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.18</v>
+        <v>3.1</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,64 +4700,64 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>2.19</v>
+        <v>2.09</v>
       </c>
       <c r="O27" t="n">
-        <v>3.56</v>
+        <v>3.22</v>
       </c>
       <c r="P27" t="n">
-        <v>3.03</v>
+        <v>3.62</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,64 +4859,64 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>2.09</v>
+        <v>2.61</v>
       </c>
       <c r="O28" t="n">
-        <v>3.22</v>
+        <v>2.86</v>
       </c>
       <c r="P28" t="n">
-        <v>3.62</v>
+        <v>3.01</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,64 +5018,64 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>2.61</v>
+        <v>2.19</v>
       </c>
       <c r="O29" t="n">
-        <v>2.86</v>
+        <v>3.56</v>
       </c>
       <c r="P29" t="n">
-        <v>3.01</v>
+        <v>3.03</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="R29" t="n">
-        <v>2.12</v>
+        <v>2.27</v>
       </c>
       <c r="S29" t="n">
-        <v>1.46</v>
+        <v>1.31</v>
       </c>
       <c r="T29" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="U29" t="n">
-        <v>3.1</v>
+        <v>2.53</v>
       </c>
       <c r="V29" t="n">
-        <v>1.31</v>
+        <v>1.45</v>
       </c>
       <c r="W29" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X29" t="n">
         <v>1.05</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.37</v>
+        <v>1.24</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.8</v>
+        <v>3.95</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.24</v>
+        <v>1.72</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.62</v>
+        <v>1.98</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.8</v>
+        <v>2.97</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.21</v>
+        <v>1.38</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.92</v>
+        <v>1.63</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.83</v>
+        <v>2.14</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="AJ29" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,64 +5177,64 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1.89</v>
+        <v>3.22</v>
       </c>
       <c r="O30" t="n">
-        <v>2.95</v>
+        <v>2.91</v>
       </c>
       <c r="P30" t="n">
-        <v>4.1</v>
+        <v>2.44</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,64 +5336,64 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>3.5</v>
+        <v>1.89</v>
       </c>
       <c r="O31" t="n">
-        <v>3.87</v>
+        <v>2.95</v>
       </c>
       <c r="P31" t="n">
-        <v>1.99</v>
+        <v>4.1</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="AJ31" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,64 +5495,64 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>3.22</v>
+        <v>3.5</v>
       </c>
       <c r="O32" t="n">
-        <v>2.91</v>
+        <v>3.87</v>
       </c>
       <c r="P32" t="n">
-        <v>2.44</v>
+        <v>1.99</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="R32" t="n">
-        <v>1.9</v>
+        <v>2.45</v>
       </c>
       <c r="S32" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF32" t="n">
         <v>1.44</v>
       </c>
-      <c r="T32" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U32" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X32" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>1.82</v>
-      </c>
       <c r="AG32" t="n">
-        <v>1.78</v>
+        <v>2.5</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,64 +6290,64 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.86</v>
+        <v>1.32</v>
       </c>
       <c r="O37" t="n">
-        <v>3.71</v>
+        <v>4.8</v>
       </c>
       <c r="P37" t="n">
-        <v>4.15</v>
+        <v>7.8</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z37" t="n">
-        <v>4.14</v>
+        <v>4</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.76</v>
+        <v>1.61</v>
       </c>
       <c r="AB37" t="n">
         <v>2.08</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="AG37" t="n">
-        <v>2.1</v>
+        <v>1.78</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AK37" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,64 +6449,64 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6617,55 +6617,55 @@
         <v>2.75</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK39" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,64 +7085,64 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>6.23</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7155,10 +7155,10 @@
         </is>
       </c>
       <c r="AJ42" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK42" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL42" t="n">
         <v>0</v>
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>1.97</v>
+        <v>2.23</v>
       </c>
       <c r="O44" t="n">
-        <v>2.93</v>
+        <v>3.1</v>
       </c>
       <c r="P44" t="n">
-        <v>3.99</v>
+        <v>3.3</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7436,10 +7436,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -8207,55 +8207,55 @@
         <v>2.12</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>4.66</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD49" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG49" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8268,10 +8268,10 @@
         </is>
       </c>
       <c r="AJ49" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AK49" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AL49" t="n">
         <v>0</v>
@@ -8366,34 +8366,34 @@
         <v>2.22</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T50" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA50" t="n">
         <v>1.84</v>
@@ -8402,19 +8402,19 @@
         <v>1.81</v>
       </c>
       <c r="AC50" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD50" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG50" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8427,10 +8427,10 @@
         </is>
       </c>
       <c r="AJ50" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK50" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL50" t="n">
         <v>0</v>
@@ -8684,55 +8684,55 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S52" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T52" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U52" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V52" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W52" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X52" t="n">
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AC52" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD52" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG52" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8745,10 +8745,10 @@
         </is>
       </c>
       <c r="AJ52" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AK52" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AL52" t="n">
         <v>0</v>
@@ -8843,34 +8843,34 @@
         <v>3.75</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S53" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T53" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U53" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V53" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W53" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X53" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA53" t="n">
         <v>1.94</v>
@@ -8879,19 +8879,19 @@
         <v>1.71</v>
       </c>
       <c r="AC53" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD53" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG53" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -8904,10 +8904,10 @@
         </is>
       </c>
       <c r="AJ53" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK53" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL53" t="n">
         <v>0</v>

--- a/jogos_2026-07-11.xlsx
+++ b/jogos_2026-07-11.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.45</v>
+        <v>2.14</v>
       </c>
       <c r="O3" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="P3" t="n">
-        <v>2.4</v>
+        <v>2.85</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.14</v>
+        <v>2.45</v>
       </c>
       <c r="O4" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="P4" t="n">
-        <v>2.85</v>
+        <v>2.4</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="O9" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="P9" t="n">
-        <v>3.41</v>
+        <v>3.35</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.3</v>
+        <v>2.51</v>
       </c>
       <c r="R9" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="S9" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="T9" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="U9" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="V9" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="W9" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X9" t="n">
         <v>1.06</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>1.3</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.74</v>
+        <v>2.02</v>
       </c>
       <c r="O10" t="n">
-        <v>3.3</v>
+        <v>3.22</v>
       </c>
       <c r="P10" t="n">
-        <v>2.47</v>
+        <v>3.41</v>
       </c>
       <c r="Q10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z10" t="n">
         <v>3.2</v>
       </c>
-      <c r="R10" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y10" t="n">
+      <c r="AA10" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD10" t="n">
         <v>1.25</v>
       </c>
-      <c r="Z10" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AE10" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.4</v>
+        <v>1.77</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,65 +2315,65 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>6.07</v>
+        <v>2.74</v>
       </c>
       <c r="O12" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="P12" t="n">
-        <v>1.58</v>
+        <v>2.47</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.61</v>
+        <v>3.2</v>
       </c>
       <c r="R12" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG12" t="n">
         <v>2.1</v>
       </c>
-      <c r="S12" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="U12" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AH12" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.11</v>
+        <v>1.4</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,80 +2474,80 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>7.49</v>
+        <v>6.07</v>
       </c>
       <c r="O13" t="n">
-        <v>4.55</v>
+        <v>3.7</v>
       </c>
       <c r="P13" t="n">
-        <v>1.34</v>
+        <v>1.58</v>
       </c>
       <c r="Q13" t="n">
-        <v>6.95</v>
+        <v>5.61</v>
       </c>
       <c r="R13" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="S13" t="n">
-        <v>1.32</v>
+        <v>1.46</v>
       </c>
       <c r="T13" t="n">
-        <v>3.2</v>
+        <v>2.53</v>
       </c>
       <c r="U13" t="n">
-        <v>2.5</v>
+        <v>3.22</v>
       </c>
       <c r="V13" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="W13" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X13" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="Z13" t="n">
-        <v>4</v>
+        <v>2.72</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.7</v>
+        <v>2.15</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.05</v>
+        <v>1.61</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.4</v>
+        <v>4.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="AE13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AK13" t="n">
         <v>1.11</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1.03</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="O14" t="n">
-        <v>3.2</v>
+        <v>3.32</v>
       </c>
       <c r="P14" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2</v>
+        <v>7.49</v>
       </c>
       <c r="O15" t="n">
-        <v>3.32</v>
+        <v>4.55</v>
       </c>
       <c r="P15" t="n">
-        <v>3.65</v>
+        <v>1.34</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>6.95</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.15</v>
+        <v>1.7</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.66</v>
+        <v>2.05</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.59</v>
+        <v>3.18</v>
       </c>
       <c r="O17" t="n">
-        <v>4.46</v>
+        <v>3.48</v>
       </c>
       <c r="P17" t="n">
-        <v>5.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.97</v>
+        <v>3.4</v>
       </c>
       <c r="R17" t="n">
-        <v>2.49</v>
+        <v>2.3</v>
       </c>
       <c r="S17" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="T17" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="U17" t="n">
-        <v>2.13</v>
+        <v>2.5</v>
       </c>
       <c r="V17" t="n">
-        <v>1.67</v>
+        <v>1.46</v>
       </c>
       <c r="W17" t="n">
-        <v>1.16</v>
+        <v>1.06</v>
       </c>
       <c r="X17" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="Z17" t="n">
         <v>5.1</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.44</v>
+        <v>1.73</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.16</v>
+        <v>2.8</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.69</v>
+        <v>1.4</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.4</v>
+        <v>1.35</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.52</v>
+        <v>2.15</v>
       </c>
       <c r="O19" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="P19" t="n">
-        <v>5</v>
+        <v>3.1</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.15</v>
+        <v>1.59</v>
       </c>
       <c r="O20" t="n">
-        <v>3.2</v>
+        <v>4.46</v>
       </c>
       <c r="P20" t="n">
-        <v>3.1</v>
+        <v>5.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.53</v>
+        <v>1.36</v>
       </c>
       <c r="O21" t="n">
-        <v>3.38</v>
+        <v>4.3</v>
       </c>
       <c r="P21" t="n">
-        <v>2.39</v>
+        <v>7.5</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.36</v>
+        <v>2.53</v>
       </c>
       <c r="O22" t="n">
-        <v>4.3</v>
+        <v>3.38</v>
       </c>
       <c r="P22" t="n">
-        <v>7.5</v>
+        <v>2.39</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,64 +4700,64 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>2.09</v>
+        <v>2.61</v>
       </c>
       <c r="O27" t="n">
-        <v>3.22</v>
+        <v>2.86</v>
       </c>
       <c r="P27" t="n">
-        <v>3.62</v>
+        <v>3.01</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,64 +4859,64 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>2.61</v>
+        <v>2.09</v>
       </c>
       <c r="O28" t="n">
-        <v>2.86</v>
+        <v>3.22</v>
       </c>
       <c r="P28" t="n">
-        <v>3.01</v>
+        <v>3.62</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="AJ28" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,64 +5177,64 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>3.22</v>
+        <v>1.89</v>
       </c>
       <c r="O30" t="n">
-        <v>2.91</v>
+        <v>2.95</v>
       </c>
       <c r="P30" t="n">
-        <v>2.44</v>
+        <v>4.1</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,64 +5336,64 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1.89</v>
+        <v>3.22</v>
       </c>
       <c r="O31" t="n">
-        <v>2.95</v>
+        <v>2.91</v>
       </c>
       <c r="P31" t="n">
-        <v>4.1</v>
+        <v>2.44</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,64 +5495,64 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>3.5</v>
+        <v>1.74</v>
       </c>
       <c r="O32" t="n">
-        <v>3.87</v>
+        <v>3.78</v>
       </c>
       <c r="P32" t="n">
-        <v>1.99</v>
+        <v>3.84</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.3</v>
+        <v>2.25</v>
       </c>
       <c r="R32" t="n">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="S32" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="T32" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="U32" t="n">
-        <v>2.25</v>
+        <v>2.02</v>
       </c>
       <c r="V32" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="W32" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X32" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="Z32" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.25</v>
+        <v>2.02</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AF32" t="n">
         <v>1.44</v>
       </c>
       <c r="AG32" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>1.7</v>
+        <v>1.18</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.35</v>
+        <v>1.9</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,64 +5654,64 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1.74</v>
+        <v>3.5</v>
       </c>
       <c r="O33" t="n">
-        <v>3.78</v>
+        <v>3.87</v>
       </c>
       <c r="P33" t="n">
-        <v>3.84</v>
+        <v>1.99</v>
       </c>
       <c r="Q33" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R33" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="S33" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="T33" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U33" t="n">
         <v>2.25</v>
       </c>
-      <c r="R33" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="S33" t="n">
+      <c r="V33" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X33" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE33" t="n">
         <v>1.22</v>
-      </c>
-      <c r="T33" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="U33" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>1.27</v>
       </c>
       <c r="AF33" t="n">
         <v>1.44</v>
       </c>
       <c r="AG33" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>1.18</v>
+        <v>1.7</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.9</v>
+        <v>1.35</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,64 +6131,64 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1.64</v>
+        <v>1.32</v>
       </c>
       <c r="O36" t="n">
-        <v>3.85</v>
+        <v>4.8</v>
       </c>
       <c r="P36" t="n">
-        <v>4.15</v>
+        <v>7.8</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z36" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.76</v>
+        <v>1.61</v>
       </c>
       <c r="AB36" t="n">
         <v>2.08</v>
       </c>
       <c r="AC36" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AE36" t="n">
         <v>1.15</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AG36" t="n">
-        <v>2.05</v>
+        <v>1.78</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AK36" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,64 +6290,64 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.32</v>
+        <v>1.86</v>
       </c>
       <c r="O37" t="n">
-        <v>4.8</v>
+        <v>3.71</v>
       </c>
       <c r="P37" t="n">
-        <v>7.8</v>
+        <v>4.15</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z37" t="n">
-        <v>4</v>
+        <v>4.14</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.61</v>
+        <v>1.76</v>
       </c>
       <c r="AB37" t="n">
         <v>2.08</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.78</v>
+        <v>2.1</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AK37" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,43 +6449,43 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1.86</v>
+        <v>1.64</v>
       </c>
       <c r="O38" t="n">
-        <v>3.71</v>
+        <v>3.85</v>
       </c>
       <c r="P38" t="n">
         <v>4.15</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.25</v>
+        <v>2.09</v>
       </c>
       <c r="R38" t="n">
         <v>2.3</v>
       </c>
       <c r="S38" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T38" t="n">
-        <v>3.04</v>
+        <v>3.3</v>
       </c>
       <c r="U38" t="n">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="V38" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="W38" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X38" t="n">
         <v>1.04</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z38" t="n">
-        <v>4.14</v>
+        <v>3.95</v>
       </c>
       <c r="AA38" t="n">
         <v>1.76</v>
@@ -6494,19 +6494,19 @@
         <v>2.08</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG38" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK38" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="O41" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="P41" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,64 +7085,64 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>1.97</v>
+        <v>2.35</v>
       </c>
       <c r="O42" t="n">
-        <v>2.93</v>
+        <v>2.9</v>
       </c>
       <c r="P42" t="n">
-        <v>3.99</v>
+        <v>3.25</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>6.23</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7155,10 +7155,10 @@
         </is>
       </c>
       <c r="AJ42" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK42" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AL42" t="n">
         <v>0</v>
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,64 +7244,64 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>2.35</v>
+        <v>1.97</v>
       </c>
       <c r="O43" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="P43" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="Q43" t="n">
         <v>2.9</v>
       </c>
-      <c r="P43" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>6.23</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7314,10 +7314,10 @@
         </is>
       </c>
       <c r="AJ43" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK43" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL43" t="n">
         <v>0</v>
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>2.16</v>
+        <v>2</v>
       </c>
       <c r="O47" t="n">
-        <v>2.85</v>
+        <v>3.05</v>
       </c>
       <c r="P47" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>

--- a/jogos_2026-07-11.xlsx
+++ b/jogos_2026-07-11.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.75</v>
+        <v>2.14</v>
       </c>
       <c r="O2" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P2" t="n">
-        <v>2.17</v>
+        <v>2.85</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.14</v>
+        <v>2.45</v>
       </c>
       <c r="O3" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="P3" t="n">
-        <v>2.85</v>
+        <v>2.4</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="O4" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="P4" t="n">
-        <v>2.4</v>
+        <v>2.17</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,28 +1838,28 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.05</v>
+        <v>2.23</v>
       </c>
       <c r="O9" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="P9" t="n">
-        <v>3.35</v>
+        <v>2.97</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.51</v>
+        <v>2.86</v>
       </c>
       <c r="R9" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="S9" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="T9" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="U9" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="V9" t="n">
         <v>1.33</v>
@@ -1868,34 +1868,34 @@
         <v>1.06</v>
       </c>
       <c r="X9" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y9" t="n">
         <v>1.33</v>
       </c>
       <c r="Z9" t="n">
-        <v>3</v>
+        <v>3.19</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.8</v>
+        <v>3.64</v>
       </c>
       <c r="AD9" t="n">
         <v>1.22</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.75</v>
+        <v>1.54</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,80 +2156,80 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.23</v>
+        <v>2.74</v>
       </c>
       <c r="O11" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AC11" t="n">
         <v>3.18</v>
       </c>
-      <c r="P11" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="R11" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="V11" t="n">
+      <c r="AD11" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ11" t="n">
         <v>1.33</v>
       </c>
-      <c r="W11" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AK11" t="n">
-        <v>1.54</v>
+        <v>1.4</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.74</v>
+        <v>6.07</v>
       </c>
       <c r="O12" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="P12" t="n">
-        <v>2.47</v>
+        <v>1.58</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.2</v>
+        <v>5.61</v>
       </c>
       <c r="R12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AA12" t="n">
         <v>2.15</v>
       </c>
-      <c r="S12" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="U12" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.88</v>
-      </c>
       <c r="AB12" t="n">
-        <v>1.84</v>
+        <v>1.61</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.18</v>
+        <v>4.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.67</v>
+        <v>2.25</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.1</v>
+        <v>1.57</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.4</v>
+        <v>1.11</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>6.07</v>
+        <v>7.49</v>
       </c>
       <c r="O13" t="n">
-        <v>3.7</v>
+        <v>4.55</v>
       </c>
       <c r="P13" t="n">
-        <v>1.58</v>
+        <v>1.34</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.61</v>
+        <v>6.95</v>
       </c>
       <c r="R13" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="S13" t="n">
-        <v>1.46</v>
+        <v>1.32</v>
       </c>
       <c r="T13" t="n">
-        <v>2.53</v>
+        <v>3.2</v>
       </c>
       <c r="U13" t="n">
-        <v>3.22</v>
+        <v>2.5</v>
       </c>
       <c r="V13" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="W13" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X13" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD13" t="n">
         <v>1.36</v>
       </c>
-      <c r="Z13" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AE13" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="O14" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P14" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="R14" t="n">
         <v>2</v>
       </c>
-      <c r="O14" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="P14" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>7.49</v>
+        <v>2</v>
       </c>
       <c r="O15" t="n">
-        <v>4.55</v>
+        <v>3.32</v>
       </c>
       <c r="P15" t="n">
-        <v>1.34</v>
+        <v>3.65</v>
       </c>
       <c r="Q15" t="n">
-        <v>6.95</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.7</v>
+        <v>2.15</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.05</v>
+        <v>1.66</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.52</v>
+        <v>1.59</v>
       </c>
       <c r="O18" t="n">
-        <v>4.2</v>
+        <v>4.46</v>
       </c>
       <c r="P18" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.59</v>
+        <v>1.52</v>
       </c>
       <c r="O20" t="n">
-        <v>4.46</v>
+        <v>4.2</v>
       </c>
       <c r="P20" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,64 +4700,64 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>2.61</v>
+        <v>2.09</v>
       </c>
       <c r="O27" t="n">
-        <v>2.86</v>
+        <v>3.22</v>
       </c>
       <c r="P27" t="n">
-        <v>3.01</v>
+        <v>3.62</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,64 +4859,64 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>2.09</v>
+        <v>2.19</v>
       </c>
       <c r="O28" t="n">
-        <v>3.22</v>
+        <v>3.56</v>
       </c>
       <c r="P28" t="n">
-        <v>3.62</v>
+        <v>3.03</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,80 +5018,80 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>2.19</v>
+        <v>2.61</v>
       </c>
       <c r="O29" t="n">
-        <v>3.56</v>
+        <v>2.86</v>
       </c>
       <c r="P29" t="n">
-        <v>3.03</v>
+        <v>3.01</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="R29" t="n">
-        <v>2.27</v>
+        <v>2.12</v>
       </c>
       <c r="S29" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U29" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="V29" t="n">
         <v>1.31</v>
       </c>
-      <c r="T29" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U29" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.45</v>
-      </c>
       <c r="W29" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X29" t="n">
         <v>1.05</v>
       </c>
       <c r="Y29" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ29" t="n">
         <v>1.24</v>
       </c>
-      <c r="Z29" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ29" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AK29" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,64 +5177,64 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1.89</v>
+        <v>1.74</v>
       </c>
       <c r="O30" t="n">
-        <v>2.95</v>
+        <v>3.78</v>
       </c>
       <c r="P30" t="n">
-        <v>4.1</v>
+        <v>3.84</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,64 +5495,64 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>1.74</v>
+        <v>3.5</v>
       </c>
       <c r="O32" t="n">
-        <v>3.78</v>
+        <v>3.87</v>
       </c>
       <c r="P32" t="n">
-        <v>3.84</v>
+        <v>1.99</v>
       </c>
       <c r="Q32" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R32" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="S32" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U32" t="n">
         <v>2.25</v>
       </c>
-      <c r="R32" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="S32" t="n">
+      <c r="V32" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE32" t="n">
         <v>1.22</v>
-      </c>
-      <c r="T32" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="U32" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1.27</v>
       </c>
       <c r="AF32" t="n">
         <v>1.44</v>
       </c>
       <c r="AG32" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>1.18</v>
+        <v>1.7</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.9</v>
+        <v>1.35</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,64 +5654,64 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>3.5</v>
+        <v>1.89</v>
       </c>
       <c r="O33" t="n">
-        <v>3.87</v>
+        <v>2.95</v>
       </c>
       <c r="P33" t="n">
-        <v>1.99</v>
+        <v>4.1</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,64 +6131,64 @@
         </is>
       </c>
       <c r="N36" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="O36" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="P36" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="R36" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S36" t="n">
         <v>1.32</v>
       </c>
-      <c r="O36" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="P36" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
-      <c r="R36" t="n">
-        <v>0</v>
-      </c>
-      <c r="S36" t="n">
-        <v>0</v>
-      </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z36" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.61</v>
+        <v>1.76</v>
       </c>
       <c r="AB36" t="n">
         <v>2.08</v>
       </c>
       <c r="AC36" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AE36" t="n">
         <v>1.15</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.78</v>
+        <v>2.05</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AK36" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,64 +6290,64 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.86</v>
+        <v>1.32</v>
       </c>
       <c r="O37" t="n">
-        <v>3.71</v>
+        <v>4.8</v>
       </c>
       <c r="P37" t="n">
-        <v>4.15</v>
+        <v>7.8</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z37" t="n">
-        <v>4.14</v>
+        <v>4</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.76</v>
+        <v>1.61</v>
       </c>
       <c r="AB37" t="n">
         <v>2.08</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="AG37" t="n">
-        <v>2.1</v>
+        <v>1.78</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AK37" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,43 +6449,43 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1.64</v>
+        <v>1.86</v>
       </c>
       <c r="O38" t="n">
-        <v>3.85</v>
+        <v>3.71</v>
       </c>
       <c r="P38" t="n">
         <v>4.15</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.09</v>
+        <v>2.25</v>
       </c>
       <c r="R38" t="n">
         <v>2.3</v>
       </c>
       <c r="S38" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T38" t="n">
-        <v>3.3</v>
+        <v>3.04</v>
       </c>
       <c r="U38" t="n">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="V38" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="W38" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X38" t="n">
         <v>1.04</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z38" t="n">
-        <v>3.95</v>
+        <v>4.14</v>
       </c>
       <c r="AA38" t="n">
         <v>1.76</v>
@@ -6494,19 +6494,19 @@
         <v>2.08</v>
       </c>
       <c r="AC38" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG38" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK38" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,64 +6926,64 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>2.04</v>
+        <v>1.97</v>
       </c>
       <c r="O41" t="n">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="P41" t="n">
-        <v>4</v>
+        <v>3.99</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>6.23</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -6996,10 +6996,10 @@
         </is>
       </c>
       <c r="AJ41" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK41" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL41" t="n">
         <v>0</v>
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,64 +7244,64 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="O43" t="n">
-        <v>2.93</v>
+        <v>3</v>
       </c>
       <c r="P43" t="n">
-        <v>3.99</v>
+        <v>4.4</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>6.23</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF43" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7314,10 +7314,10 @@
         </is>
       </c>
       <c r="AJ43" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK43" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AL43" t="n">
         <v>0</v>
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="O46" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="P46" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>

--- a/jogos_2026-07-11.xlsx
+++ b/jogos_2026-07-11.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.14</v>
+        <v>2.75</v>
       </c>
       <c r="O2" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P2" t="n">
-        <v>2.85</v>
+        <v>2.17</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.45</v>
+        <v>2.14</v>
       </c>
       <c r="O3" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="P3" t="n">
-        <v>2.4</v>
+        <v>2.85</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.75</v>
+        <v>2.45</v>
       </c>
       <c r="O4" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="P4" t="n">
-        <v>2.17</v>
+        <v>2.4</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,28 +1838,28 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.23</v>
+        <v>2.05</v>
       </c>
       <c r="O9" t="n">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="P9" t="n">
-        <v>2.97</v>
+        <v>3.35</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.86</v>
+        <v>2.51</v>
       </c>
       <c r="R9" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="S9" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="T9" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="U9" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="V9" t="n">
         <v>1.33</v>
@@ -1868,34 +1868,34 @@
         <v>1.06</v>
       </c>
       <c r="X9" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y9" t="n">
         <v>1.33</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.19</v>
+        <v>3</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.64</v>
+        <v>3.8</v>
       </c>
       <c r="AD9" t="n">
         <v>1.22</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.54</v>
+        <v>1.75</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,65 +1997,65 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.02</v>
+        <v>7.49</v>
       </c>
       <c r="O10" t="n">
-        <v>3.22</v>
+        <v>4.55</v>
       </c>
       <c r="P10" t="n">
-        <v>3.41</v>
+        <v>1.34</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.3</v>
+        <v>6.95</v>
       </c>
       <c r="R10" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="S10" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="T10" t="n">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="U10" t="n">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="V10" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="W10" t="n">
         <v>1.07</v>
       </c>
       <c r="X10" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.97</v>
+        <v>1.7</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.73</v>
+        <v>2.05</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF10" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG10" t="n">
         <v>1.75</v>
       </c>
-      <c r="AG10" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AH10" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.77</v>
+        <v>1.03</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.74</v>
+        <v>2.02</v>
       </c>
       <c r="O11" t="n">
-        <v>3.3</v>
+        <v>3.22</v>
       </c>
       <c r="P11" t="n">
-        <v>2.47</v>
+        <v>3.41</v>
       </c>
       <c r="Q11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z11" t="n">
         <v>3.2</v>
       </c>
-      <c r="R11" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y11" t="n">
+      <c r="AA11" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD11" t="n">
         <v>1.25</v>
       </c>
-      <c r="Z11" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AE11" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.4</v>
+        <v>1.77</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>6.07</v>
+        <v>2.23</v>
       </c>
       <c r="O12" t="n">
-        <v>3.7</v>
+        <v>3.18</v>
       </c>
       <c r="P12" t="n">
-        <v>1.58</v>
+        <v>2.97</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.61</v>
+        <v>2.86</v>
       </c>
       <c r="R12" t="n">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="S12" t="n">
-        <v>1.46</v>
+        <v>1.37</v>
       </c>
       <c r="T12" t="n">
-        <v>2.53</v>
+        <v>2.63</v>
       </c>
       <c r="U12" t="n">
-        <v>3.22</v>
+        <v>2.91</v>
       </c>
       <c r="V12" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W12" t="n">
         <v>1.06</v>
       </c>
       <c r="X12" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.72</v>
+        <v>3.19</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.15</v>
+        <v>1.99</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.61</v>
+        <v>1.71</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.2</v>
+        <v>3.64</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.25</v>
+        <v>1.79</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.57</v>
+        <v>1.9</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.11</v>
+        <v>1.54</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>7.49</v>
+        <v>2.74</v>
       </c>
       <c r="O13" t="n">
-        <v>4.55</v>
+        <v>3.3</v>
       </c>
       <c r="P13" t="n">
-        <v>1.34</v>
+        <v>2.47</v>
       </c>
       <c r="Q13" t="n">
-        <v>6.95</v>
+        <v>3.2</v>
       </c>
       <c r="R13" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="S13" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="T13" t="n">
-        <v>3.2</v>
+        <v>2.81</v>
       </c>
       <c r="U13" t="n">
-        <v>2.5</v>
+        <v>2.81</v>
       </c>
       <c r="V13" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="W13" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z13" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.7</v>
+        <v>1.88</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.05</v>
+        <v>1.84</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.4</v>
+        <v>3.18</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.03</v>
+        <v>1.4</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="O14" t="n">
-        <v>3.2</v>
+        <v>3.32</v>
       </c>
       <c r="P14" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2</v>
+        <v>6.07</v>
       </c>
       <c r="O15" t="n">
-        <v>3.32</v>
+        <v>3.7</v>
       </c>
       <c r="P15" t="n">
-        <v>3.65</v>
+        <v>1.58</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>5.61</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AA15" t="n">
         <v>2.15</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.15</v>
+        <v>3.18</v>
       </c>
       <c r="O16" t="n">
-        <v>3.2</v>
+        <v>3.48</v>
       </c>
       <c r="P16" t="n">
-        <v>3.1</v>
+        <v>2.25</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>3.18</v>
+        <v>2.15</v>
       </c>
       <c r="O17" t="n">
-        <v>3.48</v>
+        <v>3.2</v>
       </c>
       <c r="P17" t="n">
-        <v>2.25</v>
+        <v>3.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>4.46</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>4.46</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,64 +4700,64 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>2.09</v>
+        <v>2.61</v>
       </c>
       <c r="O27" t="n">
-        <v>3.22</v>
+        <v>2.86</v>
       </c>
       <c r="P27" t="n">
-        <v>3.62</v>
+        <v>3.01</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,64 +4859,64 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>2.19</v>
+        <v>2.09</v>
       </c>
       <c r="O28" t="n">
-        <v>3.56</v>
+        <v>3.22</v>
       </c>
       <c r="P28" t="n">
-        <v>3.03</v>
+        <v>3.62</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="AJ28" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,64 +5018,64 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>2.61</v>
+        <v>2.19</v>
       </c>
       <c r="O29" t="n">
-        <v>2.86</v>
+        <v>3.56</v>
       </c>
       <c r="P29" t="n">
-        <v>3.01</v>
+        <v>3.03</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="R29" t="n">
-        <v>2.12</v>
+        <v>2.27</v>
       </c>
       <c r="S29" t="n">
-        <v>1.46</v>
+        <v>1.31</v>
       </c>
       <c r="T29" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="U29" t="n">
-        <v>3.1</v>
+        <v>2.53</v>
       </c>
       <c r="V29" t="n">
-        <v>1.31</v>
+        <v>1.45</v>
       </c>
       <c r="W29" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X29" t="n">
         <v>1.05</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.37</v>
+        <v>1.24</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.8</v>
+        <v>3.95</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.24</v>
+        <v>1.72</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.62</v>
+        <v>1.98</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.8</v>
+        <v>2.97</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.21</v>
+        <v>1.38</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.92</v>
+        <v>1.63</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.83</v>
+        <v>2.14</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="AJ29" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,64 +5177,64 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1.74</v>
+        <v>3.22</v>
       </c>
       <c r="O30" t="n">
-        <v>3.78</v>
+        <v>2.91</v>
       </c>
       <c r="P30" t="n">
-        <v>3.84</v>
+        <v>2.44</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.25</v>
+        <v>3.8</v>
       </c>
       <c r="R30" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="S30" t="n">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="T30" t="n">
-        <v>3.75</v>
+        <v>2.63</v>
       </c>
       <c r="U30" t="n">
-        <v>2.02</v>
+        <v>3.2</v>
       </c>
       <c r="V30" t="n">
-        <v>1.68</v>
+        <v>1.3</v>
       </c>
       <c r="W30" t="n">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="X30" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.09</v>
+        <v>1.37</v>
       </c>
       <c r="Z30" t="n">
-        <v>5.25</v>
+        <v>2.85</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.44</v>
+        <v>2.16</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.6</v>
+        <v>1.62</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.02</v>
+        <v>3.9</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.65</v>
+        <v>1.21</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.27</v>
+        <v>1.03</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.44</v>
+        <v>1.82</v>
       </c>
       <c r="AG30" t="n">
-        <v>2.63</v>
+        <v>1.78</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.9</v>
+        <v>1.36</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,80 +5336,80 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>3.22</v>
+        <v>1.74</v>
       </c>
       <c r="O31" t="n">
-        <v>2.91</v>
+        <v>3.78</v>
       </c>
       <c r="P31" t="n">
-        <v>2.44</v>
+        <v>3.84</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.8</v>
+        <v>2.25</v>
       </c>
       <c r="R31" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="S31" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ31" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AK31" t="n">
         <v>1.9</v>
-      </c>
-      <c r="S31" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U31" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X31" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ31" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>1.36</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,64 +5495,64 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>3.5</v>
+        <v>1.89</v>
       </c>
       <c r="O32" t="n">
-        <v>3.87</v>
+        <v>2.95</v>
       </c>
       <c r="P32" t="n">
-        <v>1.99</v>
+        <v>4.1</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,64 +5654,64 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1.89</v>
+        <v>3.5</v>
       </c>
       <c r="O33" t="n">
-        <v>2.95</v>
+        <v>3.87</v>
       </c>
       <c r="P33" t="n">
-        <v>4.1</v>
+        <v>1.99</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,64 +6131,64 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1.64</v>
+        <v>1.32</v>
       </c>
       <c r="O36" t="n">
-        <v>3.85</v>
+        <v>4.8</v>
       </c>
       <c r="P36" t="n">
-        <v>4.15</v>
+        <v>7.8</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z36" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.76</v>
+        <v>1.61</v>
       </c>
       <c r="AB36" t="n">
         <v>2.08</v>
       </c>
       <c r="AC36" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AE36" t="n">
         <v>1.15</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AG36" t="n">
-        <v>2.05</v>
+        <v>1.78</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AK36" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,64 +6290,64 @@
         </is>
       </c>
       <c r="N37" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="O37" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="P37" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="R37" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S37" t="n">
         <v>1.32</v>
       </c>
-      <c r="O37" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="P37" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
-      <c r="R37" t="n">
-        <v>0</v>
-      </c>
-      <c r="S37" t="n">
-        <v>0</v>
-      </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z37" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.61</v>
+        <v>1.76</v>
       </c>
       <c r="AB37" t="n">
         <v>2.08</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AE37" t="n">
         <v>1.15</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.78</v>
+        <v>2.05</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AK37" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>2.16</v>
+        <v>2.35</v>
       </c>
       <c r="O40" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="P40" t="n">
-        <v>3.85</v>
+        <v>3.25</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,64 +6926,64 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>1.97</v>
+        <v>2.23</v>
       </c>
       <c r="O41" t="n">
-        <v>2.93</v>
+        <v>3.1</v>
       </c>
       <c r="P41" t="n">
-        <v>3.99</v>
+        <v>3.3</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>6.23</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG41" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -6996,10 +6996,10 @@
         </is>
       </c>
       <c r="AJ41" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK41" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AL41" t="n">
         <v>0</v>
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>2.23</v>
+        <v>2.04</v>
       </c>
       <c r="O44" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P44" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="O45" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="P45" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,64 +7721,64 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="O46" t="n">
-        <v>3.05</v>
+        <v>2.93</v>
       </c>
       <c r="P46" t="n">
-        <v>4.1</v>
+        <v>3.99</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>6.23</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7791,10 +7791,10 @@
         </is>
       </c>
       <c r="AJ46" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK46" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL46" t="n">
         <v>0</v>
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>

--- a/jogos_2026-07-11.xlsx
+++ b/jogos_2026-07-11.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.14</v>
+        <v>2.45</v>
       </c>
       <c r="O3" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="P3" t="n">
-        <v>2.85</v>
+        <v>2.4</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.45</v>
+        <v>2.14</v>
       </c>
       <c r="O4" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="P4" t="n">
-        <v>2.4</v>
+        <v>2.85</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,31 +1838,31 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.05</v>
+        <v>6.07</v>
       </c>
       <c r="O9" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="P9" t="n">
-        <v>3.35</v>
+        <v>1.58</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.51</v>
+        <v>5.61</v>
       </c>
       <c r="R9" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S9" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="T9" t="n">
-        <v>2.75</v>
+        <v>2.53</v>
       </c>
       <c r="U9" t="n">
-        <v>2.9</v>
+        <v>3.22</v>
       </c>
       <c r="V9" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W9" t="n">
         <v>1.06</v>
@@ -1871,31 +1871,31 @@
         <v>1.06</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z9" t="n">
-        <v>3</v>
+        <v>2.72</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.84</v>
+        <v>2.25</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.75</v>
+        <v>1.11</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,80 +1997,80 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>7.49</v>
+        <v>2.05</v>
       </c>
       <c r="O10" t="n">
-        <v>4.55</v>
+        <v>3.2</v>
       </c>
       <c r="P10" t="n">
-        <v>1.34</v>
+        <v>3.35</v>
       </c>
       <c r="Q10" t="n">
-        <v>6.95</v>
+        <v>2.38</v>
       </c>
       <c r="R10" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="S10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="V10" t="n">
         <v>1.32</v>
       </c>
-      <c r="T10" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.44</v>
-      </c>
       <c r="W10" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X10" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y10" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ10" t="n">
         <v>1.22</v>
       </c>
-      <c r="Z10" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG10" t="n">
+      <c r="AK10" t="n">
         <v>1.75</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>1.03</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="O11" t="n">
-        <v>3.22</v>
+        <v>3.32</v>
       </c>
       <c r="P11" t="n">
-        <v>3.41</v>
+        <v>3.65</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.97</v>
+        <v>2.15</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.23</v>
+        <v>1.87</v>
       </c>
       <c r="O12" t="n">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="P12" t="n">
-        <v>2.97</v>
+        <v>3.6</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.86</v>
+        <v>2.52</v>
       </c>
       <c r="R12" t="n">
-        <v>2.03</v>
+        <v>2.2</v>
       </c>
       <c r="S12" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="T12" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="U12" t="n">
-        <v>2.91</v>
+        <v>2.8</v>
       </c>
       <c r="V12" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="W12" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X12" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.19</v>
+        <v>3.14</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.99</v>
+        <v>1.92</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.64</v>
+        <v>3.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF12" t="n">
         <v>1.79</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.54</v>
+        <v>1.83</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2</v>
+        <v>2.23</v>
       </c>
       <c r="O14" t="n">
-        <v>3.32</v>
+        <v>3.18</v>
       </c>
       <c r="P14" t="n">
-        <v>3.65</v>
+        <v>2.97</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,80 +2792,80 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>6.07</v>
+        <v>6.2</v>
       </c>
       <c r="O15" t="n">
-        <v>3.7</v>
+        <v>4.55</v>
       </c>
       <c r="P15" t="n">
-        <v>1.58</v>
+        <v>1.34</v>
       </c>
       <c r="Q15" t="n">
-        <v>5.61</v>
+        <v>6.25</v>
       </c>
       <c r="R15" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="S15" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD15" t="n">
         <v>1.46</v>
       </c>
-      <c r="T15" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="U15" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W15" t="n">
+      <c r="AE15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ15" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AK15" t="n">
         <v>1.06</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1.11</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.15</v>
+        <v>1.59</v>
       </c>
       <c r="O17" t="n">
-        <v>3.2</v>
+        <v>4.46</v>
       </c>
       <c r="P17" t="n">
-        <v>3.1</v>
+        <v>5.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.59</v>
+        <v>2.15</v>
       </c>
       <c r="O19" t="n">
-        <v>4.46</v>
+        <v>3.2</v>
       </c>
       <c r="P19" t="n">
-        <v>5.2</v>
+        <v>3.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.52</v>
+        <v>3.18</v>
       </c>
       <c r="O20" t="n">
-        <v>4.2</v>
+        <v>3.48</v>
       </c>
       <c r="P20" t="n">
-        <v>5</v>
+        <v>2.25</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.36</v>
+        <v>2.53</v>
       </c>
       <c r="O21" t="n">
-        <v>4.3</v>
+        <v>3.38</v>
       </c>
       <c r="P21" t="n">
-        <v>7.5</v>
+        <v>2.39</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.53</v>
+        <v>1.36</v>
       </c>
       <c r="O22" t="n">
-        <v>3.38</v>
+        <v>4.3</v>
       </c>
       <c r="P22" t="n">
-        <v>2.39</v>
+        <v>7.5</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,65 +4382,65 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1.45</v>
+        <v>2.81</v>
       </c>
       <c r="O25" t="n">
-        <v>4.64</v>
+        <v>3.54</v>
       </c>
       <c r="P25" t="n">
-        <v>6.95</v>
+        <v>2.45</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.75</v>
+        <v>3.38</v>
       </c>
       <c r="R25" t="n">
-        <v>2.47</v>
+        <v>2.25</v>
       </c>
       <c r="S25" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="T25" t="n">
-        <v>3.25</v>
+        <v>2.99</v>
       </c>
       <c r="U25" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="V25" t="n">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="W25" t="n">
         <v>1.11</v>
       </c>
       <c r="X25" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="Z25" t="n">
-        <v>4.33</v>
+        <v>3.8</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.62</v>
+        <v>1.76</v>
       </c>
       <c r="AB25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG25" t="n">
         <v>2.2</v>
       </c>
-      <c r="AC25" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.77</v>
-      </c>
       <c r="AH25" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>1.17</v>
+        <v>1.53</v>
       </c>
       <c r="AK25" t="n">
-        <v>3.1</v>
+        <v>1.43</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,64 +4541,64 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>2.81</v>
+        <v>1.45</v>
       </c>
       <c r="O26" t="n">
-        <v>3.54</v>
+        <v>4.64</v>
       </c>
       <c r="P26" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="R26" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="S26" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U26" t="n">
         <v>2.45</v>
       </c>
-      <c r="Q26" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="R26" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="S26" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="U26" t="n">
-        <v>2.5</v>
-      </c>
       <c r="V26" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="W26" t="n">
         <v>1.11</v>
       </c>
       <c r="X26" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.8</v>
+        <v>4.33</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.76</v>
+        <v>1.62</v>
       </c>
       <c r="AB26" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.88</v>
+        <v>2.63</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.2</v>
+        <v>1.77</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>1.53</v>
+        <v>1.17</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.43</v>
+        <v>3.1</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,64 +4700,64 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>2.61</v>
+        <v>2.13</v>
       </c>
       <c r="O27" t="n">
-        <v>2.86</v>
+        <v>3.21</v>
       </c>
       <c r="P27" t="n">
-        <v>3.01</v>
+        <v>3.52</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,64 +4859,64 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>2.09</v>
+        <v>2.19</v>
       </c>
       <c r="O28" t="n">
-        <v>3.22</v>
+        <v>3.56</v>
       </c>
       <c r="P28" t="n">
-        <v>3.62</v>
+        <v>3.03</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,80 +5018,80 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>2.19</v>
+        <v>2.61</v>
       </c>
       <c r="O29" t="n">
-        <v>3.56</v>
+        <v>2.86</v>
       </c>
       <c r="P29" t="n">
-        <v>3.03</v>
+        <v>3.01</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.45</v>
+        <v>3.1</v>
       </c>
       <c r="R29" t="n">
-        <v>2.27</v>
+        <v>1.97</v>
       </c>
       <c r="S29" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="U29" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="V29" t="n">
         <v>1.31</v>
       </c>
-      <c r="T29" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U29" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.45</v>
-      </c>
       <c r="W29" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X29" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y29" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ29" t="n">
         <v>1.24</v>
       </c>
-      <c r="Z29" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ29" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AK29" t="n">
-        <v>1.8</v>
+        <v>1.52</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,64 +5177,64 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>3.22</v>
+        <v>3.5</v>
       </c>
       <c r="O30" t="n">
-        <v>2.91</v>
+        <v>3.87</v>
       </c>
       <c r="P30" t="n">
-        <v>2.44</v>
+        <v>1.99</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="R30" t="n">
-        <v>1.9</v>
+        <v>2.45</v>
       </c>
       <c r="S30" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF30" t="n">
         <v>1.44</v>
       </c>
-      <c r="T30" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U30" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X30" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>1.82</v>
-      </c>
       <c r="AG30" t="n">
-        <v>1.78</v>
+        <v>2.5</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,64 +5336,64 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1.74</v>
+        <v>1.89</v>
       </c>
       <c r="O31" t="n">
-        <v>3.78</v>
+        <v>2.95</v>
       </c>
       <c r="P31" t="n">
-        <v>3.84</v>
+        <v>4.1</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="AJ31" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,64 +5495,64 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>1.89</v>
+        <v>2.75</v>
       </c>
       <c r="O32" t="n">
-        <v>2.95</v>
+        <v>3.01</v>
       </c>
       <c r="P32" t="n">
-        <v>4.1</v>
+        <v>2.7</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK32" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,64 +5654,64 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>3.5</v>
+        <v>1.74</v>
       </c>
       <c r="O33" t="n">
-        <v>3.87</v>
+        <v>3.78</v>
       </c>
       <c r="P33" t="n">
-        <v>1.99</v>
+        <v>3.84</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.3</v>
+        <v>2.25</v>
       </c>
       <c r="R33" t="n">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="S33" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="T33" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="U33" t="n">
-        <v>2.25</v>
+        <v>2.02</v>
       </c>
       <c r="V33" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="W33" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="Z33" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.25</v>
+        <v>2.02</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AF33" t="n">
         <v>1.44</v>
       </c>
       <c r="AG33" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>1.7</v>
+        <v>1.18</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.35</v>
+        <v>1.9</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -5813,19 +5813,19 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>12</v>
+        <v>7.5</v>
       </c>
       <c r="O34" t="n">
         <v>3.92</v>
       </c>
       <c r="P34" t="n">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="Q34" t="n">
-        <v>7.3</v>
+        <v>5.5</v>
       </c>
       <c r="R34" t="n">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="S34" t="n">
         <v>1.33</v>
@@ -5837,7 +5837,7 @@
         <v>2.85</v>
       </c>
       <c r="V34" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W34" t="n">
         <v>1.08</v>
@@ -5846,7 +5846,7 @@
         <v>1.02</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Z34" t="n">
         <v>3.55</v>
@@ -5858,19 +5858,19 @@
         <v>1.8</v>
       </c>
       <c r="AC34" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="AE34" t="n">
         <v>1.06</v>
       </c>
       <c r="AF34" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.64</v>
+        <v>1.82</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,64 +6131,64 @@
         </is>
       </c>
       <c r="N36" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="O36" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="P36" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="R36" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S36" t="n">
         <v>1.32</v>
       </c>
-      <c r="O36" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="P36" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
-      <c r="R36" t="n">
-        <v>0</v>
-      </c>
-      <c r="S36" t="n">
-        <v>0</v>
-      </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z36" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.61</v>
+        <v>1.76</v>
       </c>
       <c r="AB36" t="n">
         <v>2.08</v>
       </c>
       <c r="AC36" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AE36" t="n">
         <v>1.15</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.78</v>
+        <v>2.05</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AK36" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,43 +6290,43 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.64</v>
+        <v>1.86</v>
       </c>
       <c r="O37" t="n">
-        <v>3.85</v>
+        <v>3.71</v>
       </c>
       <c r="P37" t="n">
         <v>4.15</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.09</v>
+        <v>2.25</v>
       </c>
       <c r="R37" t="n">
         <v>2.3</v>
       </c>
       <c r="S37" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T37" t="n">
-        <v>3.3</v>
+        <v>3.04</v>
       </c>
       <c r="U37" t="n">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="V37" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="W37" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X37" t="n">
         <v>1.04</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z37" t="n">
-        <v>3.95</v>
+        <v>4.14</v>
       </c>
       <c r="AA37" t="n">
         <v>1.76</v>
@@ -6335,19 +6335,19 @@
         <v>2.08</v>
       </c>
       <c r="AC37" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG37" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK37" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,64 +6449,64 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1.86</v>
+        <v>1.32</v>
       </c>
       <c r="O38" t="n">
-        <v>3.71</v>
+        <v>4.8</v>
       </c>
       <c r="P38" t="n">
-        <v>4.15</v>
+        <v>7.8</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z38" t="n">
-        <v>4.14</v>
+        <v>4</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.76</v>
+        <v>1.61</v>
       </c>
       <c r="AB38" t="n">
         <v>2.08</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="AG38" t="n">
-        <v>2.1</v>
+        <v>1.78</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AK38" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>2.35</v>
+        <v>2.16</v>
       </c>
       <c r="O40" t="n">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="P40" t="n">
-        <v>3.25</v>
+        <v>3.85</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>2.23</v>
+        <v>2</v>
       </c>
       <c r="O41" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="P41" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="O43" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="P43" t="n">
-        <v>4.4</v>
+        <v>3.25</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="O45" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="P45" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>2.16</v>
+        <v>1.95</v>
       </c>
       <c r="O47" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="P47" t="n">
-        <v>3.85</v>
+        <v>4.4</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>

--- a/jogos_2026-07-11.xlsx
+++ b/jogos_2026-07-11.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,65 +725,65 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.75</v>
+        <v>2.35</v>
       </c>
       <c r="O2" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P2" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R2" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AG2" t="n">
         <v>2.17</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>0</v>
-      </c>
       <c r="AH2" t="inlineStr">
         <is>
           <t>[]</t>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.45</v>
+        <v>2.78</v>
       </c>
       <c r="O3" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="P3" t="n">
-        <v>2.4</v>
+        <v>2.21</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.14</v>
+        <v>2.45</v>
       </c>
       <c r="O4" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="R4" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="T4" t="n">
         <v>3.25</v>
       </c>
-      <c r="P4" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="O5" t="n">
-        <v>5.1</v>
+        <v>4.55</v>
       </c>
       <c r="P5" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="O6" t="n">
-        <v>3.65</v>
+        <v>3.74</v>
       </c>
       <c r="P6" t="n">
-        <v>4</v>
+        <v>4.47</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="O7" t="n">
         <v>3.28</v>
       </c>
       <c r="P7" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>6.07</v>
+        <v>2.74</v>
       </c>
       <c r="O9" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="P9" t="n">
-        <v>1.58</v>
+        <v>2.47</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.61</v>
+        <v>3.29</v>
       </c>
       <c r="R9" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S9" t="n">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="T9" t="n">
-        <v>2.53</v>
+        <v>2.81</v>
       </c>
       <c r="U9" t="n">
-        <v>3.22</v>
+        <v>2.88</v>
       </c>
       <c r="V9" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="W9" t="n">
         <v>1.06</v>
       </c>
       <c r="X9" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.72</v>
+        <v>3.3</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.15</v>
+        <v>1.96</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.61</v>
+        <v>1.85</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.2</v>
+        <v>3.18</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.25</v>
+        <v>1.7</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.11</v>
+        <v>1.4</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.05</v>
+        <v>5.5</v>
       </c>
       <c r="O10" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="P10" t="n">
-        <v>3.35</v>
+        <v>1.53</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.38</v>
+        <v>6.5</v>
       </c>
       <c r="R10" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="S10" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="T10" t="n">
-        <v>2.75</v>
+        <v>2.53</v>
       </c>
       <c r="U10" t="n">
-        <v>3.14</v>
+        <v>3.22</v>
       </c>
       <c r="V10" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W10" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE10" t="n">
         <v>1.06</v>
       </c>
-      <c r="Y10" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.04</v>
-      </c>
       <c r="AF10" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.75</v>
+        <v>1.1</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="O11" t="n">
-        <v>3.32</v>
+        <v>3.1</v>
       </c>
       <c r="P11" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,31 +2474,31 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.74</v>
+        <v>2.23</v>
       </c>
       <c r="O13" t="n">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="P13" t="n">
-        <v>2.47</v>
+        <v>2.97</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="R13" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S13" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="T13" t="n">
-        <v>2.81</v>
+        <v>2.62</v>
       </c>
       <c r="U13" t="n">
-        <v>2.81</v>
+        <v>2.91</v>
       </c>
       <c r="V13" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="W13" t="n">
         <v>1.03</v>
@@ -2507,31 +2507,31 @@
         <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.3</v>
+        <v>3.19</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.88</v>
+        <v>2.06</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.84</v>
+        <v>1.71</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.18</v>
+        <v>3.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.67</v>
+        <v>1.79</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.4</v>
+        <v>1.54</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.23</v>
+        <v>2.05</v>
       </c>
       <c r="O14" t="n">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="P14" t="n">
-        <v>2.97</v>
+        <v>3.35</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.88</v>
+        <v>2.38</v>
       </c>
       <c r="R14" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S14" t="n">
         <v>1.4</v>
       </c>
       <c r="T14" t="n">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="U14" t="n">
-        <v>2.91</v>
+        <v>3.14</v>
       </c>
       <c r="V14" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W14" t="n">
         <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.19</v>
+        <v>3</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AE14" t="n">
         <v>1.04</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.54</v>
+        <v>1.75</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.59</v>
+        <v>3.18</v>
       </c>
       <c r="O17" t="n">
-        <v>4.46</v>
+        <v>3.48</v>
       </c>
       <c r="P17" t="n">
-        <v>5.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.97</v>
+        <v>3.4</v>
       </c>
       <c r="R17" t="n">
-        <v>2.49</v>
+        <v>2.3</v>
       </c>
       <c r="S17" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="T17" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="U17" t="n">
-        <v>2.13</v>
+        <v>2.5</v>
       </c>
       <c r="V17" t="n">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="W17" t="n">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="X17" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y17" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE17" t="n">
         <v>1.1</v>
       </c>
-      <c r="Z17" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AF17" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.4</v>
+        <v>1.33</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>3.18</v>
+        <v>1.59</v>
       </c>
       <c r="O20" t="n">
-        <v>3.48</v>
+        <v>4.46</v>
       </c>
       <c r="P20" t="n">
-        <v>2.25</v>
+        <v>5.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.4</v>
+        <v>1.95</v>
       </c>
       <c r="R20" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="S20" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="T20" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="U20" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="V20" t="n">
-        <v>1.46</v>
+        <v>1.67</v>
       </c>
       <c r="W20" t="n">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="X20" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="Z20" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.73</v>
+        <v>1.51</v>
       </c>
       <c r="AB20" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.4</v>
+        <v>1.69</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.2</v>
+        <v>2.31</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.3</v>
+        <v>1.05</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.35</v>
+        <v>2.4</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.53</v>
+        <v>1.36</v>
       </c>
       <c r="O21" t="n">
-        <v>3.38</v>
+        <v>4.3</v>
       </c>
       <c r="P21" t="n">
-        <v>2.39</v>
+        <v>7.5</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.36</v>
+        <v>2.52</v>
       </c>
       <c r="O22" t="n">
-        <v>4.3</v>
+        <v>3.42</v>
       </c>
       <c r="P22" t="n">
-        <v>7.5</v>
+        <v>2.4</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,80 +4064,80 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.96</v>
+        <v>2.85</v>
       </c>
       <c r="R23" t="n">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="S23" t="n">
-        <v>1.35</v>
+        <v>1.14</v>
       </c>
       <c r="T23" t="n">
-        <v>2.9</v>
+        <v>4.8</v>
       </c>
       <c r="U23" t="n">
-        <v>2.54</v>
+        <v>2.01</v>
       </c>
       <c r="V23" t="n">
-        <v>1.44</v>
+        <v>1.76</v>
       </c>
       <c r="W23" t="n">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="X23" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y23" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ23" t="n">
         <v>1.24</v>
       </c>
-      <c r="Z23" t="n">
-        <v>4.54</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ23" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AK23" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>4.02</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="R24" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="S24" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="T24" t="n">
-        <v>4.8</v>
+        <v>3.1</v>
       </c>
       <c r="U24" t="n">
-        <v>2</v>
+        <v>2.54</v>
       </c>
       <c r="V24" t="n">
-        <v>1.76</v>
+        <v>1.44</v>
       </c>
       <c r="W24" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="X24" t="n">
         <v>1.01</v>
       </c>
       <c r="Y24" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AE24" t="n">
         <v>1.11</v>
       </c>
-      <c r="Z24" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AF24" t="n">
-        <v>1.33</v>
+        <v>1.61</v>
       </c>
       <c r="AG24" t="n">
-        <v>3.1</v>
+        <v>2.18</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4296,7 +4296,7 @@
         <v>1.25</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4382,46 +4382,46 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.81</v>
+        <v>2.62</v>
       </c>
       <c r="O25" t="n">
-        <v>3.54</v>
+        <v>3.25</v>
       </c>
       <c r="P25" t="n">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.38</v>
+        <v>3.3</v>
       </c>
       <c r="R25" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S25" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="T25" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="U25" t="n">
         <v>2.5</v>
       </c>
       <c r="V25" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W25" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X25" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="Z25" t="n">
         <v>3.8</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AB25" t="n">
         <v>2</v>
@@ -4430,10 +4430,10 @@
         <v>2.88</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AF25" t="n">
         <v>1.6</v>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>1.53</v>
+        <v>1.3</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4541,19 +4541,19 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.45</v>
+        <v>1.34</v>
       </c>
       <c r="O26" t="n">
-        <v>4.64</v>
+        <v>4.8</v>
       </c>
       <c r="P26" t="n">
-        <v>6.95</v>
+        <v>7</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="R26" t="n">
-        <v>2.47</v>
+        <v>2.68</v>
       </c>
       <c r="S26" t="n">
         <v>1.28</v>
@@ -4562,34 +4562,34 @@
         <v>3.25</v>
       </c>
       <c r="U26" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="V26" t="n">
         <v>1.51</v>
       </c>
       <c r="W26" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X26" t="n">
         <v>1.03</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="Z26" t="n">
-        <v>4.33</v>
+        <v>5.34</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.63</v>
+        <v>2.66</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AE26" t="n">
         <v>1.16</v>
@@ -4598,7 +4598,7 @@
         <v>1.85</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="AK26" t="n">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,64 +4700,64 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>2.13</v>
+        <v>1.95</v>
       </c>
       <c r="O27" t="n">
-        <v>3.21</v>
+        <v>3.4</v>
       </c>
       <c r="P27" t="n">
-        <v>3.52</v>
+        <v>3.51</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,80 +4859,80 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>2.19</v>
+        <v>2.61</v>
       </c>
       <c r="O28" t="n">
-        <v>3.56</v>
+        <v>2.86</v>
       </c>
       <c r="P28" t="n">
-        <v>3.03</v>
+        <v>3.01</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.45</v>
+        <v>3.1</v>
       </c>
       <c r="R28" t="n">
-        <v>2.27</v>
+        <v>1.97</v>
       </c>
       <c r="S28" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="U28" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="V28" t="n">
         <v>1.31</v>
       </c>
-      <c r="T28" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U28" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.45</v>
-      </c>
       <c r="W28" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X28" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y28" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ28" t="n">
         <v>1.24</v>
       </c>
-      <c r="Z28" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ28" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AK28" t="n">
-        <v>1.8</v>
+        <v>1.52</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,64 +5018,64 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>2.61</v>
+        <v>2.13</v>
       </c>
       <c r="O29" t="n">
-        <v>2.86</v>
+        <v>3.21</v>
       </c>
       <c r="P29" t="n">
-        <v>3.01</v>
+        <v>3.52</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="AJ29" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -5177,64 +5177,64 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>3.5</v>
+        <v>2.94</v>
       </c>
       <c r="O30" t="n">
-        <v>3.87</v>
+        <v>3.65</v>
       </c>
       <c r="P30" t="n">
-        <v>1.99</v>
+        <v>2.14</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R30" t="n">
         <v>2.45</v>
       </c>
       <c r="S30" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="T30" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="U30" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="V30" t="n">
         <v>1.6</v>
       </c>
       <c r="W30" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X30" t="n">
         <v>1.03</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="Z30" t="n">
         <v>5</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AB30" t="n">
         <v>2.4</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="AD30" t="n">
         <v>1.57</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AF30" t="n">
         <v>1.44</v>
       </c>
       <c r="AG30" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5250,7 +5250,7 @@
         <v>1.7</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,64 +5336,64 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1.89</v>
+        <v>2.75</v>
       </c>
       <c r="O31" t="n">
-        <v>2.95</v>
+        <v>3.01</v>
       </c>
       <c r="P31" t="n">
-        <v>4.1</v>
+        <v>2.7</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,80 +5495,80 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>2.75</v>
+        <v>1.74</v>
       </c>
       <c r="O32" t="n">
-        <v>3.01</v>
+        <v>3.78</v>
       </c>
       <c r="P32" t="n">
-        <v>2.7</v>
+        <v>3.84</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.3</v>
+        <v>2.26</v>
       </c>
       <c r="R32" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S32" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ32" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AK32" t="n">
         <v>1.9</v>
-      </c>
-      <c r="S32" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="U32" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X32" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ32" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>1.41</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,64 +5654,64 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1.74</v>
+        <v>1.89</v>
       </c>
       <c r="O33" t="n">
-        <v>3.78</v>
+        <v>2.95</v>
       </c>
       <c r="P33" t="n">
-        <v>3.84</v>
+        <v>4.1</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,64 +6131,64 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1.64</v>
+        <v>1.32</v>
       </c>
       <c r="O36" t="n">
-        <v>3.85</v>
+        <v>4.8</v>
       </c>
       <c r="P36" t="n">
-        <v>4.15</v>
+        <v>7.8</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z36" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.76</v>
+        <v>1.61</v>
       </c>
       <c r="AB36" t="n">
         <v>2.08</v>
       </c>
       <c r="AC36" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AE36" t="n">
         <v>1.15</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AG36" t="n">
-        <v>2.05</v>
+        <v>1.78</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AK36" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,64 +6449,64 @@
         </is>
       </c>
       <c r="N38" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="O38" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="P38" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="R38" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S38" t="n">
         <v>1.32</v>
       </c>
-      <c r="O38" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="P38" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
-      <c r="R38" t="n">
-        <v>0</v>
-      </c>
-      <c r="S38" t="n">
-        <v>0</v>
-      </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z38" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.61</v>
+        <v>1.76</v>
       </c>
       <c r="AB38" t="n">
         <v>2.08</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AE38" t="n">
         <v>1.15</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.78</v>
+        <v>2.05</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AK38" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>2.16</v>
+        <v>1.95</v>
       </c>
       <c r="O40" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="P40" t="n">
-        <v>3.85</v>
+        <v>4.4</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,64 +6926,64 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="O41" t="n">
-        <v>3.05</v>
+        <v>2.93</v>
       </c>
       <c r="P41" t="n">
-        <v>4.1</v>
+        <v>3.99</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>6.23</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -6996,10 +6996,10 @@
         </is>
       </c>
       <c r="AJ41" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK41" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL41" t="n">
         <v>0</v>
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="O43" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="P43" t="n">
-        <v>3.25</v>
+        <v>4.1</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>2.04</v>
+        <v>2.35</v>
       </c>
       <c r="O45" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="P45" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,64 +7721,64 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>6.23</v>
+        <v>0</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7791,10 +7791,10 @@
         </is>
       </c>
       <c r="AJ46" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK46" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AL46" t="n">
         <v>0</v>
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>1.95</v>
+        <v>2.16</v>
       </c>
       <c r="O47" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="P47" t="n">
-        <v>4.4</v>
+        <v>3.85</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>

--- a/jogos_2026-07-11.xlsx
+++ b/jogos_2026-07-11.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,31 +725,31 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="O2" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="P2" t="n">
-        <v>2.57</v>
+        <v>2.4</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.8</v>
+        <v>3.12</v>
       </c>
       <c r="R2" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="S2" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T2" t="n">
-        <v>2.97</v>
+        <v>3.25</v>
       </c>
       <c r="U2" t="n">
-        <v>2.63</v>
+        <v>2.44</v>
       </c>
       <c r="V2" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W2" t="n">
         <v>1.07</v>
@@ -758,31 +758,31 @@
         <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.8</v>
+        <v>1.63</v>
       </c>
       <c r="AB2" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.59</v>
+        <v>1.54</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.17</v>
+        <v>2.28</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.78</v>
+        <v>2.35</v>
       </c>
       <c r="O3" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="P3" t="n">
-        <v>2.21</v>
+        <v>2.57</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="R3" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="S3" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T3" t="n">
-        <v>3.14</v>
+        <v>2.97</v>
       </c>
       <c r="U3" t="n">
-        <v>2.28</v>
+        <v>2.63</v>
       </c>
       <c r="V3" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W3" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X3" t="n">
         <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.98</v>
+        <v>3.7</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.61</v>
+        <v>1.8</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.52</v>
+        <v>2.7</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.32</v>
+        <v>2.17</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.35</v>
+        <v>1.52</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.45</v>
+        <v>2.78</v>
       </c>
       <c r="O4" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="P4" t="n">
-        <v>2.4</v>
+        <v>2.21</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.12</v>
+        <v>3.25</v>
       </c>
       <c r="R4" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="S4" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T4" t="n">
-        <v>3.25</v>
+        <v>3.14</v>
       </c>
       <c r="U4" t="n">
-        <v>2.44</v>
+        <v>2.28</v>
       </c>
       <c r="V4" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="W4" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X4" t="n">
         <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.95</v>
+        <v>3.98</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="AD4" t="n">
         <v>1.41</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>1.22</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>APIA Leichhardt Tigers</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sydney II</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.37</v>
+        <v>1.64</v>
       </c>
       <c r="O5" t="n">
-        <v>4.55</v>
+        <v>3.74</v>
       </c>
       <c r="P5" t="n">
-        <v>6.5</v>
+        <v>4.47</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.66</v>
+        <v>2.2</v>
       </c>
       <c r="R5" t="n">
-        <v>2.95</v>
+        <v>2.23</v>
       </c>
       <c r="S5" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="T5" t="n">
-        <v>3.68</v>
+        <v>3.25</v>
       </c>
       <c r="U5" t="n">
-        <v>1.8</v>
+        <v>2.44</v>
       </c>
       <c r="V5" t="n">
-        <v>1.67</v>
+        <v>1.45</v>
       </c>
       <c r="W5" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="Z5" t="n">
-        <v>6</v>
+        <v>3.92</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.3</v>
+        <v>1.72</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.5</v>
+        <v>2.07</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.79</v>
+        <v>2.55</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.85</v>
+        <v>1.38</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.36</v>
+        <v>1.11</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.85</v>
+        <v>2.03</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>APIA Leichhardt Tigers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Sydney II</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,65 +1361,65 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.64</v>
+        <v>1.37</v>
       </c>
       <c r="O6" t="n">
-        <v>3.74</v>
+        <v>4.55</v>
       </c>
       <c r="P6" t="n">
-        <v>4.47</v>
+        <v>6.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.2</v>
+        <v>1.66</v>
       </c>
       <c r="R6" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AG6" t="n">
         <v>2.23</v>
       </c>
-      <c r="S6" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="T6" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>2.07</v>
-      </c>
       <c r="AH6" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.03</v>
+        <v>2.85</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.74</v>
+        <v>2.23</v>
       </c>
       <c r="O9" t="n">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="P9" t="n">
-        <v>2.47</v>
+        <v>2.97</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.29</v>
+        <v>2.88</v>
       </c>
       <c r="R9" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S9" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="T9" t="n">
-        <v>2.81</v>
+        <v>2.62</v>
       </c>
       <c r="U9" t="n">
-        <v>2.88</v>
+        <v>2.91</v>
       </c>
       <c r="V9" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W9" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X9" t="n">
         <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.3</v>
+        <v>3.19</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.96</v>
+        <v>2.06</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.18</v>
+        <v>3.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="AG9" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.4</v>
+        <v>1.54</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,80 +1997,80 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>5.5</v>
+        <v>2.05</v>
       </c>
       <c r="O10" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="P10" t="n">
-        <v>1.53</v>
+        <v>3.35</v>
       </c>
       <c r="Q10" t="n">
-        <v>6.5</v>
+        <v>2.38</v>
       </c>
       <c r="R10" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="S10" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="T10" t="n">
-        <v>2.53</v>
+        <v>2.75</v>
       </c>
       <c r="U10" t="n">
-        <v>3.22</v>
+        <v>3.14</v>
       </c>
       <c r="V10" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W10" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X10" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.72</v>
+        <v>3</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.23</v>
+        <v>2.05</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.2</v>
+        <v>3.45</v>
       </c>
       <c r="AD10" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ10" t="n">
         <v>1.22</v>
       </c>
-      <c r="AE10" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.23</v>
-      </c>
       <c r="AK10" t="n">
-        <v>1.1</v>
+        <v>1.75</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.05</v>
+        <v>5.5</v>
       </c>
       <c r="O11" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="P11" t="n">
-        <v>3.6</v>
+        <v>1.53</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,80 +2474,80 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.23</v>
+        <v>6.2</v>
       </c>
       <c r="O13" t="n">
-        <v>3.18</v>
+        <v>4.55</v>
       </c>
       <c r="P13" t="n">
-        <v>2.97</v>
+        <v>1.34</v>
       </c>
       <c r="Q13" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="R13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ13" t="n">
         <v>2.88</v>
       </c>
-      <c r="R13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AK13" t="n">
-        <v>1.54</v>
+        <v>1.06</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,80 +2633,80 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.05</v>
+        <v>2.74</v>
       </c>
       <c r="O14" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P14" t="n">
-        <v>3.35</v>
+        <v>2.47</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.38</v>
+        <v>3.29</v>
       </c>
       <c r="R14" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG14" t="n">
         <v>2</v>
       </c>
-      <c r="S14" t="n">
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AK14" t="n">
         <v>1.4</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U14" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1.75</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>6.2</v>
+        <v>2.05</v>
       </c>
       <c r="O15" t="n">
-        <v>4.55</v>
+        <v>3.1</v>
       </c>
       <c r="P15" t="n">
-        <v>1.34</v>
+        <v>3.6</v>
       </c>
       <c r="Q15" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.57</v>
+        <v>2.15</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.17</v>
+        <v>1.66</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>3.18</v>
+        <v>2.15</v>
       </c>
       <c r="O17" t="n">
-        <v>3.48</v>
+        <v>3.2</v>
       </c>
       <c r="P17" t="n">
-        <v>2.25</v>
+        <v>3.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,64 +4382,64 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.62</v>
+        <v>1.34</v>
       </c>
       <c r="O25" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P25" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="R25" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="S25" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="T25" t="n">
         <v>3.25</v>
       </c>
-      <c r="P25" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="R25" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="S25" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="T25" t="n">
-        <v>3</v>
-      </c>
       <c r="U25" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="V25" t="n">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="W25" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X25" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.8</v>
+        <v>5.34</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AB25" t="n">
-        <v>2</v>
+        <v>2.21</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.88</v>
+        <v>2.66</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>1.3</v>
+        <v>1.06</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.4</v>
+        <v>3.12</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,64 +4541,64 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.34</v>
+        <v>2.62</v>
       </c>
       <c r="O26" t="n">
-        <v>4.8</v>
+        <v>3.25</v>
       </c>
       <c r="P26" t="n">
-        <v>7</v>
+        <v>2.47</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.76</v>
+        <v>3.3</v>
       </c>
       <c r="R26" t="n">
-        <v>2.68</v>
+        <v>2.2</v>
       </c>
       <c r="S26" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="T26" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="U26" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="V26" t="n">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="W26" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X26" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z26" t="n">
-        <v>5.34</v>
+        <v>3.8</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.21</v>
+        <v>2</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.66</v>
+        <v>2.88</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>1.06</v>
+        <v>1.3</v>
       </c>
       <c r="AK26" t="n">
-        <v>3.12</v>
+        <v>1.4</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,64 +4700,64 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.95</v>
+        <v>2.13</v>
       </c>
       <c r="O27" t="n">
-        <v>3.4</v>
+        <v>3.21</v>
       </c>
       <c r="P27" t="n">
-        <v>3.51</v>
+        <v>3.52</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,64 +5018,64 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>2.13</v>
+        <v>1.95</v>
       </c>
       <c r="O29" t="n">
-        <v>3.21</v>
+        <v>3.4</v>
       </c>
       <c r="P29" t="n">
-        <v>3.52</v>
+        <v>3.51</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,64 +5177,64 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>2.94</v>
+        <v>1.89</v>
       </c>
       <c r="O30" t="n">
-        <v>3.65</v>
+        <v>2.95</v>
       </c>
       <c r="P30" t="n">
-        <v>2.14</v>
+        <v>4.1</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,64 +5495,64 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>1.74</v>
+        <v>2.94</v>
       </c>
       <c r="O32" t="n">
-        <v>3.78</v>
+        <v>3.65</v>
       </c>
       <c r="P32" t="n">
-        <v>3.84</v>
+        <v>2.14</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.26</v>
+        <v>3.4</v>
       </c>
       <c r="R32" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="S32" t="n">
         <v>1.22</v>
       </c>
       <c r="T32" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="U32" t="n">
         <v>2.15</v>
       </c>
       <c r="V32" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="W32" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X32" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="Z32" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.02</v>
+        <v>2.21</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AF32" t="n">
         <v>1.44</v>
       </c>
       <c r="AG32" t="n">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>1.18</v>
+        <v>1.7</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.9</v>
+        <v>1.34</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,64 +5654,64 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1.89</v>
+        <v>1.74</v>
       </c>
       <c r="O33" t="n">
-        <v>2.95</v>
+        <v>3.78</v>
       </c>
       <c r="P33" t="n">
-        <v>4.1</v>
+        <v>3.84</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,64 +6131,64 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1.32</v>
+        <v>1.86</v>
       </c>
       <c r="O36" t="n">
-        <v>4.8</v>
+        <v>3.71</v>
       </c>
       <c r="P36" t="n">
-        <v>7.8</v>
+        <v>4.15</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z36" t="n">
-        <v>4</v>
+        <v>4.14</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.61</v>
+        <v>1.76</v>
       </c>
       <c r="AB36" t="n">
         <v>2.08</v>
       </c>
       <c r="AC36" t="n">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.78</v>
+        <v>2.1</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AK36" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,43 +6290,43 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.86</v>
+        <v>1.64</v>
       </c>
       <c r="O37" t="n">
-        <v>3.71</v>
+        <v>3.85</v>
       </c>
       <c r="P37" t="n">
         <v>4.15</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.25</v>
+        <v>2.09</v>
       </c>
       <c r="R37" t="n">
         <v>2.3</v>
       </c>
       <c r="S37" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T37" t="n">
-        <v>3.04</v>
+        <v>3.3</v>
       </c>
       <c r="U37" t="n">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="V37" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="W37" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X37" t="n">
         <v>1.04</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z37" t="n">
-        <v>4.14</v>
+        <v>3.95</v>
       </c>
       <c r="AA37" t="n">
         <v>1.76</v>
@@ -6335,19 +6335,19 @@
         <v>2.08</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG37" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK37" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,64 +6449,64 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1.64</v>
+        <v>1.32</v>
       </c>
       <c r="O38" t="n">
-        <v>3.85</v>
+        <v>4.8</v>
       </c>
       <c r="P38" t="n">
-        <v>4.15</v>
+        <v>7.8</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z38" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.76</v>
+        <v>1.61</v>
       </c>
       <c r="AB38" t="n">
         <v>2.08</v>
       </c>
       <c r="AC38" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AE38" t="n">
         <v>1.15</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AG38" t="n">
-        <v>2.05</v>
+        <v>1.78</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AK38" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,64 +6767,64 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="O40" t="n">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="P40" t="n">
-        <v>4.4</v>
+        <v>3.99</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="AJ40" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK40" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,64 +6926,64 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>1.97</v>
+        <v>2.35</v>
       </c>
       <c r="O41" t="n">
-        <v>2.93</v>
+        <v>2.9</v>
       </c>
       <c r="P41" t="n">
-        <v>3.99</v>
+        <v>3.25</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>6.23</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG41" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -6996,10 +6996,10 @@
         </is>
       </c>
       <c r="AJ41" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK41" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AL41" t="n">
         <v>0</v>
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="O43" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="P43" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="O44" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="P44" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="O45" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="P45" t="n">
-        <v>3.25</v>
+        <v>4.1</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>

--- a/jogos_2026-07-11.xlsx
+++ b/jogos_2026-07-11.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.35</v>
+        <v>2.78</v>
       </c>
       <c r="O3" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="P3" t="n">
-        <v>2.57</v>
+        <v>2.21</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="R3" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="S3" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T3" t="n">
-        <v>2.97</v>
+        <v>3.14</v>
       </c>
       <c r="U3" t="n">
-        <v>2.63</v>
+        <v>2.28</v>
       </c>
       <c r="V3" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W3" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X3" t="n">
         <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.7</v>
+        <v>3.98</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.8</v>
+        <v>1.61</v>
       </c>
       <c r="AB3" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.7</v>
+        <v>2.52</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.17</v>
+        <v>2.32</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.52</v>
+        <v>1.35</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.78</v>
+        <v>2.35</v>
       </c>
       <c r="O4" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="P4" t="n">
-        <v>2.21</v>
+        <v>2.57</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="R4" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="S4" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T4" t="n">
-        <v>3.14</v>
+        <v>2.97</v>
       </c>
       <c r="U4" t="n">
-        <v>2.28</v>
+        <v>2.63</v>
       </c>
       <c r="V4" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W4" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X4" t="n">
         <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.98</v>
+        <v>3.7</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.61</v>
+        <v>1.8</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.52</v>
+        <v>2.7</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.32</v>
+        <v>2.17</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.35</v>
+        <v>1.52</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>APIA Leichhardt Tigers</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Sydney II</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,65 +1202,65 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.64</v>
+        <v>1.37</v>
       </c>
       <c r="O5" t="n">
-        <v>3.74</v>
+        <v>4.55</v>
       </c>
       <c r="P5" t="n">
-        <v>4.47</v>
+        <v>6.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.2</v>
+        <v>1.66</v>
       </c>
       <c r="R5" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AG5" t="n">
         <v>2.23</v>
       </c>
-      <c r="S5" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="T5" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>2.07</v>
-      </c>
       <c r="AH5" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.03</v>
+        <v>2.85</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>APIA Leichhardt Tigers</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sydney II</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.37</v>
+        <v>1.64</v>
       </c>
       <c r="O6" t="n">
-        <v>4.55</v>
+        <v>3.74</v>
       </c>
       <c r="P6" t="n">
-        <v>6.5</v>
+        <v>4.47</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.66</v>
+        <v>2.2</v>
       </c>
       <c r="R6" t="n">
-        <v>2.95</v>
+        <v>2.23</v>
       </c>
       <c r="S6" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="T6" t="n">
-        <v>3.68</v>
+        <v>3.25</v>
       </c>
       <c r="U6" t="n">
-        <v>1.8</v>
+        <v>2.44</v>
       </c>
       <c r="V6" t="n">
-        <v>1.67</v>
+        <v>1.45</v>
       </c>
       <c r="W6" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="Z6" t="n">
-        <v>6</v>
+        <v>3.92</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.3</v>
+        <v>1.72</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.5</v>
+        <v>2.07</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.79</v>
+        <v>2.55</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.85</v>
+        <v>1.38</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.36</v>
+        <v>1.11</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.85</v>
+        <v>2.03</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.23</v>
+        <v>1.87</v>
       </c>
       <c r="O9" t="n">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="P9" t="n">
-        <v>2.97</v>
+        <v>3.6</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.88</v>
+        <v>2.52</v>
       </c>
       <c r="R9" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S9" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T9" t="n">
         <v>2.62</v>
       </c>
       <c r="U9" t="n">
-        <v>2.91</v>
+        <v>2.8</v>
       </c>
       <c r="V9" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="W9" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.19</v>
+        <v>3.14</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.06</v>
+        <v>1.92</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="AC9" t="n">
         <v>3.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF9" t="n">
         <v>1.79</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>1.3</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.54</v>
+        <v>1.83</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2000,61 +2000,61 @@
         <v>2.05</v>
       </c>
       <c r="O10" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P10" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,80 +2156,80 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>5.5</v>
+        <v>2.05</v>
       </c>
       <c r="O11" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="P11" t="n">
-        <v>1.53</v>
+        <v>3.35</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.5</v>
+        <v>2.38</v>
       </c>
       <c r="R11" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="S11" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="T11" t="n">
-        <v>2.53</v>
+        <v>2.75</v>
       </c>
       <c r="U11" t="n">
-        <v>3.22</v>
+        <v>3.14</v>
       </c>
       <c r="V11" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W11" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X11" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.72</v>
+        <v>3</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.23</v>
+        <v>2.05</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.2</v>
+        <v>3.45</v>
       </c>
       <c r="AD11" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ11" t="n">
         <v>1.22</v>
       </c>
-      <c r="AE11" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.23</v>
-      </c>
       <c r="AK11" t="n">
-        <v>1.1</v>
+        <v>1.75</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.87</v>
+        <v>2.23</v>
       </c>
       <c r="O12" t="n">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="P12" t="n">
-        <v>3.6</v>
+        <v>2.97</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.52</v>
+        <v>2.88</v>
       </c>
       <c r="R12" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S12" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T12" t="n">
         <v>2.62</v>
       </c>
       <c r="U12" t="n">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
       <c r="V12" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="W12" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.14</v>
+        <v>3.19</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.92</v>
+        <v>2.06</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="AC12" t="n">
         <v>3.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AF12" t="n">
         <v>1.79</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         <v>1.3</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.83</v>
+        <v>1.54</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,80 +2474,80 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="O13" t="n">
-        <v>4.55</v>
+        <v>3.5</v>
       </c>
       <c r="P13" t="n">
-        <v>1.34</v>
+        <v>1.53</v>
       </c>
       <c r="Q13" t="n">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="R13" t="n">
-        <v>2.4</v>
+        <v>2.07</v>
       </c>
       <c r="S13" t="n">
-        <v>1.32</v>
+        <v>1.48</v>
       </c>
       <c r="T13" t="n">
-        <v>3.2</v>
+        <v>2.53</v>
       </c>
       <c r="U13" t="n">
-        <v>2.44</v>
+        <v>3.22</v>
       </c>
       <c r="V13" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="W13" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="X13" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.16</v>
+        <v>1.36</v>
       </c>
       <c r="Z13" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC13" t="n">
         <v>4.2</v>
       </c>
-      <c r="AA13" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AD13" t="n">
-        <v>1.46</v>
+        <v>1.22</v>
       </c>
       <c r="AE13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AK13" t="n">
         <v>1.1</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ13" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1.06</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,80 +2633,80 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.74</v>
+        <v>6.2</v>
       </c>
       <c r="O14" t="n">
-        <v>3.3</v>
+        <v>4.55</v>
       </c>
       <c r="P14" t="n">
-        <v>2.47</v>
+        <v>1.34</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.29</v>
+        <v>6.25</v>
       </c>
       <c r="R14" t="n">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="S14" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="T14" t="n">
-        <v>2.81</v>
+        <v>3.2</v>
       </c>
       <c r="U14" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ14" t="n">
         <v>2.88</v>
       </c>
-      <c r="V14" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W14" t="n">
+      <c r="AK14" t="n">
         <v>1.06</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1.4</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.05</v>
+        <v>2.74</v>
       </c>
       <c r="O15" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="P15" t="n">
-        <v>3.6</v>
+        <v>2.47</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.15</v>
+        <v>1.96</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.66</v>
+        <v>1.85</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.52</v>
+        <v>2.15</v>
       </c>
       <c r="O18" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="P18" t="n">
-        <v>5</v>
+        <v>3.1</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.36</v>
+        <v>2.52</v>
       </c>
       <c r="O21" t="n">
-        <v>4.3</v>
+        <v>3.42</v>
       </c>
       <c r="P21" t="n">
-        <v>7.5</v>
+        <v>2.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.52</v>
+        <v>1.36</v>
       </c>
       <c r="O22" t="n">
-        <v>3.42</v>
+        <v>4.3</v>
       </c>
       <c r="P22" t="n">
-        <v>2.4</v>
+        <v>7.5</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,64 +4382,64 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1.34</v>
+        <v>2.62</v>
       </c>
       <c r="O25" t="n">
-        <v>4.8</v>
+        <v>3.25</v>
       </c>
       <c r="P25" t="n">
-        <v>7</v>
+        <v>2.47</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.76</v>
+        <v>3.3</v>
       </c>
       <c r="R25" t="n">
-        <v>2.68</v>
+        <v>2.2</v>
       </c>
       <c r="S25" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="T25" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="U25" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="V25" t="n">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="W25" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X25" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z25" t="n">
-        <v>5.34</v>
+        <v>3.8</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.21</v>
+        <v>2</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.66</v>
+        <v>2.88</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>1.06</v>
+        <v>1.3</v>
       </c>
       <c r="AK25" t="n">
-        <v>3.12</v>
+        <v>1.4</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,64 +4541,64 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>2.62</v>
+        <v>1.34</v>
       </c>
       <c r="O26" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P26" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="R26" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="S26" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="T26" t="n">
         <v>3.25</v>
       </c>
-      <c r="P26" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="R26" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="S26" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="T26" t="n">
-        <v>3</v>
-      </c>
       <c r="U26" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="V26" t="n">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="W26" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X26" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.8</v>
+        <v>5.34</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AB26" t="n">
-        <v>2</v>
+        <v>2.21</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.88</v>
+        <v>2.66</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>1.3</v>
+        <v>1.06</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.4</v>
+        <v>3.12</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,64 +4700,64 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>2.13</v>
+        <v>2.61</v>
       </c>
       <c r="O27" t="n">
-        <v>3.21</v>
+        <v>2.86</v>
       </c>
       <c r="P27" t="n">
-        <v>3.52</v>
+        <v>3.01</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,64 +4859,64 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>2.61</v>
+        <v>1.95</v>
       </c>
       <c r="O28" t="n">
-        <v>2.86</v>
+        <v>3.4</v>
       </c>
       <c r="P28" t="n">
-        <v>3.01</v>
+        <v>3.51</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.1</v>
+        <v>2.42</v>
       </c>
       <c r="R28" t="n">
-        <v>1.97</v>
+        <v>2.2</v>
       </c>
       <c r="S28" t="n">
-        <v>1.45</v>
+        <v>1.35</v>
       </c>
       <c r="T28" t="n">
-        <v>2.55</v>
+        <v>2.87</v>
       </c>
       <c r="U28" t="n">
-        <v>3.1</v>
+        <v>2.63</v>
       </c>
       <c r="V28" t="n">
-        <v>1.31</v>
+        <v>1.47</v>
       </c>
       <c r="W28" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X28" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.75</v>
+        <v>3.95</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.24</v>
+        <v>1.73</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.9</v>
+        <v>2.8</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.94</v>
+        <v>1.6</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.79</v>
+        <v>2.15</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="AJ28" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.52</v>
+        <v>1.82</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,64 +5018,64 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>1.95</v>
+        <v>2.13</v>
       </c>
       <c r="O29" t="n">
-        <v>3.4</v>
+        <v>3.21</v>
       </c>
       <c r="P29" t="n">
-        <v>3.51</v>
+        <v>3.52</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="AJ29" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,80 +5336,80 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>2.75</v>
+        <v>1.74</v>
       </c>
       <c r="O31" t="n">
-        <v>3.01</v>
+        <v>3.78</v>
       </c>
       <c r="P31" t="n">
-        <v>2.7</v>
+        <v>3.84</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.3</v>
+        <v>2.26</v>
       </c>
       <c r="R31" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S31" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ31" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AK31" t="n">
         <v>1.9</v>
-      </c>
-      <c r="S31" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="U31" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X31" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ31" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>1.41</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,64 +5654,64 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1.74</v>
+        <v>2.75</v>
       </c>
       <c r="O33" t="n">
-        <v>3.78</v>
+        <v>3.01</v>
       </c>
       <c r="P33" t="n">
-        <v>3.84</v>
+        <v>2.7</v>
       </c>
       <c r="Q33" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="S33" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="U33" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X33" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AA33" t="n">
         <v>2.26</v>
       </c>
-      <c r="R33" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S33" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="T33" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U33" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X33" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AB33" t="n">
-        <v>2.63</v>
+        <v>1.57</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.02</v>
+        <v>4</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.65</v>
+        <v>1.17</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.27</v>
+        <v>1.03</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.44</v>
+        <v>1.82</v>
       </c>
       <c r="AG33" t="n">
-        <v>2.63</v>
+        <v>1.78</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.9</v>
+        <v>1.41</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -6608,58 +6608,58 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>2.55</v>
+        <v>2.86</v>
       </c>
       <c r="O39" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="P39" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="R39" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="S39" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="T39" t="n">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="U39" t="n">
-        <v>3.15</v>
+        <v>3.18</v>
       </c>
       <c r="V39" t="n">
         <v>1.28</v>
       </c>
       <c r="W39" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X39" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z39" t="n">
         <v>2.7</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AC39" t="n">
         <v>4.2</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF39" t="n">
         <v>1.85</v>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="AJ39" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK39" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,64 +6767,64 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="O40" t="n">
-        <v>2.93</v>
+        <v>3</v>
       </c>
       <c r="P40" t="n">
-        <v>3.99</v>
+        <v>4.4</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="AJ40" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>2.23</v>
+        <v>2.16</v>
       </c>
       <c r="O42" t="n">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="P42" t="n">
-        <v>3.3</v>
+        <v>3.85</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>2.16</v>
+        <v>2</v>
       </c>
       <c r="O44" t="n">
-        <v>2.85</v>
+        <v>3.05</v>
       </c>
       <c r="P44" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,64 +7562,64 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="O45" t="n">
-        <v>3.05</v>
+        <v>2.93</v>
       </c>
       <c r="P45" t="n">
-        <v>4.1</v>
+        <v>3.99</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7632,10 +7632,10 @@
         </is>
       </c>
       <c r="AJ45" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK45" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL45" t="n">
         <v>0</v>
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>1.95</v>
+        <v>2.23</v>
       </c>
       <c r="O46" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P46" t="n">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="O49" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P49" t="n">
-        <v>2.12</v>
+        <v>1.8</v>
       </c>
       <c r="Q49" t="n">
         <v>4.66</v>
@@ -8225,37 +8225,37 @@
         <v>1.36</v>
       </c>
       <c r="W49" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X49" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Z49" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="AA49" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB49" t="n">
         <v>1.9</v>
       </c>
-      <c r="AB49" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AC49" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF49" t="n">
         <v>1.75</v>
       </c>
       <c r="AG49" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8268,10 +8268,10 @@
         </is>
       </c>
       <c r="AJ49" t="n">
-        <v>1.83</v>
+        <v>1.27</v>
       </c>
       <c r="AK49" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AL49" t="n">
         <v>0</v>
@@ -8516,10 +8516,10 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="O51" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="P51" t="n">
         <v>3.55</v>

--- a/jogos_2026-07-11.xlsx
+++ b/jogos_2026-07-11.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,31 +725,31 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="O2" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="P2" t="n">
-        <v>2.4</v>
+        <v>2.57</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.12</v>
+        <v>2.8</v>
       </c>
       <c r="R2" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="S2" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T2" t="n">
-        <v>3.25</v>
+        <v>2.97</v>
       </c>
       <c r="U2" t="n">
-        <v>2.44</v>
+        <v>2.63</v>
       </c>
       <c r="V2" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W2" t="n">
         <v>1.07</v>
@@ -758,31 +758,31 @@
         <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.63</v>
+        <v>1.8</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.28</v>
+        <v>2.17</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.78</v>
+        <v>2.45</v>
       </c>
       <c r="O3" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="P3" t="n">
-        <v>2.21</v>
+        <v>2.4</v>
       </c>
       <c r="Q3" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="T3" t="n">
         <v>3.25</v>
       </c>
-      <c r="R3" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="T3" t="n">
-        <v>3.14</v>
-      </c>
       <c r="U3" t="n">
-        <v>2.28</v>
+        <v>2.44</v>
       </c>
       <c r="V3" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="W3" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X3" t="n">
         <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.98</v>
+        <v>3.95</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.52</v>
+        <v>2.55</v>
       </c>
       <c r="AD3" t="n">
         <v>1.41</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>1.22</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.35</v>
+        <v>2.78</v>
       </c>
       <c r="O4" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="P4" t="n">
-        <v>2.57</v>
+        <v>2.21</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="R4" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="S4" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T4" t="n">
-        <v>2.97</v>
+        <v>3.14</v>
       </c>
       <c r="U4" t="n">
-        <v>2.63</v>
+        <v>2.28</v>
       </c>
       <c r="V4" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W4" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X4" t="n">
         <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.7</v>
+        <v>3.98</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.8</v>
+        <v>1.61</v>
       </c>
       <c r="AB4" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.7</v>
+        <v>2.52</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.17</v>
+        <v>2.32</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.52</v>
+        <v>1.35</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>APIA Leichhardt Tigers</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sydney II</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.37</v>
+        <v>1.64</v>
       </c>
       <c r="O5" t="n">
-        <v>4.55</v>
+        <v>3.74</v>
       </c>
       <c r="P5" t="n">
-        <v>6.5</v>
+        <v>4.47</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.66</v>
+        <v>2.2</v>
       </c>
       <c r="R5" t="n">
-        <v>2.95</v>
+        <v>2.23</v>
       </c>
       <c r="S5" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="T5" t="n">
-        <v>3.68</v>
+        <v>3.25</v>
       </c>
       <c r="U5" t="n">
-        <v>1.8</v>
+        <v>2.44</v>
       </c>
       <c r="V5" t="n">
-        <v>1.67</v>
+        <v>1.45</v>
       </c>
       <c r="W5" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="Z5" t="n">
-        <v>6</v>
+        <v>3.92</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.3</v>
+        <v>1.72</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.5</v>
+        <v>2.07</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.79</v>
+        <v>2.55</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.85</v>
+        <v>1.38</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.36</v>
+        <v>1.11</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.85</v>
+        <v>2.03</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>APIA Leichhardt Tigers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Sydney II</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,65 +1361,65 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.64</v>
+        <v>1.37</v>
       </c>
       <c r="O6" t="n">
-        <v>3.74</v>
+        <v>4.55</v>
       </c>
       <c r="P6" t="n">
-        <v>4.47</v>
+        <v>6.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.2</v>
+        <v>1.66</v>
       </c>
       <c r="R6" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AG6" t="n">
         <v>2.23</v>
       </c>
-      <c r="S6" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="T6" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>2.07</v>
-      </c>
       <c r="AH6" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.03</v>
+        <v>2.85</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.87</v>
+        <v>2.05</v>
       </c>
       <c r="O9" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P9" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.52</v>
+        <v>2.38</v>
       </c>
       <c r="R9" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="S9" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T9" t="n">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="U9" t="n">
-        <v>2.8</v>
+        <v>3.14</v>
       </c>
       <c r="V9" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="W9" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.92</v>
+        <v>2.05</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="O10" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="P10" t="n">
         <v>3.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.15</v>
+        <v>1.92</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.66</v>
+        <v>1.76</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.05</v>
+        <v>5.5</v>
       </c>
       <c r="O11" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="P11" t="n">
-        <v>3.35</v>
+        <v>1.53</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.38</v>
+        <v>6.5</v>
       </c>
       <c r="R11" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="S11" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="T11" t="n">
-        <v>2.75</v>
+        <v>2.53</v>
       </c>
       <c r="U11" t="n">
-        <v>3.14</v>
+        <v>3.22</v>
       </c>
       <c r="V11" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W11" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE11" t="n">
         <v>1.06</v>
       </c>
-      <c r="Y11" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.04</v>
-      </c>
       <c r="AF11" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.75</v>
+        <v>1.1</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,80 +2315,80 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.23</v>
+        <v>6.2</v>
       </c>
       <c r="O12" t="n">
-        <v>3.18</v>
+        <v>4.55</v>
       </c>
       <c r="P12" t="n">
-        <v>2.97</v>
+        <v>1.34</v>
       </c>
       <c r="Q12" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ12" t="n">
         <v>2.88</v>
       </c>
-      <c r="R12" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U12" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AK12" t="n">
-        <v>1.54</v>
+        <v>1.06</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>5.5</v>
+        <v>2.23</v>
       </c>
       <c r="O13" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AC13" t="n">
         <v>3.5</v>
-      </c>
-      <c r="P13" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="R13" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="U13" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>4.2</v>
       </c>
       <c r="AD13" t="n">
         <v>1.22</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.2</v>
+        <v>1.79</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.6</v>
+        <v>1.87</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.1</v>
+        <v>1.54</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>6.2</v>
+        <v>2.74</v>
       </c>
       <c r="O14" t="n">
-        <v>4.55</v>
+        <v>3.3</v>
       </c>
       <c r="P14" t="n">
-        <v>1.34</v>
+        <v>2.47</v>
       </c>
       <c r="Q14" t="n">
-        <v>6.25</v>
+        <v>3.29</v>
       </c>
       <c r="R14" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="S14" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="T14" t="n">
-        <v>3.2</v>
+        <v>2.81</v>
       </c>
       <c r="U14" t="n">
-        <v>2.44</v>
+        <v>2.88</v>
       </c>
       <c r="V14" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="W14" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X14" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.57</v>
+        <v>1.96</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.17</v>
+        <v>1.85</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.4</v>
+        <v>3.18</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.46</v>
+        <v>1.27</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>2.88</v>
+        <v>1.33</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.06</v>
+        <v>1.4</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.74</v>
+        <v>2.05</v>
       </c>
       <c r="O15" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P15" t="n">
-        <v>2.47</v>
+        <v>3.6</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
         <v>2.15</v>
       </c>
-      <c r="S15" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="U15" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.96</v>
-      </c>
       <c r="AB15" t="n">
-        <v>1.85</v>
+        <v>1.66</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>3.18</v>
+        <v>1.59</v>
       </c>
       <c r="O16" t="n">
-        <v>3.48</v>
+        <v>4.46</v>
       </c>
       <c r="P16" t="n">
-        <v>2.25</v>
+        <v>5.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.4</v>
+        <v>1.95</v>
       </c>
       <c r="R16" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="S16" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="T16" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="U16" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="V16" t="n">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="W16" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="X16" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.9</v>
+        <v>5.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.73</v>
+        <v>1.51</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.05</v>
+        <v>2.7</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.36</v>
+        <v>1.69</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.2</v>
+        <v>2.31</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.3</v>
+        <v>1.05</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.33</v>
+        <v>2.4</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.15</v>
+        <v>1.52</v>
       </c>
       <c r="O18" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="P18" t="n">
-        <v>3.1</v>
+        <v>5</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.59</v>
+        <v>2.15</v>
       </c>
       <c r="O20" t="n">
-        <v>4.46</v>
+        <v>3.2</v>
       </c>
       <c r="P20" t="n">
-        <v>5.2</v>
+        <v>3.1</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,64 +4382,64 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.62</v>
+        <v>1.34</v>
       </c>
       <c r="O25" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P25" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="R25" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="S25" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="T25" t="n">
         <v>3.25</v>
       </c>
-      <c r="P25" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="R25" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="S25" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="T25" t="n">
-        <v>3</v>
-      </c>
       <c r="U25" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="V25" t="n">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="W25" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X25" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.8</v>
+        <v>5.34</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AB25" t="n">
-        <v>2</v>
+        <v>2.21</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.88</v>
+        <v>2.66</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>1.3</v>
+        <v>1.06</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.4</v>
+        <v>3.12</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,64 +4541,64 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.34</v>
+        <v>2.62</v>
       </c>
       <c r="O26" t="n">
-        <v>4.8</v>
+        <v>3.25</v>
       </c>
       <c r="P26" t="n">
-        <v>7</v>
+        <v>2.47</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.76</v>
+        <v>3.3</v>
       </c>
       <c r="R26" t="n">
-        <v>2.68</v>
+        <v>2.2</v>
       </c>
       <c r="S26" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="T26" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="U26" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="V26" t="n">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="W26" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X26" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z26" t="n">
-        <v>5.34</v>
+        <v>3.8</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.21</v>
+        <v>2</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.66</v>
+        <v>2.88</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>1.06</v>
+        <v>1.3</v>
       </c>
       <c r="AK26" t="n">
-        <v>3.12</v>
+        <v>1.4</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,64 +4700,64 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>2.61</v>
+        <v>2.13</v>
       </c>
       <c r="O27" t="n">
-        <v>2.86</v>
+        <v>3.21</v>
       </c>
       <c r="P27" t="n">
-        <v>3.01</v>
+        <v>3.52</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,64 +5018,64 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>2.13</v>
+        <v>2.61</v>
       </c>
       <c r="O29" t="n">
-        <v>3.21</v>
+        <v>2.86</v>
       </c>
       <c r="P29" t="n">
-        <v>3.52</v>
+        <v>3.01</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,64 +5177,64 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1.89</v>
+        <v>2.94</v>
       </c>
       <c r="O30" t="n">
-        <v>2.95</v>
+        <v>3.65</v>
       </c>
       <c r="P30" t="n">
-        <v>4.1</v>
+        <v>2.14</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,64 +5495,64 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>2.94</v>
+        <v>2.75</v>
       </c>
       <c r="O32" t="n">
-        <v>3.65</v>
+        <v>3.01</v>
       </c>
       <c r="P32" t="n">
-        <v>2.14</v>
+        <v>2.7</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="R32" t="n">
-        <v>2.45</v>
+        <v>1.9</v>
       </c>
       <c r="S32" t="n">
-        <v>1.22</v>
+        <v>1.48</v>
       </c>
       <c r="T32" t="n">
-        <v>3.8</v>
+        <v>2.47</v>
       </c>
       <c r="U32" t="n">
-        <v>2.15</v>
+        <v>3.1</v>
       </c>
       <c r="V32" t="n">
-        <v>1.6</v>
+        <v>1.31</v>
       </c>
       <c r="W32" t="n">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="X32" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE32" t="n">
         <v>1.03</v>
       </c>
-      <c r="Y32" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AF32" t="n">
-        <v>1.44</v>
+        <v>1.82</v>
       </c>
       <c r="AG32" t="n">
-        <v>2.55</v>
+        <v>1.78</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>1.7</v>
+        <v>1.36</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,64 +5654,64 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>2.75</v>
+        <v>1.89</v>
       </c>
       <c r="O33" t="n">
-        <v>3.01</v>
+        <v>2.95</v>
       </c>
       <c r="P33" t="n">
-        <v>2.7</v>
+        <v>4.1</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1.95</v>
+        <v>2.23</v>
       </c>
       <c r="O40" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P40" t="n">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,64 +7085,64 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>2.16</v>
+        <v>1.97</v>
       </c>
       <c r="O42" t="n">
-        <v>2.85</v>
+        <v>2.93</v>
       </c>
       <c r="P42" t="n">
-        <v>3.85</v>
+        <v>3.99</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7155,10 +7155,10 @@
         </is>
       </c>
       <c r="AJ42" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK42" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL42" t="n">
         <v>0</v>
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="O43" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="P43" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="O44" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="P44" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,64 +7562,64 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>1.97</v>
+        <v>2.16</v>
       </c>
       <c r="O45" t="n">
-        <v>2.93</v>
+        <v>2.85</v>
       </c>
       <c r="P45" t="n">
-        <v>3.99</v>
+        <v>3.85</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7632,10 +7632,10 @@
         </is>
       </c>
       <c r="AJ45" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK45" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AL45" t="n">
         <v>0</v>
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>2.35</v>
+        <v>2.04</v>
       </c>
       <c r="O47" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="P47" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>

--- a/jogos_2026-07-11.xlsx
+++ b/jogos_2026-07-11.xlsx
@@ -734,22 +734,22 @@
         <v>2.57</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="R2" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S2" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T2" t="n">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="U2" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="V2" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W2" t="n">
         <v>1.07</v>
@@ -761,19 +761,19 @@
         <v>1.21</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.7</v>
+        <v>3.58</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AB2" t="n">
         <v>2</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="AE2" t="n">
         <v>1.1</v>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>2.18</v>
       </c>
       <c r="S3" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T3" t="n">
-        <v>3.25</v>
+        <v>3.14</v>
       </c>
       <c r="U3" t="n">
         <v>2.44</v>
@@ -917,31 +917,31 @@
         <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.95</v>
+        <v>4.05</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="AB3" t="n">
         <v>2.1</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AE3" t="n">
         <v>1.11</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -1043,22 +1043,22 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.78</v>
+        <v>2.71</v>
       </c>
       <c r="O4" t="n">
-        <v>3.45</v>
+        <v>3.44</v>
       </c>
       <c r="P4" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="R4" t="n">
         <v>2.21</v>
       </c>
-      <c r="Q4" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R4" t="n">
-        <v>2.22</v>
-      </c>
       <c r="S4" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T4" t="n">
         <v>3.14</v>
@@ -1070,7 +1070,7 @@
         <v>1.5</v>
       </c>
       <c r="W4" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X4" t="n">
         <v>1.01</v>
@@ -1082,19 +1082,19 @@
         <v>3.98</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AF4" t="n">
         <v>1.53</v>
@@ -1116,7 +1116,7 @@
         <v>1.22</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>APIA Leichhardt Tigers</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Sydney II</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,65 +1202,65 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.64</v>
+        <v>1.37</v>
       </c>
       <c r="O5" t="n">
-        <v>3.74</v>
+        <v>4.55</v>
       </c>
       <c r="P5" t="n">
-        <v>4.47</v>
+        <v>6.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.2</v>
+        <v>1.84</v>
       </c>
       <c r="R5" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AG5" t="n">
         <v>2.23</v>
       </c>
-      <c r="S5" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="T5" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>2.07</v>
-      </c>
       <c r="AH5" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.03</v>
+        <v>2.65</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>APIA Leichhardt Tigers</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sydney II</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.37</v>
+        <v>1.64</v>
       </c>
       <c r="O6" t="n">
-        <v>4.55</v>
+        <v>3.74</v>
       </c>
       <c r="P6" t="n">
-        <v>6.5</v>
+        <v>4.47</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.66</v>
+        <v>2.2</v>
       </c>
       <c r="R6" t="n">
-        <v>2.95</v>
+        <v>2.22</v>
       </c>
       <c r="S6" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="T6" t="n">
-        <v>3.68</v>
+        <v>3.04</v>
       </c>
       <c r="U6" t="n">
-        <v>1.8</v>
+        <v>2.44</v>
       </c>
       <c r="V6" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="AA6" t="n">
         <v>1.67</v>
       </c>
-      <c r="W6" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AB6" t="n">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.79</v>
+        <v>2.62</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.85</v>
+        <v>1.38</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.36</v>
+        <v>1.11</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.85</v>
+        <v>2.03</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.05</v>
+        <v>2.23</v>
       </c>
       <c r="O9" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="P9" t="n">
-        <v>3.35</v>
+        <v>2.97</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="R9" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="S9" t="n">
         <v>1.4</v>
       </c>
       <c r="T9" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="U9" t="n">
-        <v>3.14</v>
+        <v>2.91</v>
       </c>
       <c r="V9" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W9" t="n">
         <v>1.03</v>
       </c>
       <c r="X9" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Z9" t="n">
-        <v>3</v>
+        <v>3.21</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AE9" t="n">
         <v>1.04</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.87</v>
+        <v>2.05</v>
       </c>
       <c r="O10" t="n">
-        <v>3.3</v>
+        <v>3.17</v>
       </c>
       <c r="P10" t="n">
-        <v>3.6</v>
+        <v>3.17</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.92</v>
+        <v>2.15</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.76</v>
+        <v>1.66</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,80 +2156,80 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>5.5</v>
+        <v>2.74</v>
       </c>
       <c r="O11" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P11" t="n">
-        <v>1.53</v>
+        <v>2.47</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.5</v>
+        <v>3.1</v>
       </c>
       <c r="R11" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="S11" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ11" t="n">
         <v>1.48</v>
       </c>
-      <c r="T11" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="U11" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.23</v>
-      </c>
       <c r="AK11" t="n">
-        <v>1.1</v>
+        <v>1.48</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>6.2</v>
+        <v>2.05</v>
       </c>
       <c r="O12" t="n">
-        <v>4.55</v>
+        <v>3.2</v>
       </c>
       <c r="P12" t="n">
-        <v>1.34</v>
+        <v>3.35</v>
       </c>
       <c r="Q12" t="n">
-        <v>6.25</v>
+        <v>2.49</v>
       </c>
       <c r="R12" t="n">
-        <v>2.4</v>
+        <v>2.14</v>
       </c>
       <c r="S12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3</v>
+      </c>
+      <c r="V12" t="n">
         <v>1.32</v>
       </c>
-      <c r="T12" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U12" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.5</v>
-      </c>
       <c r="W12" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="X12" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE12" t="n">
         <v>1.04</v>
       </c>
-      <c r="Y12" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AF12" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>2.88</v>
+        <v>1.25</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.06</v>
+        <v>1.77</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,80 +2474,80 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.23</v>
+        <v>6.2</v>
       </c>
       <c r="O13" t="n">
-        <v>3.18</v>
+        <v>4.2</v>
       </c>
       <c r="P13" t="n">
-        <v>2.97</v>
+        <v>1.28</v>
       </c>
       <c r="Q13" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="R13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ13" t="n">
         <v>2.88</v>
       </c>
-      <c r="R13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AK13" t="n">
-        <v>1.54</v>
+        <v>1.06</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.74</v>
+        <v>1.87</v>
       </c>
       <c r="O14" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P14" t="n">
-        <v>2.47</v>
+        <v>3.6</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.29</v>
+        <v>2.52</v>
       </c>
       <c r="R14" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S14" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T14" t="n">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
       <c r="U14" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="V14" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W14" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD14" t="n">
         <v>1.25</v>
       </c>
-      <c r="Z14" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AE14" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="AG14" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.4</v>
+        <v>1.83</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.05</v>
+        <v>5.5</v>
       </c>
       <c r="O15" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="P15" t="n">
-        <v>3.6</v>
+        <v>1.53</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2960,7 +2960,7 @@
         <v>5.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="R16" t="n">
         <v>2.5</v>
@@ -2978,7 +2978,7 @@
         <v>1.67</v>
       </c>
       <c r="W16" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X16" t="n">
         <v>1.02</v>
@@ -2990,19 +2990,19 @@
         <v>5.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AF16" t="n">
         <v>1.53</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.52</v>
+        <v>2.15</v>
       </c>
       <c r="O18" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="P18" t="n">
-        <v>5</v>
+        <v>3.1</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.15</v>
+        <v>3.18</v>
       </c>
       <c r="O20" t="n">
-        <v>3.2</v>
+        <v>3.48</v>
       </c>
       <c r="P20" t="n">
-        <v>3.1</v>
+        <v>2.25</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.52</v>
+        <v>1.36</v>
       </c>
       <c r="O21" t="n">
-        <v>3.42</v>
+        <v>4.3</v>
       </c>
       <c r="P21" t="n">
-        <v>2.4</v>
+        <v>7.5</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.36</v>
+        <v>2.5</v>
       </c>
       <c r="O22" t="n">
-        <v>4.3</v>
+        <v>3.42</v>
       </c>
       <c r="P22" t="n">
-        <v>7.5</v>
+        <v>2.37</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="R23" t="n">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="S23" t="n">
-        <v>1.14</v>
+        <v>1.35</v>
       </c>
       <c r="T23" t="n">
-        <v>4.8</v>
+        <v>3.2</v>
       </c>
       <c r="U23" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AB23" t="n">
         <v>2.01</v>
       </c>
-      <c r="V23" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>6.15</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>3.3</v>
-      </c>
       <c r="AC23" t="n">
-        <v>1.96</v>
+        <v>3</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.8</v>
+        <v>1.39</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.31</v>
+        <v>1.11</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.33</v>
+        <v>1.61</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.98</v>
+        <v>2.18</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="R24" t="n">
-        <v>2.25</v>
+        <v>2.36</v>
       </c>
       <c r="S24" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="T24" t="n">
+        <v>4</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>6.26</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AE24" t="n">
         <v>1.3</v>
       </c>
-      <c r="T24" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U24" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>4.54</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.11</v>
-      </c>
       <c r="AF24" t="n">
-        <v>1.61</v>
+        <v>1.36</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.18</v>
+        <v>2.98</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="O25" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="P25" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="Q25" t="n">
         <v>1.76</v>
@@ -4541,10 +4541,10 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>2.62</v>
+        <v>2.52</v>
       </c>
       <c r="O26" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="P26" t="n">
         <v>2.47</v>
@@ -4556,7 +4556,7 @@
         <v>2.2</v>
       </c>
       <c r="S26" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T26" t="n">
         <v>3</v>
@@ -4595,7 +4595,7 @@
         <v>1.13</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AG26" t="n">
         <v>2.2</v>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AK26" t="n">
         <v>1.4</v>
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,64 +4700,64 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>2.13</v>
+        <v>2.61</v>
       </c>
       <c r="O27" t="n">
-        <v>3.21</v>
+        <v>2.86</v>
       </c>
       <c r="P27" t="n">
-        <v>3.52</v>
+        <v>3.01</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,64 +4859,64 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>1.95</v>
+        <v>2.13</v>
       </c>
       <c r="O28" t="n">
-        <v>3.4</v>
+        <v>3.21</v>
       </c>
       <c r="P28" t="n">
-        <v>3.51</v>
+        <v>3.52</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="AJ28" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,64 +5018,64 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>2.61</v>
+        <v>1.95</v>
       </c>
       <c r="O29" t="n">
-        <v>2.86</v>
+        <v>3.4</v>
       </c>
       <c r="P29" t="n">
-        <v>3.01</v>
+        <v>3.51</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.1</v>
+        <v>2.45</v>
       </c>
       <c r="R29" t="n">
-        <v>1.97</v>
+        <v>2.25</v>
       </c>
       <c r="S29" t="n">
-        <v>1.45</v>
+        <v>1.35</v>
       </c>
       <c r="T29" t="n">
-        <v>2.55</v>
+        <v>2.87</v>
       </c>
       <c r="U29" t="n">
-        <v>3.1</v>
+        <v>2.63</v>
       </c>
       <c r="V29" t="n">
-        <v>1.31</v>
+        <v>1.47</v>
       </c>
       <c r="W29" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X29" t="n">
         <v>1.03</v>
       </c>
-      <c r="X29" t="n">
-        <v>1.04</v>
-      </c>
       <c r="Y29" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.75</v>
+        <v>3.95</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.24</v>
+        <v>1.74</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.62</v>
+        <v>2.05</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.9</v>
+        <v>2.88</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.94</v>
+        <v>1.6</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.79</v>
+        <v>2.15</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="AJ29" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.52</v>
+        <v>1.82</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,64 +5177,64 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>2.94</v>
+        <v>2.75</v>
       </c>
       <c r="O30" t="n">
-        <v>3.65</v>
+        <v>3.01</v>
       </c>
       <c r="P30" t="n">
-        <v>2.14</v>
+        <v>2.7</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="R30" t="n">
-        <v>2.45</v>
+        <v>1.9</v>
       </c>
       <c r="S30" t="n">
-        <v>1.22</v>
+        <v>1.48</v>
       </c>
       <c r="T30" t="n">
-        <v>3.8</v>
+        <v>2.47</v>
       </c>
       <c r="U30" t="n">
-        <v>2.15</v>
+        <v>3.1</v>
       </c>
       <c r="V30" t="n">
-        <v>1.6</v>
+        <v>1.31</v>
       </c>
       <c r="W30" t="n">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="X30" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AE30" t="n">
         <v>1.03</v>
       </c>
-      <c r="Y30" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AF30" t="n">
-        <v>1.44</v>
+        <v>1.94</v>
       </c>
       <c r="AG30" t="n">
-        <v>2.55</v>
+        <v>1.79</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>1.7</v>
+        <v>1.36</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,28 +5336,28 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1.74</v>
+        <v>2.83</v>
       </c>
       <c r="O31" t="n">
-        <v>3.78</v>
+        <v>3.75</v>
       </c>
       <c r="P31" t="n">
-        <v>3.84</v>
+        <v>2.13</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.26</v>
+        <v>3.4</v>
       </c>
       <c r="R31" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="S31" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T31" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="U31" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="V31" t="n">
         <v>1.62</v>
@@ -5366,34 +5366,34 @@
         <v>1.12</v>
       </c>
       <c r="X31" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="Z31" t="n">
-        <v>5.3</v>
+        <v>5.42</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.02</v>
+        <v>2.32</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AF31" t="n">
         <v>1.44</v>
       </c>
       <c r="AG31" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="AJ31" t="n">
-        <v>1.18</v>
+        <v>1.7</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.9</v>
+        <v>1.34</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,64 +5495,64 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>2.75</v>
+        <v>1.89</v>
       </c>
       <c r="O32" t="n">
-        <v>3.01</v>
+        <v>2.95</v>
       </c>
       <c r="P32" t="n">
-        <v>2.7</v>
+        <v>4.1</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,64 +5654,64 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1.89</v>
+        <v>1.75</v>
       </c>
       <c r="O33" t="n">
-        <v>2.95</v>
+        <v>3.8</v>
       </c>
       <c r="P33" t="n">
-        <v>4.1</v>
+        <v>3.84</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -5822,10 +5822,10 @@
         <v>1.47</v>
       </c>
       <c r="Q34" t="n">
-        <v>5.5</v>
+        <v>7.3</v>
       </c>
       <c r="R34" t="n">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="S34" t="n">
         <v>1.33</v>
@@ -5849,28 +5849,28 @@
         <v>1.3</v>
       </c>
       <c r="Z34" t="n">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AC34" t="n">
         <v>3.3</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="AE34" t="n">
         <v>1.06</v>
       </c>
       <c r="AF34" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.82</v>
+        <v>1.64</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5972,64 +5972,64 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>5.75</v>
+        <v>4.6</v>
       </c>
       <c r="O35" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="P35" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="Q35" t="n">
-        <v>5.48</v>
+        <v>5.36</v>
       </c>
       <c r="R35" t="n">
-        <v>2.52</v>
+        <v>2.68</v>
       </c>
       <c r="S35" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="T35" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="U35" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="V35" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="W35" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X35" t="n">
         <v>1.02</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="Z35" t="n">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AB35" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AE35" t="n">
         <v>1.25</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AG35" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6042,7 +6042,7 @@
         </is>
       </c>
       <c r="AJ35" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AK35" t="n">
         <v>1.13</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,64 +6131,64 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1.86</v>
+        <v>1.32</v>
       </c>
       <c r="O36" t="n">
-        <v>3.71</v>
+        <v>4.8</v>
       </c>
       <c r="P36" t="n">
-        <v>4.15</v>
+        <v>7.8</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z36" t="n">
-        <v>4.14</v>
+        <v>4</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.76</v>
+        <v>1.61</v>
       </c>
       <c r="AB36" t="n">
         <v>2.08</v>
       </c>
       <c r="AC36" t="n">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="AG36" t="n">
-        <v>2.1</v>
+        <v>1.78</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AK36" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6290,61 +6290,61 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="O37" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="P37" t="n">
-        <v>4.15</v>
+        <v>4.55</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="R37" t="n">
         <v>2.3</v>
       </c>
       <c r="S37" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T37" t="n">
         <v>3.3</v>
       </c>
       <c r="U37" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="V37" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="W37" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X37" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z37" t="n">
-        <v>3.95</v>
+        <v>3.65</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AC37" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AE37" t="n">
         <v>1.15</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AG37" t="n">
         <v>2.05</v>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK37" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,64 +6449,64 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1.32</v>
+        <v>1.7</v>
       </c>
       <c r="O38" t="n">
-        <v>4.8</v>
+        <v>3.75</v>
       </c>
       <c r="P38" t="n">
-        <v>7.8</v>
+        <v>4.58</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z38" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.61</v>
+        <v>1.74</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.78</v>
+        <v>2.1</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AK38" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>2.86</v>
+        <v>2.75</v>
       </c>
       <c r="O39" t="n">
         <v>2.9</v>
@@ -6629,7 +6629,7 @@
         <v>2.41</v>
       </c>
       <c r="U39" t="n">
-        <v>3.18</v>
+        <v>3.15</v>
       </c>
       <c r="V39" t="n">
         <v>1.28</v>
@@ -6647,10 +6647,10 @@
         <v>2.7</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AC39" t="n">
         <v>4.2</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,49 +6767,49 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>2.23</v>
+        <v>2.62</v>
       </c>
       <c r="O40" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="P40" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA40" t="n">
         <v>3.1</v>
       </c>
-      <c r="P40" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
-      <c r="R40" t="n">
-        <v>0</v>
-      </c>
-      <c r="S40" t="n">
-        <v>0</v>
-      </c>
-      <c r="T40" t="n">
-        <v>0</v>
-      </c>
-      <c r="U40" t="n">
-        <v>0</v>
-      </c>
-      <c r="V40" t="n">
-        <v>0</v>
-      </c>
-      <c r="W40" t="n">
-        <v>0</v>
-      </c>
-      <c r="X40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>0</v>
-      </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,64 +6926,64 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="O41" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="P41" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -6996,10 +6996,10 @@
         </is>
       </c>
       <c r="AJ41" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AK41" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL41" t="n">
         <v>0</v>
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,80 +7085,80 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>1.97</v>
+        <v>1.73</v>
       </c>
       <c r="O42" t="n">
-        <v>2.93</v>
+        <v>2.9</v>
       </c>
       <c r="P42" t="n">
-        <v>3.99</v>
+        <v>5.25</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.9</v>
+        <v>2.48</v>
       </c>
       <c r="R42" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="S42" t="n">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="T42" t="n">
-        <v>2.18</v>
+        <v>2.04</v>
       </c>
       <c r="U42" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="V42" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="W42" t="n">
         <v>1.03</v>
       </c>
       <c r="X42" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.38</v>
+        <v>2.03</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.78</v>
+        <v>3.04</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AC42" t="n">
-        <v>5.6</v>
+        <v>6.25</v>
       </c>
       <c r="AD42" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ42" t="n">
         <v>1.08</v>
       </c>
-      <c r="AE42" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AG42" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ42" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AK42" t="n">
-        <v>1.57</v>
+        <v>1.92</v>
       </c>
       <c r="AL42" t="n">
         <v>0</v>
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,64 +7244,64 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="O43" t="n">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="P43" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7314,10 +7314,10 @@
         </is>
       </c>
       <c r="AJ43" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK43" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AL43" t="n">
         <v>0</v>
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,64 +7403,64 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="O44" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="P44" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="AJ44" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK44" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL44" t="n">
         <v>0</v>
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,64 +7562,64 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>2.16</v>
+        <v>1.97</v>
       </c>
       <c r="O45" t="n">
-        <v>2.85</v>
+        <v>2.93</v>
       </c>
       <c r="P45" t="n">
-        <v>3.85</v>
+        <v>3.99</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7632,10 +7632,10 @@
         </is>
       </c>
       <c r="AJ45" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK45" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL45" t="n">
         <v>0</v>
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,64 +7721,64 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7791,10 +7791,10 @@
         </is>
       </c>
       <c r="AJ46" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK46" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL46" t="n">
         <v>0</v>
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>2.04</v>
+        <v>1.65</v>
       </c>
       <c r="O47" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P47" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -7919,10 +7919,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -8225,22 +8225,22 @@
         <v>1.36</v>
       </c>
       <c r="W49" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X49" t="n">
         <v>1.05</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z49" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="AA49" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB49" t="n">
         <v>1.85</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>1.9</v>
       </c>
       <c r="AC49" t="n">
         <v>3.3</v>
@@ -8366,22 +8366,22 @@
         <v>2.22</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="R50" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="S50" t="n">
         <v>1.34</v>
       </c>
       <c r="T50" t="n">
-        <v>2.29</v>
+        <v>3</v>
       </c>
       <c r="U50" t="n">
         <v>2.2</v>
       </c>
       <c r="V50" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W50" t="n">
         <v>1.08</v>
@@ -8396,10 +8396,10 @@
         <v>3.4</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.84</v>
+        <v>1.67</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AC50" t="n">
         <v>3.08</v>
@@ -8408,7 +8408,7 @@
         <v>1.28</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF50" t="n">
         <v>1.67</v>
@@ -8427,10 +8427,10 @@
         </is>
       </c>
       <c r="AJ50" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="AK50" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AL50" t="n">
         <v>0</v>
@@ -8516,64 +8516,64 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="O51" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="P51" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="S51" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="T51" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U51" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="V51" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W51" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X51" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AC51" t="n">
-        <v>0</v>
+        <v>6.16</v>
       </c>
       <c r="AD51" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AG51" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8586,10 +8586,10 @@
         </is>
       </c>
       <c r="AJ51" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK51" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AL51" t="n">
         <v>0</v>
@@ -8843,19 +8843,19 @@
         <v>3.75</v>
       </c>
       <c r="Q53" t="n">
-        <v>2.76</v>
+        <v>2.38</v>
       </c>
       <c r="R53" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S53" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T53" t="n">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="U53" t="n">
-        <v>2.75</v>
+        <v>2.83</v>
       </c>
       <c r="V53" t="n">
         <v>1.36</v>
@@ -8864,25 +8864,25 @@
         <v>1.04</v>
       </c>
       <c r="X53" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z53" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AC53" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AD53" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE53" t="n">
         <v>1.08</v>
@@ -8904,10 +8904,10 @@
         </is>
       </c>
       <c r="AJ53" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK53" t="n">
-        <v>1.58</v>
+        <v>1.71</v>
       </c>
       <c r="AL53" t="n">
         <v>0</v>

--- a/jogos_2026-07-11.xlsx
+++ b/jogos_2026-07-11.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,31 +725,31 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="O2" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="P2" t="n">
-        <v>2.57</v>
+        <v>2.4</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.88</v>
+        <v>3.12</v>
       </c>
       <c r="R2" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="S2" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="T2" t="n">
-        <v>2.92</v>
+        <v>3.14</v>
       </c>
       <c r="U2" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="V2" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="W2" t="n">
         <v>1.07</v>
@@ -758,31 +758,31 @@
         <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.58</v>
+        <v>4.05</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.74</v>
+        <v>1.66</v>
       </c>
       <c r="AB2" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.78</v>
+        <v>2.62</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.45</v>
+        <v>2.71</v>
       </c>
       <c r="O3" t="n">
-        <v>3.6</v>
+        <v>3.44</v>
       </c>
       <c r="P3" t="n">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.12</v>
+        <v>3.37</v>
       </c>
       <c r="R3" t="n">
-        <v>2.18</v>
+        <v>2.21</v>
       </c>
       <c r="S3" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T3" t="n">
         <v>3.14</v>
       </c>
       <c r="U3" t="n">
-        <v>2.44</v>
+        <v>2.28</v>
       </c>
       <c r="V3" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="W3" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X3" t="n">
         <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.05</v>
+        <v>3.98</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF3" t="n">
         <v>1.53</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.29</v>
+        <v>2.32</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>1.22</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.71</v>
+        <v>2.35</v>
       </c>
       <c r="O4" t="n">
-        <v>3.44</v>
+        <v>3.35</v>
       </c>
       <c r="P4" t="n">
-        <v>2.26</v>
+        <v>2.57</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.37</v>
+        <v>2.88</v>
       </c>
       <c r="R4" t="n">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="S4" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="T4" t="n">
-        <v>3.14</v>
+        <v>2.92</v>
       </c>
       <c r="U4" t="n">
-        <v>2.28</v>
+        <v>2.5</v>
       </c>
       <c r="V4" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="W4" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X4" t="n">
         <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.98</v>
+        <v>3.58</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.62</v>
+        <v>1.74</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.5</v>
+        <v>2.78</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.43</v>
+        <v>1.34</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.32</v>
+        <v>2.17</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.37</v>
+        <v>1.46</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.23</v>
+        <v>2.05</v>
       </c>
       <c r="O9" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="P9" t="n">
-        <v>2.97</v>
+        <v>3.17</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2000,61 +2000,61 @@
         <v>2.05</v>
       </c>
       <c r="O10" t="n">
-        <v>3.17</v>
+        <v>3.2</v>
       </c>
       <c r="P10" t="n">
-        <v>3.17</v>
+        <v>3.35</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,80 +2156,80 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.74</v>
+        <v>1.87</v>
       </c>
       <c r="O11" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P11" t="n">
-        <v>2.47</v>
+        <v>3.6</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.1</v>
+        <v>2.52</v>
       </c>
       <c r="R11" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S11" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T11" t="n">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="U11" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="V11" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W11" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X11" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="AA11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AG11" t="n">
         <v>1.95</v>
       </c>
-      <c r="AB11" t="n">
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AK11" t="n">
         <v>1.83</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>1.48</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.05</v>
+        <v>5.5</v>
       </c>
       <c r="O12" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="P12" t="n">
-        <v>3.35</v>
+        <v>1.53</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.49</v>
+        <v>6.5</v>
       </c>
       <c r="R12" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="S12" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="T12" t="n">
-        <v>2.75</v>
+        <v>2.53</v>
       </c>
       <c r="U12" t="n">
-        <v>3</v>
+        <v>3.22</v>
       </c>
       <c r="V12" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W12" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X12" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE12" t="n">
         <v>1.06</v>
       </c>
-      <c r="Y12" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.04</v>
-      </c>
       <c r="AF12" t="n">
-        <v>1.87</v>
+        <v>2.2</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.82</v>
+        <v>1.6</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.25</v>
+        <v>2.38</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.77</v>
+        <v>1.1</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.87</v>
+        <v>2.23</v>
       </c>
       <c r="O14" t="n">
-        <v>3.25</v>
+        <v>3.18</v>
       </c>
       <c r="P14" t="n">
-        <v>3.6</v>
+        <v>2.97</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.52</v>
+        <v>2.55</v>
       </c>
       <c r="R14" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="S14" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T14" t="n">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="U14" t="n">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
       <c r="V14" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="W14" t="n">
         <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.25</v>
+        <v>3.21</v>
       </c>
       <c r="AA14" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="AC14" t="n">
         <v>3.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AF14" t="n">
         <v>1.79</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,80 +2792,80 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>5.5</v>
+        <v>2.74</v>
       </c>
       <c r="O15" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P15" t="n">
-        <v>1.53</v>
+        <v>2.47</v>
       </c>
       <c r="Q15" t="n">
-        <v>6.5</v>
+        <v>3.1</v>
       </c>
       <c r="R15" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="S15" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ15" t="n">
         <v>1.48</v>
       </c>
-      <c r="T15" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="U15" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ15" t="n">
-        <v>2.38</v>
-      </c>
       <c r="AK15" t="n">
-        <v>1.1</v>
+        <v>1.48</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.59</v>
+        <v>3.18</v>
       </c>
       <c r="O16" t="n">
-        <v>4.46</v>
+        <v>3.48</v>
       </c>
       <c r="P16" t="n">
-        <v>5.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.99</v>
+        <v>3.4</v>
       </c>
       <c r="R16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U16" t="n">
         <v>2.5</v>
       </c>
-      <c r="S16" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="U16" t="n">
-        <v>2.1</v>
-      </c>
       <c r="V16" t="n">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="W16" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="X16" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="Z16" t="n">
-        <v>5.5</v>
+        <v>3.9</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.52</v>
+        <v>1.73</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.6</v>
+        <v>2.09</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.15</v>
+        <v>2.8</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.67</v>
+        <v>1.36</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.24</v>
+        <v>1.11</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.31</v>
+        <v>2.2</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.05</v>
+        <v>1.3</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.4</v>
+        <v>1.36</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.15</v>
+        <v>1.52</v>
       </c>
       <c r="O18" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="P18" t="n">
-        <v>3.1</v>
+        <v>5</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="O19" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="P19" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="R19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA19" t="n">
         <v>1.52</v>
       </c>
-      <c r="O19" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="P19" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>0</v>
-      </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>3.18</v>
+        <v>2.15</v>
       </c>
       <c r="O20" t="n">
-        <v>3.48</v>
+        <v>3.2</v>
       </c>
       <c r="P20" t="n">
-        <v>2.25</v>
+        <v>3.1</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.36</v>
+        <v>2.5</v>
       </c>
       <c r="O21" t="n">
-        <v>4.3</v>
+        <v>3.42</v>
       </c>
       <c r="P21" t="n">
-        <v>7.5</v>
+        <v>2.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.5</v>
+        <v>1.36</v>
       </c>
       <c r="O22" t="n">
-        <v>3.42</v>
+        <v>4.3</v>
       </c>
       <c r="P22" t="n">
-        <v>2.37</v>
+        <v>7.5</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="R23" t="n">
-        <v>2.25</v>
+        <v>2.36</v>
       </c>
       <c r="S23" t="n">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="T23" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="U23" t="n">
-        <v>2.64</v>
+        <v>2.01</v>
       </c>
       <c r="V23" t="n">
-        <v>1.44</v>
+        <v>1.74</v>
       </c>
       <c r="W23" t="n">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="X23" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.23</v>
+        <v>1.06</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.54</v>
+        <v>6.26</v>
       </c>
       <c r="AA23" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AD23" t="n">
         <v>1.82</v>
       </c>
-      <c r="AB23" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.39</v>
-      </c>
       <c r="AE23" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.61</v>
+        <v>1.36</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.18</v>
+        <v>2.98</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="R24" t="n">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="S24" t="n">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="T24" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="U24" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AB24" t="n">
         <v>2.01</v>
       </c>
-      <c r="V24" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>6.26</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>3.3</v>
-      </c>
       <c r="AC24" t="n">
-        <v>2.01</v>
+        <v>3</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.82</v>
+        <v>1.39</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.3</v>
+        <v>1.11</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.36</v>
+        <v>1.61</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.98</v>
+        <v>2.18</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,64 +4382,64 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1.27</v>
+        <v>2.52</v>
       </c>
       <c r="O25" t="n">
-        <v>5.1</v>
+        <v>3.5</v>
       </c>
       <c r="P25" t="n">
-        <v>6.2</v>
+        <v>2.47</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.76</v>
+        <v>3.3</v>
       </c>
       <c r="R25" t="n">
-        <v>2.68</v>
+        <v>2.2</v>
       </c>
       <c r="S25" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="T25" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="U25" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="V25" t="n">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="W25" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X25" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z25" t="n">
-        <v>5.34</v>
+        <v>3.8</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.21</v>
+        <v>2</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.66</v>
+        <v>2.88</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.85</v>
+        <v>1.55</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>1.06</v>
+        <v>1.5</v>
       </c>
       <c r="AK25" t="n">
-        <v>3.12</v>
+        <v>1.4</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,64 +4541,64 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>2.52</v>
+        <v>1.27</v>
       </c>
       <c r="O26" t="n">
-        <v>3.5</v>
+        <v>5.1</v>
       </c>
       <c r="P26" t="n">
-        <v>2.47</v>
+        <v>6.2</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.3</v>
+        <v>1.76</v>
       </c>
       <c r="R26" t="n">
-        <v>2.2</v>
+        <v>2.68</v>
       </c>
       <c r="S26" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="T26" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="U26" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="V26" t="n">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="W26" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X26" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.8</v>
+        <v>5.34</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AB26" t="n">
-        <v>2</v>
+        <v>2.21</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.88</v>
+        <v>2.66</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.55</v>
+        <v>1.85</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>1.5</v>
+        <v>1.06</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.4</v>
+        <v>3.12</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4653,7 +4653,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,25 +4700,25 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>2.61</v>
+        <v>2.75</v>
       </c>
       <c r="O27" t="n">
-        <v>2.86</v>
+        <v>3.01</v>
       </c>
       <c r="P27" t="n">
-        <v>3.01</v>
+        <v>2.7</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="R27" t="n">
-        <v>2.12</v>
+        <v>1.9</v>
       </c>
       <c r="S27" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="T27" t="n">
-        <v>2.75</v>
+        <v>2.47</v>
       </c>
       <c r="U27" t="n">
         <v>3.1</v>
@@ -4730,34 +4730,34 @@
         <v>1.03</v>
       </c>
       <c r="X27" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.05</v>
+        <v>2.75</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.71</v>
+        <v>1.57</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AE27" t="n">
         <v>1.03</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.77</v>
+        <v>1.94</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.6</v>
+        <v>1.41</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4803,7 +4803,7 @@
         <v>0</v>
       </c>
       <c r="AU27" s="3" t="n">
-        <v>46214.41666666666</v>
+        <v>46214.375</v>
       </c>
     </row>
     <row r="28">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,80 +5018,80 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>1.95</v>
+        <v>2.61</v>
       </c>
       <c r="O29" t="n">
-        <v>3.4</v>
+        <v>2.86</v>
       </c>
       <c r="P29" t="n">
-        <v>3.51</v>
+        <v>3.01</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.45</v>
+        <v>3.1</v>
       </c>
       <c r="R29" t="n">
-        <v>2.25</v>
+        <v>1.97</v>
       </c>
       <c r="S29" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="T29" t="n">
-        <v>2.87</v>
+        <v>2.75</v>
       </c>
       <c r="U29" t="n">
-        <v>2.63</v>
+        <v>3.2</v>
       </c>
       <c r="V29" t="n">
-        <v>1.47</v>
+        <v>1.3</v>
       </c>
       <c r="W29" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X29" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE29" t="n">
         <v>1.03</v>
       </c>
-      <c r="Y29" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1.11</v>
-      </c>
       <c r="AF29" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ29" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AK29" t="n">
         <v>1.6</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ29" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>1.82</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -5130,12 +5130,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,64 +5177,64 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>2.75</v>
+        <v>1.95</v>
       </c>
       <c r="O30" t="n">
-        <v>3.01</v>
+        <v>3.4</v>
       </c>
       <c r="P30" t="n">
-        <v>2.7</v>
+        <v>3.51</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.3</v>
+        <v>2.45</v>
       </c>
       <c r="R30" t="n">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="S30" t="n">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="T30" t="n">
-        <v>2.47</v>
+        <v>2.87</v>
       </c>
       <c r="U30" t="n">
-        <v>3.1</v>
+        <v>2.63</v>
       </c>
       <c r="V30" t="n">
-        <v>1.31</v>
+        <v>1.47</v>
       </c>
       <c r="W30" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X30" t="n">
         <v>1.03</v>
       </c>
-      <c r="X30" t="n">
-        <v>1.05</v>
-      </c>
       <c r="Y30" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AD30" t="n">
         <v>1.36</v>
       </c>
-      <c r="Z30" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AE30" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.94</v>
+        <v>1.6</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.79</v>
+        <v>2.15</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.41</v>
+        <v>1.82</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5280,7 +5280,7 @@
         <v>0</v>
       </c>
       <c r="AU30" s="3" t="n">
-        <v>46214.45833333334</v>
+        <v>46214.41666666666</v>
       </c>
     </row>
     <row r="31">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="O33" t="n">
         <v>3.8</v>
       </c>
       <c r="P33" t="n">
-        <v>3.84</v>
+        <v>3.6</v>
       </c>
       <c r="Q33" t="n">
         <v>2.26</v>
@@ -5861,7 +5861,7 @@
         <v>3.3</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="AE34" t="n">
         <v>1.06</v>
@@ -5886,7 +5886,7 @@
         <v>1.23</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,64 +6131,64 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1.32</v>
+        <v>1.67</v>
       </c>
       <c r="O36" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="P36" t="n">
-        <v>7.8</v>
+        <v>4.55</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z36" t="n">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AB36" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AC36" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="AE36" t="n">
         <v>1.15</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.78</v>
+        <v>2.05</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AK36" t="n">
-        <v>2.7</v>
+        <v>2.15</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,64 +6290,64 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.67</v>
+        <v>1.32</v>
       </c>
       <c r="O37" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P37" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z37" t="n">
         <v>4</v>
       </c>
-      <c r="P37" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="R37" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="S37" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="T37" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U37" t="n">
+      <c r="AA37" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AC37" t="n">
         <v>2.5</v>
       </c>
-      <c r="V37" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X37" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>2.8</v>
-      </c>
       <c r="AD37" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="AE37" t="n">
         <v>1.15</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="AG37" t="n">
-        <v>2.05</v>
+        <v>1.78</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AK37" t="n">
-        <v>2.15</v>
+        <v>2.7</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,64 +6767,64 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>2.62</v>
+        <v>2.3</v>
       </c>
       <c r="O40" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="P40" t="n">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AA40" t="n">
-        <v>3.1</v>
+        <v>3.34</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="AJ40" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AK40" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,64 +6926,64 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>2.3</v>
+        <v>1.73</v>
       </c>
       <c r="O41" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="P41" t="n">
-        <v>3.6</v>
+        <v>5.25</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.3</v>
+        <v>2.48</v>
       </c>
       <c r="R41" t="n">
-        <v>1.59</v>
+        <v>1.78</v>
       </c>
       <c r="S41" t="n">
-        <v>1.84</v>
+        <v>1.69</v>
       </c>
       <c r="T41" t="n">
-        <v>1.86</v>
+        <v>2.04</v>
       </c>
       <c r="U41" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="V41" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="W41" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X41" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.94</v>
+        <v>2.03</v>
       </c>
       <c r="AA41" t="n">
-        <v>3.34</v>
+        <v>3.04</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AC41" t="n">
-        <v>7.3</v>
+        <v>6.25</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AE41" t="n">
         <v>1.02</v>
       </c>
       <c r="AF41" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="AG41" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -6996,10 +6996,10 @@
         </is>
       </c>
       <c r="AJ41" t="n">
-        <v>1.44</v>
+        <v>1.08</v>
       </c>
       <c r="AK41" t="n">
-        <v>1.52</v>
+        <v>1.92</v>
       </c>
       <c r="AL41" t="n">
         <v>0</v>
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,64 +7085,64 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>1.73</v>
+        <v>1.97</v>
       </c>
       <c r="O42" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="P42" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="Q42" t="n">
         <v>2.9</v>
       </c>
-      <c r="P42" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>2.48</v>
-      </c>
       <c r="R42" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="S42" t="n">
-        <v>1.69</v>
+        <v>1.6</v>
       </c>
       <c r="T42" t="n">
-        <v>2.04</v>
+        <v>2.13</v>
       </c>
       <c r="U42" t="n">
-        <v>4.2</v>
+        <v>3.88</v>
       </c>
       <c r="V42" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="W42" t="n">
         <v>1.03</v>
       </c>
       <c r="X42" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.03</v>
+        <v>2.38</v>
       </c>
       <c r="AA42" t="n">
-        <v>3.04</v>
+        <v>2.78</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="AC42" t="n">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AE42" t="n">
         <v>1.02</v>
       </c>
       <c r="AF42" t="n">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.38</v>
+        <v>1.57</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7155,10 +7155,10 @@
         </is>
       </c>
       <c r="AJ42" t="n">
-        <v>1.08</v>
+        <v>1.29</v>
       </c>
       <c r="AK42" t="n">
-        <v>1.92</v>
+        <v>1.57</v>
       </c>
       <c r="AL42" t="n">
         <v>0</v>
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,64 +7244,64 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="O43" t="n">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="P43" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.94</v>
+        <v>2.63</v>
       </c>
       <c r="R43" t="n">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="S43" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U43" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="V43" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W43" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X43" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y43" t="n">
         <v>1.64</v>
       </c>
-      <c r="T43" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="U43" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="V43" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="W43" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X43" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>1.6</v>
-      </c>
       <c r="Z43" t="n">
-        <v>2.19</v>
+        <v>2.12</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.78</v>
+        <v>2.92</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="AC43" t="n">
-        <v>5.65</v>
+        <v>6.35</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF43" t="n">
-        <v>2.3</v>
+        <v>2.57</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7314,10 +7314,10 @@
         </is>
       </c>
       <c r="AJ43" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="AK43" t="n">
-        <v>1.59</v>
+        <v>1.82</v>
       </c>
       <c r="AL43" t="n">
         <v>0</v>
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,64 +7403,64 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>2</v>
+        <v>2.62</v>
       </c>
       <c r="O44" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="P44" t="n">
         <v>2.8</v>
       </c>
-      <c r="P44" t="n">
-        <v>3.8</v>
-      </c>
       <c r="Q44" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.83</v>
+        <v>3.1</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AC44" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="AJ44" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK44" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AL44" t="n">
         <v>0</v>
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,43 +7562,43 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="O45" t="n">
-        <v>2.93</v>
+        <v>2.8</v>
       </c>
       <c r="P45" t="n">
-        <v>3.99</v>
+        <v>3.5</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="R45" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="S45" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="T45" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="U45" t="n">
-        <v>3.88</v>
+        <v>3.92</v>
       </c>
       <c r="V45" t="n">
         <v>1.18</v>
       </c>
       <c r="W45" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X45" t="n">
         <v>1.09</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.38</v>
+        <v>2.19</v>
       </c>
       <c r="AA45" t="n">
         <v>2.78</v>
@@ -7607,19 +7607,19 @@
         <v>1.34</v>
       </c>
       <c r="AC45" t="n">
-        <v>6.5</v>
+        <v>5.65</v>
       </c>
       <c r="AD45" t="n">
         <v>1.08</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF45" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7632,10 +7632,10 @@
         </is>
       </c>
       <c r="AJ45" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="AK45" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AL45" t="n">
         <v>0</v>
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,64 +7721,64 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>1.83</v>
+        <v>1.65</v>
       </c>
       <c r="O46" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P46" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" t="n">
+        <v>0</v>
+      </c>
+      <c r="W46" t="n">
+        <v>0</v>
+      </c>
+      <c r="X46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA46" t="n">
         <v>2.87</v>
       </c>
-      <c r="P46" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="R46" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="S46" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="T46" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U46" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="V46" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="W46" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X46" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>2.92</v>
-      </c>
       <c r="AB46" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="AC46" t="n">
-        <v>6.35</v>
+        <v>0</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7791,10 +7791,10 @@
         </is>
       </c>
       <c r="AJ46" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AK46" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AL46" t="n">
         <v>0</v>
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,64 +7880,64 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="O47" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="P47" t="n">
-        <v>5.5</v>
+        <v>3.8</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.87</v>
+        <v>2.83</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -7950,10 +7950,10 @@
         </is>
       </c>
       <c r="AJ47" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK47" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL47" t="n">
         <v>0</v>

--- a/jogos_2026-07-11.xlsx
+++ b/jogos_2026-07-11.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.71</v>
+        <v>2.35</v>
       </c>
       <c r="O3" t="n">
-        <v>3.44</v>
+        <v>3.35</v>
       </c>
       <c r="P3" t="n">
-        <v>2.26</v>
+        <v>2.57</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.37</v>
+        <v>2.88</v>
       </c>
       <c r="R3" t="n">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="S3" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="T3" t="n">
-        <v>3.14</v>
+        <v>2.92</v>
       </c>
       <c r="U3" t="n">
-        <v>2.28</v>
+        <v>2.5</v>
       </c>
       <c r="V3" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="W3" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X3" t="n">
         <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.98</v>
+        <v>3.58</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.62</v>
+        <v>1.74</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.5</v>
+        <v>2.78</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.43</v>
+        <v>1.34</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.32</v>
+        <v>2.17</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.37</v>
+        <v>1.46</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.35</v>
+        <v>2.71</v>
       </c>
       <c r="O4" t="n">
-        <v>3.35</v>
+        <v>3.44</v>
       </c>
       <c r="P4" t="n">
-        <v>2.57</v>
+        <v>2.26</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.88</v>
+        <v>3.37</v>
       </c>
       <c r="R4" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="S4" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="T4" t="n">
-        <v>2.92</v>
+        <v>3.14</v>
       </c>
       <c r="U4" t="n">
-        <v>2.5</v>
+        <v>2.28</v>
       </c>
       <c r="V4" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="W4" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X4" t="n">
         <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.58</v>
+        <v>3.98</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.74</v>
+        <v>1.62</v>
       </c>
       <c r="AB4" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.17</v>
+        <v>2.32</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.46</v>
+        <v>1.37</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.05</v>
+        <v>2.74</v>
       </c>
       <c r="O9" t="n">
-        <v>3.17</v>
+        <v>3.3</v>
       </c>
       <c r="P9" t="n">
-        <v>3.17</v>
+        <v>2.47</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.66</v>
+        <v>1.83</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.87</v>
+        <v>5.5</v>
       </c>
       <c r="O11" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="P11" t="n">
-        <v>3.6</v>
+        <v>1.53</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.52</v>
+        <v>6.5</v>
       </c>
       <c r="R11" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="U11" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AF11" t="n">
         <v>2.2</v>
       </c>
-      <c r="S11" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.79</v>
-      </c>
       <c r="AG11" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.3</v>
+        <v>2.38</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.83</v>
+        <v>1.1</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,80 +2315,80 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="O12" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="P12" t="n">
-        <v>1.53</v>
+        <v>1.28</v>
       </c>
       <c r="Q12" t="n">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="R12" t="n">
-        <v>2.07</v>
+        <v>2.4</v>
       </c>
       <c r="S12" t="n">
-        <v>1.48</v>
+        <v>1.32</v>
       </c>
       <c r="T12" t="n">
-        <v>2.53</v>
+        <v>3.2</v>
       </c>
       <c r="U12" t="n">
-        <v>3.22</v>
+        <v>2.44</v>
       </c>
       <c r="V12" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="W12" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="X12" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="Y12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AD12" t="n">
         <v>1.36</v>
       </c>
-      <c r="Z12" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AE12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ12" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AK12" t="n">
         <v>1.06</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ12" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>1.1</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,65 +2474,65 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>6.2</v>
+        <v>1.87</v>
       </c>
       <c r="O13" t="n">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="P13" t="n">
-        <v>1.28</v>
+        <v>3.6</v>
       </c>
       <c r="Q13" t="n">
-        <v>6.25</v>
+        <v>2.52</v>
       </c>
       <c r="R13" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="S13" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="T13" t="n">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="U13" t="n">
-        <v>2.44</v>
+        <v>2.8</v>
       </c>
       <c r="V13" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="W13" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.78</v>
+        <v>3.25</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AB13" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.74</v>
+        <v>3.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF13" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AG13" t="n">
         <v>1.95</v>
       </c>
-      <c r="AG13" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AH13" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>2.88</v>
+        <v>1.3</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.06</v>
+        <v>1.83</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.74</v>
+        <v>2.05</v>
       </c>
       <c r="O15" t="n">
-        <v>3.3</v>
+        <v>3.17</v>
       </c>
       <c r="P15" t="n">
-        <v>2.47</v>
+        <v>3.17</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.83</v>
+        <v>1.66</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="O18" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="P18" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="R18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA18" t="n">
         <v>1.52</v>
       </c>
-      <c r="O18" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="P18" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>0</v>
-      </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.59</v>
+        <v>2.15</v>
       </c>
       <c r="O19" t="n">
-        <v>4.46</v>
+        <v>3.2</v>
       </c>
       <c r="P19" t="n">
-        <v>5.2</v>
+        <v>3.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.15</v>
+        <v>1.52</v>
       </c>
       <c r="O20" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="P20" t="n">
-        <v>3.1</v>
+        <v>5</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.5</v>
+        <v>1.36</v>
       </c>
       <c r="O21" t="n">
-        <v>3.42</v>
+        <v>4.3</v>
       </c>
       <c r="P21" t="n">
-        <v>2.4</v>
+        <v>7.5</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.36</v>
+        <v>2.5</v>
       </c>
       <c r="O22" t="n">
-        <v>4.3</v>
+        <v>3.42</v>
       </c>
       <c r="P22" t="n">
-        <v>7.5</v>
+        <v>2.4</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,64 +4541,64 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.27</v>
+        <v>2.75</v>
       </c>
       <c r="O26" t="n">
-        <v>5.1</v>
+        <v>3.01</v>
       </c>
       <c r="P26" t="n">
-        <v>6.2</v>
+        <v>2.7</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.76</v>
+        <v>3.3</v>
       </c>
       <c r="R26" t="n">
-        <v>2.68</v>
+        <v>1.9</v>
       </c>
       <c r="S26" t="n">
-        <v>1.28</v>
+        <v>1.48</v>
       </c>
       <c r="T26" t="n">
-        <v>3.25</v>
+        <v>2.47</v>
       </c>
       <c r="U26" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="V26" t="n">
-        <v>1.51</v>
+        <v>1.31</v>
       </c>
       <c r="W26" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="X26" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AE26" t="n">
         <v>1.03</v>
       </c>
-      <c r="Y26" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>5.34</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1.16</v>
-      </c>
       <c r="AF26" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>1.06</v>
+        <v>1.36</v>
       </c>
       <c r="AK26" t="n">
-        <v>3.12</v>
+        <v>1.41</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,64 +4700,64 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>2.75</v>
+        <v>1.27</v>
       </c>
       <c r="O27" t="n">
-        <v>3.01</v>
+        <v>5.1</v>
       </c>
       <c r="P27" t="n">
-        <v>2.7</v>
+        <v>6.2</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.3</v>
+        <v>1.76</v>
       </c>
       <c r="R27" t="n">
-        <v>1.9</v>
+        <v>2.68</v>
       </c>
       <c r="S27" t="n">
-        <v>1.48</v>
+        <v>1.28</v>
       </c>
       <c r="T27" t="n">
-        <v>2.47</v>
+        <v>3.25</v>
       </c>
       <c r="U27" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="V27" t="n">
-        <v>1.31</v>
+        <v>1.51</v>
       </c>
       <c r="W27" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X27" t="n">
         <v>1.03</v>
       </c>
-      <c r="X27" t="n">
-        <v>1.05</v>
-      </c>
       <c r="Y27" t="n">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.75</v>
+        <v>5.34</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.26</v>
+        <v>1.68</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.57</v>
+        <v>2.21</v>
       </c>
       <c r="AC27" t="n">
-        <v>4</v>
+        <v>2.66</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.19</v>
+        <v>1.42</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>1.36</v>
+        <v>1.06</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.41</v>
+        <v>3.12</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,64 +4859,64 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>2.13</v>
+        <v>1.95</v>
       </c>
       <c r="O28" t="n">
-        <v>3.21</v>
+        <v>3.4</v>
       </c>
       <c r="P28" t="n">
-        <v>3.52</v>
+        <v>3.51</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,64 +5018,64 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>2.61</v>
+        <v>2.13</v>
       </c>
       <c r="O29" t="n">
-        <v>2.86</v>
+        <v>3.21</v>
       </c>
       <c r="P29" t="n">
-        <v>3.01</v>
+        <v>3.52</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="AJ29" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,80 +5177,80 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1.95</v>
+        <v>2.61</v>
       </c>
       <c r="O30" t="n">
-        <v>3.4</v>
+        <v>2.86</v>
       </c>
       <c r="P30" t="n">
-        <v>3.51</v>
+        <v>3.01</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.45</v>
+        <v>3.1</v>
       </c>
       <c r="R30" t="n">
-        <v>2.25</v>
+        <v>1.97</v>
       </c>
       <c r="S30" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="T30" t="n">
-        <v>2.87</v>
+        <v>2.75</v>
       </c>
       <c r="U30" t="n">
-        <v>2.63</v>
+        <v>3.2</v>
       </c>
       <c r="V30" t="n">
-        <v>1.47</v>
+        <v>1.3</v>
       </c>
       <c r="W30" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X30" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE30" t="n">
         <v>1.03</v>
       </c>
-      <c r="Y30" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>1.11</v>
-      </c>
       <c r="AF30" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ30" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AK30" t="n">
         <v>1.6</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ30" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>1.82</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,28 +5336,28 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>2.83</v>
+        <v>1.73</v>
       </c>
       <c r="O31" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="P31" t="n">
-        <v>2.13</v>
+        <v>3.6</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.4</v>
+        <v>2.26</v>
       </c>
       <c r="R31" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="S31" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T31" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="U31" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="V31" t="n">
         <v>1.62</v>
@@ -5366,25 +5366,25 @@
         <v>1.12</v>
       </c>
       <c r="X31" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="Z31" t="n">
-        <v>5.42</v>
+        <v>5.3</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.32</v>
+        <v>2.14</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="AE31" t="n">
         <v>1.22</v>
@@ -5393,7 +5393,7 @@
         <v>1.44</v>
       </c>
       <c r="AG31" t="n">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="AJ31" t="n">
-        <v>1.7</v>
+        <v>1.18</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.34</v>
+        <v>1.9</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,28 +5654,28 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1.73</v>
+        <v>2.83</v>
       </c>
       <c r="O33" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="P33" t="n">
-        <v>3.6</v>
+        <v>2.13</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.26</v>
+        <v>3.4</v>
       </c>
       <c r="R33" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="S33" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T33" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="U33" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="V33" t="n">
         <v>1.62</v>
@@ -5684,25 +5684,25 @@
         <v>1.12</v>
       </c>
       <c r="X33" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="Z33" t="n">
-        <v>5.3</v>
+        <v>5.42</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.14</v>
+        <v>2.32</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="AE33" t="n">
         <v>1.22</v>
@@ -5711,7 +5711,7 @@
         <v>1.44</v>
       </c>
       <c r="AG33" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>1.18</v>
+        <v>1.7</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.9</v>
+        <v>1.34</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,64 +6290,64 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.32</v>
+        <v>1.7</v>
       </c>
       <c r="O37" t="n">
-        <v>4.8</v>
+        <v>3.75</v>
       </c>
       <c r="P37" t="n">
-        <v>7.8</v>
+        <v>4.58</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z37" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.61</v>
+        <v>1.74</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.78</v>
+        <v>2.1</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AK37" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,64 +6449,64 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1.7</v>
+        <v>1.32</v>
       </c>
       <c r="O38" t="n">
-        <v>3.75</v>
+        <v>4.8</v>
       </c>
       <c r="P38" t="n">
-        <v>4.58</v>
+        <v>7.8</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z38" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.74</v>
+        <v>1.61</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="AG38" t="n">
-        <v>2.1</v>
+        <v>1.78</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AK38" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6614,7 +6614,7 @@
         <v>2.9</v>
       </c>
       <c r="P39" t="n">
-        <v>2.4</v>
+        <v>2.52</v>
       </c>
       <c r="Q39" t="n">
         <v>3.5</v>
@@ -6623,7 +6623,7 @@
         <v>1.92</v>
       </c>
       <c r="S39" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="T39" t="n">
         <v>2.41</v>
@@ -6638,13 +6638,13 @@
         <v>1.05</v>
       </c>
       <c r="X39" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Y39" t="n">
         <v>1.4</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.7</v>
+        <v>2.89</v>
       </c>
       <c r="AA39" t="n">
         <v>2.25</v>
@@ -6656,16 +6656,16 @@
         <v>4.2</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,64 +6767,64 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>2.3</v>
+        <v>1.65</v>
       </c>
       <c r="O40" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="P40" t="n">
-        <v>3.6</v>
+        <v>5.5</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>3.34</v>
+        <v>2.87</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="AC40" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="AJ40" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,64 +6926,64 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>1.73</v>
+        <v>2.3</v>
       </c>
       <c r="O41" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="P41" t="n">
-        <v>5.25</v>
+        <v>3.6</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.48</v>
+        <v>3.3</v>
       </c>
       <c r="R41" t="n">
-        <v>1.78</v>
+        <v>1.59</v>
       </c>
       <c r="S41" t="n">
-        <v>1.69</v>
+        <v>1.84</v>
       </c>
       <c r="T41" t="n">
-        <v>2.04</v>
+        <v>1.86</v>
       </c>
       <c r="U41" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="V41" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="W41" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X41" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AD41" t="n">
         <v>1.03</v>
-      </c>
-      <c r="X41" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>1.06</v>
       </c>
       <c r="AE41" t="n">
         <v>1.02</v>
       </c>
       <c r="AF41" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="AG41" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -6996,10 +6996,10 @@
         </is>
       </c>
       <c r="AJ41" t="n">
-        <v>1.08</v>
+        <v>1.44</v>
       </c>
       <c r="AK41" t="n">
-        <v>1.92</v>
+        <v>1.52</v>
       </c>
       <c r="AL41" t="n">
         <v>0</v>
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,64 +7244,64 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="O43" t="n">
-        <v>2.87</v>
+        <v>2.8</v>
       </c>
       <c r="P43" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.63</v>
+        <v>2.94</v>
       </c>
       <c r="R43" t="n">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="S43" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="U43" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="V43" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="W43" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X43" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Y43" t="n">
         <v>1.6</v>
       </c>
-      <c r="T43" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U43" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="V43" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="W43" t="n">
+      <c r="Z43" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AE43" t="n">
         <v>1.03</v>
       </c>
-      <c r="X43" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>6.35</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AE43" t="n">
-        <v>1.02</v>
-      </c>
       <c r="AF43" t="n">
-        <v>2.57</v>
+        <v>2.3</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.44</v>
+        <v>1.54</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7314,10 +7314,10 @@
         </is>
       </c>
       <c r="AJ43" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="AK43" t="n">
-        <v>1.82</v>
+        <v>1.59</v>
       </c>
       <c r="AL43" t="n">
         <v>0</v>
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,64 +7403,64 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>2.62</v>
+        <v>2</v>
       </c>
       <c r="O44" t="n">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="P44" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="Q44" t="n">
         <v>2.8</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AA44" t="n">
-        <v>3.1</v>
+        <v>2.83</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="AJ44" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK44" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL44" t="n">
         <v>0</v>
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,64 +7562,64 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>2.1</v>
+        <v>2.62</v>
       </c>
       <c r="O45" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="P45" t="n">
         <v>2.8</v>
       </c>
-      <c r="P45" t="n">
-        <v>3.5</v>
-      </c>
       <c r="Q45" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.78</v>
+        <v>3.1</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AC45" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7632,10 +7632,10 @@
         </is>
       </c>
       <c r="AJ45" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AK45" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AL45" t="n">
         <v>0</v>
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,64 +7721,64 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="O46" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="P46" t="n">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.87</v>
+        <v>3.04</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7791,10 +7791,10 @@
         </is>
       </c>
       <c r="AJ46" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK46" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AL46" t="n">
         <v>0</v>
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,31 +7880,31 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="O47" t="n">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="P47" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.8</v>
+        <v>2.63</v>
       </c>
       <c r="R47" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="S47" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="T47" t="n">
-        <v>2.11</v>
+        <v>2.25</v>
       </c>
       <c r="U47" t="n">
-        <v>4.05</v>
+        <v>3.9</v>
       </c>
       <c r="V47" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="W47" t="n">
         <v>1.03</v>
@@ -7913,31 +7913,31 @@
         <v>1.08</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="Z47" t="n">
-        <v>2.19</v>
+        <v>2.12</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.83</v>
+        <v>2.92</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AC47" t="n">
-        <v>6.05</v>
+        <v>6.35</v>
       </c>
       <c r="AD47" t="n">
         <v>1.06</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF47" t="n">
-        <v>2.38</v>
+        <v>2.57</v>
       </c>
       <c r="AG47" t="n">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -7950,10 +7950,10 @@
         </is>
       </c>
       <c r="AJ47" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AK47" t="n">
-        <v>1.68</v>
+        <v>1.82</v>
       </c>
       <c r="AL47" t="n">
         <v>0</v>
@@ -8035,7 +8035,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N48" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>3.8</v>
+        <v>4.08</v>
       </c>
       <c r="O49" t="n">
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="P49" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="Q49" t="n">
         <v>4.66</v>
@@ -8216,13 +8216,13 @@
         <v>1.38</v>
       </c>
       <c r="T49" t="n">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="U49" t="n">
-        <v>2.78</v>
+        <v>2.91</v>
       </c>
       <c r="V49" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W49" t="n">
         <v>1.06</v>
@@ -8234,28 +8234,28 @@
         <v>1.29</v>
       </c>
       <c r="Z49" t="n">
-        <v>3.25</v>
+        <v>3.71</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AB49" t="n">
         <v>1.85</v>
       </c>
       <c r="AC49" t="n">
-        <v>3.3</v>
+        <v>3.71</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AE49" t="n">
         <v>1.06</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG49" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8516,80 +8516,80 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>1.95</v>
+        <v>2.33</v>
       </c>
       <c r="O51" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="P51" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="Q51" t="n">
-        <v>2.69</v>
+        <v>3.08</v>
       </c>
       <c r="R51" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="S51" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U51" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V51" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W51" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X51" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ51" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AK51" t="n">
         <v>1.53</v>
-      </c>
-      <c r="T51" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="U51" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="V51" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="W51" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X51" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>6.16</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AE51" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AF51" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AG51" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ51" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AK51" t="n">
-        <v>1.72</v>
       </c>
       <c r="AL51" t="n">
         <v>0</v>

--- a/jogos_2026-07-11.xlsx
+++ b/jogos_2026-07-11.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.45</v>
+        <v>2.71</v>
       </c>
       <c r="O2" t="n">
-        <v>3.6</v>
+        <v>3.44</v>
       </c>
       <c r="P2" t="n">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.12</v>
+        <v>3.37</v>
       </c>
       <c r="R2" t="n">
-        <v>2.18</v>
+        <v>2.21</v>
       </c>
       <c r="S2" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T2" t="n">
         <v>3.14</v>
       </c>
       <c r="U2" t="n">
-        <v>2.44</v>
+        <v>2.28</v>
       </c>
       <c r="V2" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="W2" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X2" t="n">
         <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.05</v>
+        <v>3.98</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF2" t="n">
         <v>1.53</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.29</v>
+        <v>2.32</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>1.22</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.71</v>
+        <v>2.45</v>
       </c>
       <c r="O4" t="n">
-        <v>3.44</v>
+        <v>3.6</v>
       </c>
       <c r="P4" t="n">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.37</v>
+        <v>3.12</v>
       </c>
       <c r="R4" t="n">
-        <v>2.21</v>
+        <v>2.18</v>
       </c>
       <c r="S4" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T4" t="n">
         <v>3.14</v>
       </c>
       <c r="U4" t="n">
-        <v>2.28</v>
+        <v>2.44</v>
       </c>
       <c r="V4" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="W4" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X4" t="n">
         <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.98</v>
+        <v>4.05</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF4" t="n">
         <v>1.53</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>1.22</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>APIA Leichhardt Tigers</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sydney II</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.37</v>
+        <v>1.64</v>
       </c>
       <c r="O5" t="n">
-        <v>4.55</v>
+        <v>3.74</v>
       </c>
       <c r="P5" t="n">
-        <v>6.5</v>
+        <v>4.47</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.84</v>
+        <v>2.2</v>
       </c>
       <c r="R5" t="n">
-        <v>2.51</v>
+        <v>2.22</v>
       </c>
       <c r="S5" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="T5" t="n">
-        <v>3.68</v>
+        <v>3.04</v>
       </c>
       <c r="U5" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB5" t="n">
         <v>2.05</v>
       </c>
-      <c r="V5" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="AA5" t="n">
+      <c r="AC5" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AD5" t="n">
         <v>1.38</v>
       </c>
-      <c r="AB5" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.71</v>
-      </c>
       <c r="AE5" t="n">
-        <v>1.27</v>
+        <v>1.11</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.65</v>
+        <v>2.03</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>APIA Leichhardt Tigers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Sydney II</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.64</v>
+        <v>1.37</v>
       </c>
       <c r="O6" t="n">
-        <v>3.74</v>
+        <v>4.55</v>
       </c>
       <c r="P6" t="n">
-        <v>4.47</v>
+        <v>6.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.2</v>
+        <v>1.84</v>
       </c>
       <c r="R6" t="n">
-        <v>2.22</v>
+        <v>2.51</v>
       </c>
       <c r="S6" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="T6" t="n">
-        <v>3.04</v>
+        <v>3.68</v>
       </c>
       <c r="U6" t="n">
-        <v>2.44</v>
+        <v>2.05</v>
       </c>
       <c r="V6" t="n">
-        <v>1.45</v>
+        <v>1.67</v>
       </c>
       <c r="W6" t="n">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.92</v>
+        <v>5.55</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.67</v>
+        <v>1.38</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.05</v>
+        <v>2.62</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.62</v>
+        <v>2</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.38</v>
+        <v>1.71</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.11</v>
+        <v>1.27</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.07</v>
+        <v>2.23</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.03</v>
+        <v>2.65</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.74</v>
+        <v>2.23</v>
       </c>
       <c r="O9" t="n">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="P9" t="n">
-        <v>2.47</v>
+        <v>2.97</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.1</v>
+        <v>2.55</v>
       </c>
       <c r="R9" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="S9" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="T9" t="n">
-        <v>2.96</v>
+        <v>2.62</v>
       </c>
       <c r="U9" t="n">
-        <v>2.88</v>
+        <v>2.91</v>
       </c>
       <c r="V9" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W9" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X9" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.4</v>
+        <v>3.21</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.18</v>
+        <v>3.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="AG9" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.48</v>
+        <v>1.26</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,80 +1997,80 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.05</v>
+        <v>6.2</v>
       </c>
       <c r="O10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="T10" t="n">
         <v>3.2</v>
       </c>
-      <c r="P10" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="R10" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.75</v>
-      </c>
       <c r="U10" t="n">
-        <v>3</v>
+        <v>2.44</v>
       </c>
       <c r="V10" t="n">
-        <v>1.32</v>
+        <v>1.5</v>
       </c>
       <c r="W10" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="X10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ10" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AK10" t="n">
         <v>1.06</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>1.77</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,80 +2156,80 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>5.5</v>
+        <v>1.87</v>
       </c>
       <c r="O11" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC11" t="n">
         <v>3.5</v>
       </c>
-      <c r="P11" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="R11" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="U11" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="V11" t="n">
+      <c r="AD11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ11" t="n">
         <v>1.3</v>
       </c>
-      <c r="W11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ11" t="n">
-        <v>2.38</v>
-      </c>
       <c r="AK11" t="n">
-        <v>1.1</v>
+        <v>1.83</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,80 +2315,80 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="O12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC12" t="n">
         <v>4.2</v>
       </c>
-      <c r="P12" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="R12" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="T12" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U12" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y12" t="n">
+      <c r="AD12" t="n">
         <v>1.22</v>
       </c>
-      <c r="Z12" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AE12" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ12" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AK12" t="n">
         <v>1.1</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ12" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>1.06</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,65 +2474,65 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.87</v>
+        <v>2.74</v>
       </c>
       <c r="O13" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P13" t="n">
-        <v>3.6</v>
+        <v>2.47</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.52</v>
+        <v>3.1</v>
       </c>
       <c r="R13" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V13" t="n">
         <v>1.36</v>
       </c>
-      <c r="T13" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.4</v>
-      </c>
       <c r="W13" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="AA13" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG13" t="n">
         <v>2</v>
       </c>
-      <c r="AB13" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AH13" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.83</v>
+        <v>1.48</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.23</v>
+        <v>2.05</v>
       </c>
       <c r="O14" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="P14" t="n">
-        <v>2.97</v>
+        <v>3.17</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2795,61 +2795,61 @@
         <v>2.05</v>
       </c>
       <c r="O15" t="n">
-        <v>3.17</v>
+        <v>3.2</v>
       </c>
       <c r="P15" t="n">
-        <v>3.17</v>
+        <v>3.35</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="R23" t="n">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="S23" t="n">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="T23" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="U23" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AB23" t="n">
         <v>2.01</v>
       </c>
-      <c r="V23" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>6.26</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>3.3</v>
-      </c>
       <c r="AC23" t="n">
-        <v>2.01</v>
+        <v>3</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.82</v>
+        <v>1.39</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.3</v>
+        <v>1.11</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.36</v>
+        <v>1.61</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.98</v>
+        <v>2.18</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="R24" t="n">
-        <v>2.25</v>
+        <v>2.36</v>
       </c>
       <c r="S24" t="n">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="T24" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="U24" t="n">
-        <v>2.64</v>
+        <v>2.01</v>
       </c>
       <c r="V24" t="n">
-        <v>1.44</v>
+        <v>1.74</v>
       </c>
       <c r="W24" t="n">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="X24" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.23</v>
+        <v>1.06</v>
       </c>
       <c r="Z24" t="n">
-        <v>4.54</v>
+        <v>6.26</v>
       </c>
       <c r="AA24" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AD24" t="n">
         <v>1.82</v>
       </c>
-      <c r="AB24" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.39</v>
-      </c>
       <c r="AE24" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.61</v>
+        <v>1.36</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.18</v>
+        <v>2.98</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,80 +4859,80 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>1.95</v>
+        <v>2.61</v>
       </c>
       <c r="O28" t="n">
-        <v>3.4</v>
+        <v>2.86</v>
       </c>
       <c r="P28" t="n">
-        <v>3.51</v>
+        <v>3.01</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.45</v>
+        <v>3.1</v>
       </c>
       <c r="R28" t="n">
-        <v>2.25</v>
+        <v>1.97</v>
       </c>
       <c r="S28" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="T28" t="n">
-        <v>2.87</v>
+        <v>2.75</v>
       </c>
       <c r="U28" t="n">
-        <v>2.63</v>
+        <v>3.2</v>
       </c>
       <c r="V28" t="n">
-        <v>1.47</v>
+        <v>1.3</v>
       </c>
       <c r="W28" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X28" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE28" t="n">
         <v>1.03</v>
       </c>
-      <c r="Y28" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1.11</v>
-      </c>
       <c r="AF28" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ28" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AK28" t="n">
         <v>1.6</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ28" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>1.82</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,64 +5177,64 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>2.61</v>
+        <v>1.95</v>
       </c>
       <c r="O30" t="n">
-        <v>2.86</v>
+        <v>3.4</v>
       </c>
       <c r="P30" t="n">
-        <v>3.01</v>
+        <v>3.51</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.1</v>
+        <v>2.45</v>
       </c>
       <c r="R30" t="n">
-        <v>1.97</v>
+        <v>2.25</v>
       </c>
       <c r="S30" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="T30" t="n">
-        <v>2.75</v>
+        <v>2.87</v>
       </c>
       <c r="U30" t="n">
-        <v>3.2</v>
+        <v>2.63</v>
       </c>
       <c r="V30" t="n">
-        <v>1.3</v>
+        <v>1.47</v>
       </c>
       <c r="W30" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X30" t="n">
         <v>1.03</v>
       </c>
-      <c r="X30" t="n">
-        <v>1.04</v>
-      </c>
       <c r="Y30" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.05</v>
+        <v>3.95</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.24</v>
+        <v>1.74</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.62</v>
+        <v>2.05</v>
       </c>
       <c r="AC30" t="n">
-        <v>3.9</v>
+        <v>2.88</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.83</v>
+        <v>2.15</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.6</v>
+        <v>1.82</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,28 +5336,28 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1.73</v>
+        <v>2.83</v>
       </c>
       <c r="O31" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="P31" t="n">
-        <v>3.6</v>
+        <v>2.13</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.26</v>
+        <v>3.4</v>
       </c>
       <c r="R31" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="S31" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T31" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="U31" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="V31" t="n">
         <v>1.62</v>
@@ -5366,25 +5366,25 @@
         <v>1.12</v>
       </c>
       <c r="X31" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="Z31" t="n">
-        <v>5.3</v>
+        <v>5.42</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.14</v>
+        <v>2.32</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="AE31" t="n">
         <v>1.22</v>
@@ -5393,7 +5393,7 @@
         <v>1.44</v>
       </c>
       <c r="AG31" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="AJ31" t="n">
-        <v>1.18</v>
+        <v>1.7</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.9</v>
+        <v>1.34</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,64 +5495,64 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>1.89</v>
+        <v>1.73</v>
       </c>
       <c r="O32" t="n">
-        <v>2.95</v>
+        <v>3.8</v>
       </c>
       <c r="P32" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK32" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,64 +5654,64 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>2.83</v>
+        <v>1.89</v>
       </c>
       <c r="O33" t="n">
-        <v>3.75</v>
+        <v>2.95</v>
       </c>
       <c r="P33" t="n">
-        <v>2.13</v>
+        <v>4.1</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>5.42</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,64 +6131,64 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="O36" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="P36" t="n">
-        <v>4.55</v>
+        <v>4.58</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.05</v>
+        <v>2.26</v>
       </c>
       <c r="R36" t="n">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="S36" t="n">
         <v>1.33</v>
       </c>
       <c r="T36" t="n">
-        <v>3.3</v>
+        <v>3.04</v>
       </c>
       <c r="U36" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="V36" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W36" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X36" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y36" t="n">
         <v>1.2</v>
       </c>
       <c r="Z36" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="AB36" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC36" t="n">
         <v>2.8</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AG36" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AK36" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,64 +6290,64 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.7</v>
+        <v>1.32</v>
       </c>
       <c r="O37" t="n">
-        <v>3.75</v>
+        <v>4.8</v>
       </c>
       <c r="P37" t="n">
-        <v>4.58</v>
+        <v>7.8</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z37" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.74</v>
+        <v>1.61</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="AG37" t="n">
-        <v>2.1</v>
+        <v>1.78</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AK37" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,64 +6449,64 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1.32</v>
+        <v>1.67</v>
       </c>
       <c r="O38" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="P38" t="n">
-        <v>7.8</v>
+        <v>4.55</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z38" t="n">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="AE38" t="n">
         <v>1.15</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.78</v>
+        <v>2.05</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AK38" t="n">
-        <v>2.7</v>
+        <v>2.15</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,64 +6767,64 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1.65</v>
+        <v>1.97</v>
       </c>
       <c r="O40" t="n">
-        <v>3.1</v>
+        <v>2.93</v>
       </c>
       <c r="P40" t="n">
-        <v>5.5</v>
+        <v>3.99</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.87</v>
+        <v>2.78</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="AJ40" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK40" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,64 +6926,64 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>2.3</v>
+        <v>1.65</v>
       </c>
       <c r="O41" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="P41" t="n">
-        <v>3.6</v>
+        <v>5.5</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>3.34</v>
+        <v>2.87</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="AC41" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AG41" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -6996,10 +6996,10 @@
         </is>
       </c>
       <c r="AJ41" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AK41" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AL41" t="n">
         <v>0</v>
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,64 +7085,64 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>1.97</v>
+        <v>2.62</v>
       </c>
       <c r="O42" t="n">
-        <v>2.93</v>
+        <v>2.62</v>
       </c>
       <c r="P42" t="n">
-        <v>3.99</v>
+        <v>2.8</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.78</v>
+        <v>3.1</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AC42" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7155,10 +7155,10 @@
         </is>
       </c>
       <c r="AJ42" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK42" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AL42" t="n">
         <v>0</v>
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,64 +7244,64 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="O43" t="n">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="P43" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.94</v>
+        <v>2.63</v>
       </c>
       <c r="R43" t="n">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="S43" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U43" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="V43" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W43" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X43" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y43" t="n">
         <v>1.64</v>
       </c>
-      <c r="T43" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="U43" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="V43" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="W43" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X43" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>1.6</v>
-      </c>
       <c r="Z43" t="n">
-        <v>2.19</v>
+        <v>2.12</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.78</v>
+        <v>2.92</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="AC43" t="n">
-        <v>5.65</v>
+        <v>6.35</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF43" t="n">
-        <v>2.3</v>
+        <v>2.57</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7314,10 +7314,10 @@
         </is>
       </c>
       <c r="AJ43" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="AK43" t="n">
-        <v>1.59</v>
+        <v>1.82</v>
       </c>
       <c r="AL43" t="n">
         <v>0</v>
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,28 +7403,28 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="O44" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="P44" t="n">
-        <v>3.8</v>
+        <v>5.25</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.8</v>
+        <v>2.48</v>
       </c>
       <c r="R44" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="S44" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="T44" t="n">
-        <v>2.11</v>
+        <v>2.04</v>
       </c>
       <c r="U44" t="n">
-        <v>4.05</v>
+        <v>4.2</v>
       </c>
       <c r="V44" t="n">
         <v>1.16</v>
@@ -7433,34 +7433,34 @@
         <v>1.03</v>
       </c>
       <c r="X44" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.19</v>
+        <v>2.03</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.83</v>
+        <v>3.04</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AC44" t="n">
-        <v>6.05</v>
+        <v>6.25</v>
       </c>
       <c r="AD44" t="n">
         <v>1.06</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF44" t="n">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="AJ44" t="n">
-        <v>1.33</v>
+        <v>1.08</v>
       </c>
       <c r="AK44" t="n">
-        <v>1.68</v>
+        <v>1.92</v>
       </c>
       <c r="AL44" t="n">
         <v>0</v>
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,64 +7562,64 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>2.62</v>
+        <v>2</v>
       </c>
       <c r="O45" t="n">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="P45" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="Q45" t="n">
         <v>2.8</v>
       </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AA45" t="n">
-        <v>3.1</v>
+        <v>2.83</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7632,10 +7632,10 @@
         </is>
       </c>
       <c r="AJ45" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK45" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL45" t="n">
         <v>0</v>
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,64 +7721,64 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>1.73</v>
+        <v>2.3</v>
       </c>
       <c r="O46" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="P46" t="n">
-        <v>5.25</v>
+        <v>3.6</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.48</v>
+        <v>3.3</v>
       </c>
       <c r="R46" t="n">
-        <v>1.78</v>
+        <v>1.59</v>
       </c>
       <c r="S46" t="n">
-        <v>1.69</v>
+        <v>1.84</v>
       </c>
       <c r="T46" t="n">
-        <v>2.04</v>
+        <v>1.86</v>
       </c>
       <c r="U46" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="V46" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="W46" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X46" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AD46" t="n">
         <v>1.03</v>
-      </c>
-      <c r="X46" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>1.06</v>
       </c>
       <c r="AE46" t="n">
         <v>1.02</v>
       </c>
       <c r="AF46" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7791,10 +7791,10 @@
         </is>
       </c>
       <c r="AJ46" t="n">
-        <v>1.08</v>
+        <v>1.44</v>
       </c>
       <c r="AK46" t="n">
-        <v>1.92</v>
+        <v>1.52</v>
       </c>
       <c r="AL46" t="n">
         <v>0</v>
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,64 +7880,64 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="O47" t="n">
-        <v>2.87</v>
+        <v>2.8</v>
       </c>
       <c r="P47" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.63</v>
+        <v>2.94</v>
       </c>
       <c r="R47" t="n">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="S47" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="U47" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="V47" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="W47" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X47" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Y47" t="n">
         <v>1.6</v>
       </c>
-      <c r="T47" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U47" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="V47" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="W47" t="n">
+      <c r="Z47" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AE47" t="n">
         <v>1.03</v>
       </c>
-      <c r="X47" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>6.35</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AE47" t="n">
-        <v>1.02</v>
-      </c>
       <c r="AF47" t="n">
-        <v>2.57</v>
+        <v>2.3</v>
       </c>
       <c r="AG47" t="n">
-        <v>1.44</v>
+        <v>1.54</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -7950,10 +7950,10 @@
         </is>
       </c>
       <c r="AJ47" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="AK47" t="n">
-        <v>1.82</v>
+        <v>1.59</v>
       </c>
       <c r="AL47" t="n">
         <v>0</v>

--- a/jogos_2026-07-11.xlsx
+++ b/jogos_2026-07-11.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,19 +725,19 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.71</v>
+        <v>2.45</v>
       </c>
       <c r="O2" t="n">
-        <v>3.44</v>
+        <v>3.6</v>
       </c>
       <c r="P2" t="n">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.37</v>
+        <v>2.97</v>
       </c>
       <c r="R2" t="n">
-        <v>2.21</v>
+        <v>2.18</v>
       </c>
       <c r="S2" t="n">
         <v>1.29</v>
@@ -746,43 +746,43 @@
         <v>3.14</v>
       </c>
       <c r="U2" t="n">
-        <v>2.28</v>
+        <v>2.44</v>
       </c>
       <c r="V2" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="W2" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X2" t="n">
         <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.98</v>
+        <v>4.05</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF2" t="n">
         <v>1.53</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>1.22</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.35</v>
+        <v>2.71</v>
       </c>
       <c r="O3" t="n">
-        <v>3.35</v>
+        <v>3.44</v>
       </c>
       <c r="P3" t="n">
-        <v>2.57</v>
+        <v>2.26</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.88</v>
+        <v>3.37</v>
       </c>
       <c r="R3" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="S3" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="T3" t="n">
-        <v>2.92</v>
+        <v>3.12</v>
       </c>
       <c r="U3" t="n">
-        <v>2.5</v>
+        <v>2.28</v>
       </c>
       <c r="V3" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="W3" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X3" t="n">
         <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.58</v>
+        <v>3.98</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.74</v>
+        <v>1.62</v>
       </c>
       <c r="AB3" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.78</v>
+        <v>2.52</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.17</v>
+        <v>2.32</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.46</v>
+        <v>1.37</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,31 +1043,31 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="O4" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="P4" t="n">
-        <v>2.4</v>
+        <v>2.57</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.12</v>
+        <v>2.7</v>
       </c>
       <c r="R4" t="n">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="S4" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="T4" t="n">
-        <v>3.14</v>
+        <v>2.92</v>
       </c>
       <c r="U4" t="n">
-        <v>2.44</v>
+        <v>2.63</v>
       </c>
       <c r="V4" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W4" t="n">
         <v>1.07</v>
@@ -1076,31 +1076,31 @@
         <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.05</v>
+        <v>3.58</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.62</v>
+        <v>2.78</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.29</v>
+        <v>2.17</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1214,13 +1214,13 @@
         <v>2.2</v>
       </c>
       <c r="R5" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="S5" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T5" t="n">
-        <v>3.04</v>
+        <v>3.25</v>
       </c>
       <c r="U5" t="n">
         <v>2.44</v>
@@ -1229,7 +1229,7 @@
         <v>1.45</v>
       </c>
       <c r="W5" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="X5" t="n">
         <v>1.01</v>
@@ -1238,7 +1238,7 @@
         <v>1.18</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.92</v>
+        <v>3.95</v>
       </c>
       <c r="AA5" t="n">
         <v>1.67</v>
@@ -1250,10 +1250,10 @@
         <v>2.62</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF5" t="n">
         <v>1.65</v>
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="O6" t="n">
-        <v>4.55</v>
+        <v>4.2</v>
       </c>
       <c r="P6" t="n">
-        <v>6.5</v>
+        <v>5.7</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.84</v>
+        <v>1.96</v>
       </c>
       <c r="R6" t="n">
-        <v>2.51</v>
+        <v>2.39</v>
       </c>
       <c r="S6" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T6" t="n">
-        <v>3.68</v>
+        <v>3.48</v>
       </c>
       <c r="U6" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="V6" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="W6" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X6" t="n">
         <v>1</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.55</v>
+        <v>4.9</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.62</v>
+        <v>2.49</v>
       </c>
       <c r="AC6" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.23</v>
+        <v>2.17</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.65</v>
+        <v>2.43</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.23</v>
+        <v>7.49</v>
       </c>
       <c r="O9" t="n">
-        <v>3.18</v>
+        <v>4.55</v>
       </c>
       <c r="P9" t="n">
-        <v>2.97</v>
+        <v>1.28</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.55</v>
+        <v>6.25</v>
       </c>
       <c r="R9" t="n">
-        <v>2.14</v>
+        <v>2.4</v>
       </c>
       <c r="S9" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="T9" t="n">
-        <v>2.62</v>
+        <v>3.2</v>
       </c>
       <c r="U9" t="n">
-        <v>2.91</v>
+        <v>2.44</v>
       </c>
       <c r="V9" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="W9" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.21</v>
+        <v>3.82</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.04</v>
+        <v>1.75</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.71</v>
+        <v>1.97</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.79</v>
+        <v>1.95</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.26</v>
+        <v>2.88</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.57</v>
+        <v>1.06</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>6.2</v>
+        <v>2.23</v>
       </c>
       <c r="O10" t="n">
-        <v>4.2</v>
+        <v>3.18</v>
       </c>
       <c r="P10" t="n">
-        <v>1.28</v>
+        <v>2.97</v>
       </c>
       <c r="Q10" t="n">
-        <v>6.25</v>
+        <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>2.4</v>
+        <v>1.98</v>
       </c>
       <c r="S10" t="n">
-        <v>1.32</v>
+        <v>1.43</v>
       </c>
       <c r="T10" t="n">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="U10" t="n">
-        <v>2.44</v>
+        <v>2.91</v>
       </c>
       <c r="V10" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="W10" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="X10" t="n">
         <v>1.04</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.78</v>
+        <v>3.04</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.75</v>
+        <v>1.99</v>
       </c>
       <c r="AB10" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.74</v>
+        <v>3.35</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.95</v>
+        <v>1.77</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>2.88</v>
+        <v>1.3</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.06</v>
+        <v>1.54</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.87</v>
+        <v>5.3</v>
       </c>
       <c r="O11" t="n">
-        <v>3.25</v>
+        <v>3.72</v>
       </c>
       <c r="P11" t="n">
-        <v>3.6</v>
+        <v>1.55</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.52</v>
+        <v>6.5</v>
       </c>
       <c r="R11" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AA11" t="n">
         <v>2.2</v>
       </c>
-      <c r="S11" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>2</v>
-      </c>
       <c r="AB11" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.5</v>
+        <v>4.05</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.79</v>
+        <v>2.2</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.83</v>
+        <v>1.1</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,80 +2315,80 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>5.5</v>
+        <v>2.74</v>
       </c>
       <c r="O12" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P12" t="n">
-        <v>1.53</v>
+        <v>2.47</v>
       </c>
       <c r="Q12" t="n">
-        <v>6.5</v>
+        <v>3.2</v>
       </c>
       <c r="R12" t="n">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="S12" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ12" t="n">
         <v>1.48</v>
       </c>
-      <c r="T12" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="U12" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ12" t="n">
-        <v>2.38</v>
-      </c>
       <c r="AK12" t="n">
-        <v>1.1</v>
+        <v>1.48</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.74</v>
+        <v>2.05</v>
       </c>
       <c r="O13" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P13" t="n">
-        <v>2.47</v>
+        <v>3.17</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.83</v>
+        <v>1.66</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="O14" t="n">
-        <v>3.17</v>
+        <v>3.25</v>
       </c>
       <c r="P14" t="n">
-        <v>3.17</v>
+        <v>3.6</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2807,7 +2807,7 @@
         <v>2.14</v>
       </c>
       <c r="S15" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="T15" t="n">
         <v>2.75</v>
@@ -2825,7 +2825,7 @@
         <v>1.06</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Z15" t="n">
         <v>3</v>
@@ -2840,10 +2840,10 @@
         <v>3.45</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF15" t="n">
         <v>1.87</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>3.18</v>
+        <v>1.59</v>
       </c>
       <c r="O16" t="n">
-        <v>3.48</v>
+        <v>4.46</v>
       </c>
       <c r="P16" t="n">
-        <v>2.25</v>
+        <v>5.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.4</v>
+        <v>1.95</v>
       </c>
       <c r="R16" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="S16" t="n">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="T16" t="n">
-        <v>3.3</v>
+        <v>3.68</v>
       </c>
       <c r="U16" t="n">
-        <v>2.5</v>
+        <v>2.02</v>
       </c>
       <c r="V16" t="n">
-        <v>1.44</v>
+        <v>1.68</v>
       </c>
       <c r="W16" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="X16" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.9</v>
+        <v>5.4</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.73</v>
+        <v>1.48</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.09</v>
+        <v>2.7</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.8</v>
+        <v>2.12</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.36</v>
+        <v>1.68</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.11</v>
+        <v>1.28</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.3</v>
+        <v>1.05</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.36</v>
+        <v>2.4</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.59</v>
+        <v>1.52</v>
       </c>
       <c r="O18" t="n">
-        <v>4.46</v>
+        <v>4.2</v>
       </c>
       <c r="P18" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.36</v>
+        <v>2.5</v>
       </c>
       <c r="O21" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="P21" t="n">
-        <v>7.5</v>
+        <v>2.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.5</v>
+        <v>1.36</v>
       </c>
       <c r="O22" t="n">
-        <v>3.42</v>
+        <v>4.3</v>
       </c>
       <c r="P22" t="n">
-        <v>2.4</v>
+        <v>7.5</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4073,7 +4073,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="R23" t="n">
         <v>2.25</v>
@@ -4097,7 +4097,7 @@
         <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="Z23" t="n">
         <v>4.54</v>
@@ -4109,13 +4109,13 @@
         <v>2.01</v>
       </c>
       <c r="AC23" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AF23" t="n">
         <v>1.61</v>
@@ -4223,19 +4223,19 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.16</v>
+        <v>2.5</v>
       </c>
       <c r="O24" t="n">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="P24" t="n">
         <v>2.45</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.85</v>
+        <v>2.81</v>
       </c>
       <c r="R24" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="S24" t="n">
         <v>1.2</v>
@@ -4244,13 +4244,13 @@
         <v>4</v>
       </c>
       <c r="U24" t="n">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="V24" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="W24" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="X24" t="n">
         <v>1.02</v>
@@ -4259,22 +4259,22 @@
         <v>1.06</v>
       </c>
       <c r="Z24" t="n">
-        <v>6.26</v>
+        <v>11.4</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AB24" t="n">
-        <v>3.3</v>
+        <v>2.74</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AF24" t="n">
         <v>1.36</v>
@@ -4296,7 +4296,7 @@
         <v>1.26</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4385,19 +4385,19 @@
         <v>2.52</v>
       </c>
       <c r="O25" t="n">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="P25" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="Q25" t="n">
         <v>3.3</v>
       </c>
       <c r="R25" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S25" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T25" t="n">
         <v>3</v>
@@ -4421,7 +4421,7 @@
         <v>3.8</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AB25" t="n">
         <v>2</v>
@@ -4430,7 +4430,7 @@
         <v>2.88</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE25" t="n">
         <v>1.13</v>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>1.5</v>
+        <v>1.26</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4553,13 +4553,13 @@
         <v>3.3</v>
       </c>
       <c r="R26" t="n">
-        <v>1.9</v>
+        <v>2.08</v>
       </c>
       <c r="S26" t="n">
         <v>1.48</v>
       </c>
       <c r="T26" t="n">
-        <v>2.47</v>
+        <v>2.63</v>
       </c>
       <c r="U26" t="n">
         <v>3.1</v>
@@ -4574,22 +4574,22 @@
         <v>1.05</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="AA26" t="n">
         <v>2.26</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AC26" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AE26" t="n">
         <v>1.03</v>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AK26" t="n">
         <v>1.41</v>
@@ -4706,7 +4706,7 @@
         <v>5.1</v>
       </c>
       <c r="P27" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="Q27" t="n">
         <v>1.76</v>
@@ -4721,7 +4721,7 @@
         <v>3.25</v>
       </c>
       <c r="U27" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="V27" t="n">
         <v>1.51</v>
@@ -4733,28 +4733,28 @@
         <v>1.03</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="Z27" t="n">
-        <v>5.34</v>
+        <v>4.33</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.66</v>
+        <v>2.63</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AG27" t="n">
         <v>1.85</v>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="AK27" t="n">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,64 +4859,64 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>2.61</v>
+        <v>1.95</v>
       </c>
       <c r="O28" t="n">
-        <v>2.86</v>
+        <v>3.4</v>
       </c>
       <c r="P28" t="n">
-        <v>3.01</v>
+        <v>3.3</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="R28" t="n">
-        <v>1.97</v>
+        <v>2.25</v>
       </c>
       <c r="S28" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="T28" t="n">
-        <v>2.75</v>
+        <v>3.15</v>
       </c>
       <c r="U28" t="n">
-        <v>3.2</v>
+        <v>2.63</v>
       </c>
       <c r="V28" t="n">
-        <v>1.3</v>
+        <v>1.47</v>
       </c>
       <c r="W28" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="X28" t="n">
         <v>1.04</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.05</v>
+        <v>3.94</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.24</v>
+        <v>1.75</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.62</v>
+        <v>2.04</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.9</v>
+        <v>2.88</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.83</v>
+        <v>2.15</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>1.3</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.6</v>
+        <v>1.82</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -5021,10 +5021,10 @@
         <v>2.13</v>
       </c>
       <c r="O29" t="n">
-        <v>3.21</v>
+        <v>3.1</v>
       </c>
       <c r="P29" t="n">
-        <v>3.52</v>
+        <v>3.2</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,80 +5177,80 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1.95</v>
+        <v>2.61</v>
       </c>
       <c r="O30" t="n">
-        <v>3.4</v>
+        <v>2.86</v>
       </c>
       <c r="P30" t="n">
-        <v>3.51</v>
+        <v>3.01</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.45</v>
+        <v>3.1</v>
       </c>
       <c r="R30" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="S30" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="T30" t="n">
-        <v>2.87</v>
+        <v>2.75</v>
       </c>
       <c r="U30" t="n">
-        <v>2.63</v>
+        <v>3.2</v>
       </c>
       <c r="V30" t="n">
-        <v>1.47</v>
+        <v>1.3</v>
       </c>
       <c r="W30" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X30" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE30" t="n">
         <v>1.03</v>
       </c>
-      <c r="Y30" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>1.11</v>
-      </c>
       <c r="AF30" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ30" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AK30" t="n">
         <v>1.6</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ30" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>1.82</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>2.83</v>
+        <v>2.9</v>
       </c>
       <c r="O31" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="P31" t="n">
-        <v>2.13</v>
+        <v>2.19</v>
       </c>
       <c r="Q31" t="n">
         <v>3.4</v>
@@ -5351,10 +5351,10 @@
         <v>2.45</v>
       </c>
       <c r="S31" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="T31" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="U31" t="n">
         <v>2.2</v>
@@ -5363,13 +5363,13 @@
         <v>1.62</v>
       </c>
       <c r="W31" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="X31" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="Z31" t="n">
         <v>5.42</v>
@@ -5381,19 +5381,19 @@
         <v>2.4</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AF31" t="n">
         <v>1.44</v>
       </c>
       <c r="AG31" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5409,7 +5409,7 @@
         <v>1.7</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,64 +5495,64 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>1.73</v>
+        <v>1.89</v>
       </c>
       <c r="O32" t="n">
-        <v>3.8</v>
+        <v>2.95</v>
       </c>
       <c r="P32" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,64 +5654,64 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1.89</v>
+        <v>1.74</v>
       </c>
       <c r="O33" t="n">
-        <v>2.95</v>
+        <v>3.78</v>
       </c>
       <c r="P33" t="n">
-        <v>4.1</v>
+        <v>3.84</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -5825,7 +5825,7 @@
         <v>7.3</v>
       </c>
       <c r="R34" t="n">
-        <v>2.16</v>
+        <v>2.32</v>
       </c>
       <c r="S34" t="n">
         <v>1.33</v>
@@ -5843,7 +5843,7 @@
         <v>1.08</v>
       </c>
       <c r="X34" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y34" t="n">
         <v>1.3</v>
@@ -5858,10 +5858,10 @@
         <v>1.77</v>
       </c>
       <c r="AC34" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="AE34" t="n">
         <v>1.06</v>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="AJ34" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -5987,13 +5987,13 @@
         <v>2.68</v>
       </c>
       <c r="S35" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T35" t="n">
         <v>3.55</v>
       </c>
       <c r="U35" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V35" t="n">
         <v>1.64</v>
@@ -6005,31 +6005,31 @@
         <v>1.02</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="Z35" t="n">
-        <v>5.25</v>
+        <v>5.1</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AB35" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.12</v>
+        <v>2.19</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AF35" t="n">
         <v>1.54</v>
       </c>
       <c r="AG35" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6045,7 +6045,7 @@
         <v>1.18</v>
       </c>
       <c r="AK35" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -6131,7 +6131,7 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="O36" t="n">
         <v>3.75</v>
@@ -6140,10 +6140,10 @@
         <v>4.58</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="R36" t="n">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="S36" t="n">
         <v>1.33</v>
@@ -6155,10 +6155,10 @@
         <v>2.56</v>
       </c>
       <c r="V36" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W36" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X36" t="n">
         <v>1.03</v>
@@ -6170,19 +6170,19 @@
         <v>3.9</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AB36" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AC36" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="AD36" t="n">
         <v>1.36</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AF36" t="n">
         <v>1.67</v>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,64 +6290,64 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.32</v>
+        <v>1.67</v>
       </c>
       <c r="O37" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="P37" t="n">
-        <v>7.8</v>
+        <v>4.59</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z37" t="n">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AE37" t="n">
         <v>1.15</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.78</v>
+        <v>2.11</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AK37" t="n">
-        <v>2.7</v>
+        <v>2.15</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,64 +6449,64 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1.67</v>
+        <v>1.32</v>
       </c>
       <c r="O38" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P38" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z38" t="n">
         <v>4</v>
       </c>
-      <c r="P38" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="R38" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="S38" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="T38" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U38" t="n">
+      <c r="AA38" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AC38" t="n">
         <v>2.5</v>
       </c>
-      <c r="V38" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X38" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>2.8</v>
-      </c>
       <c r="AD38" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="AE38" t="n">
         <v>1.15</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="AG38" t="n">
-        <v>2.05</v>
+        <v>1.78</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AK38" t="n">
-        <v>2.15</v>
+        <v>2.7</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>2.75</v>
+        <v>2.86</v>
       </c>
       <c r="O39" t="n">
         <v>2.9</v>
@@ -6635,7 +6635,7 @@
         <v>1.28</v>
       </c>
       <c r="W39" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X39" t="n">
         <v>1.07</v>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="AJ39" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AK39" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6779,7 +6779,7 @@
         <v>2.9</v>
       </c>
       <c r="R40" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="S40" t="n">
         <v>1.6</v>
@@ -6797,25 +6797,25 @@
         <v>1.03</v>
       </c>
       <c r="X40" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AC40" t="n">
-        <v>6.5</v>
+        <v>5.6</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AE40" t="n">
         <v>1.02</v>
@@ -6840,7 +6840,7 @@
         <v>1.29</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,49 +6926,49 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>1.65</v>
+        <v>2.8</v>
       </c>
       <c r="O41" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="P41" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
+      </c>
+      <c r="V41" t="n">
+        <v>0</v>
+      </c>
+      <c r="W41" t="n">
+        <v>0</v>
+      </c>
+      <c r="X41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA41" t="n">
         <v>3.1</v>
       </c>
-      <c r="P41" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
-      <c r="R41" t="n">
-        <v>0</v>
-      </c>
-      <c r="S41" t="n">
-        <v>0</v>
-      </c>
-      <c r="T41" t="n">
-        <v>0</v>
-      </c>
-      <c r="U41" t="n">
-        <v>0</v>
-      </c>
-      <c r="V41" t="n">
-        <v>0</v>
-      </c>
-      <c r="W41" t="n">
-        <v>0</v>
-      </c>
-      <c r="X41" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>2.87</v>
-      </c>
       <c r="AB41" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,64 +7085,64 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>2.62</v>
+        <v>1.99</v>
       </c>
       <c r="O42" t="n">
-        <v>2.62</v>
+        <v>2.9</v>
       </c>
       <c r="P42" t="n">
-        <v>2.8</v>
+        <v>3.65</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AA42" t="n">
-        <v>3.1</v>
+        <v>2.78</v>
       </c>
       <c r="AB42" t="n">
         <v>1.36</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7155,10 +7155,10 @@
         </is>
       </c>
       <c r="AJ42" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK42" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL42" t="n">
         <v>0</v>
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,64 +7244,64 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>1.83</v>
+        <v>2.02</v>
       </c>
       <c r="O43" t="n">
-        <v>2.87</v>
+        <v>2.78</v>
       </c>
       <c r="P43" t="n">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="R43" t="n">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="S43" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="T43" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="U43" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="V43" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="W43" t="n">
         <v>1.03</v>
       </c>
       <c r="X43" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.92</v>
+        <v>2.8</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="AC43" t="n">
-        <v>6.35</v>
+        <v>6</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF43" t="n">
-        <v>2.57</v>
+        <v>2.25</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7314,10 +7314,10 @@
         </is>
       </c>
       <c r="AJ43" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="AK43" t="n">
-        <v>1.82</v>
+        <v>1.65</v>
       </c>
       <c r="AL43" t="n">
         <v>0</v>
@@ -7403,19 +7403,19 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="O44" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="P44" t="n">
-        <v>5.25</v>
+        <v>4.9</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="R44" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="S44" t="n">
         <v>1.69</v>
@@ -7427,40 +7427,40 @@
         <v>4.2</v>
       </c>
       <c r="V44" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="W44" t="n">
         <v>1.03</v>
       </c>
       <c r="X44" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AA44" t="n">
-        <v>3.04</v>
+        <v>3.34</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AC44" t="n">
-        <v>6.25</v>
+        <v>7.5</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AE44" t="n">
         <v>1.02</v>
       </c>
       <c r="AF44" t="n">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="AJ44" t="n">
-        <v>1.08</v>
+        <v>1.36</v>
       </c>
       <c r="AK44" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AL44" t="n">
         <v>0</v>
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,64 +7562,64 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="O45" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="P45" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="R45" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="S45" t="n">
-        <v>1.64</v>
+        <v>1.76</v>
       </c>
       <c r="T45" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="U45" t="n">
-        <v>4.05</v>
+        <v>4.65</v>
       </c>
       <c r="V45" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="W45" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X45" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.19</v>
+        <v>2.02</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.83</v>
+        <v>3.28</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AC45" t="n">
-        <v>6.05</v>
+        <v>7.1</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF45" t="n">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7632,10 +7632,10 @@
         </is>
       </c>
       <c r="AJ45" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AK45" t="n">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="AL45" t="n">
         <v>0</v>
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,64 +7721,64 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="O46" t="n">
-        <v>2.5</v>
+        <v>2.87</v>
       </c>
       <c r="P46" t="n">
-        <v>3.6</v>
+        <v>4.96</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.3</v>
+        <v>2.45</v>
       </c>
       <c r="R46" t="n">
-        <v>1.59</v>
+        <v>1.85</v>
       </c>
       <c r="S46" t="n">
-        <v>1.84</v>
+        <v>1.66</v>
       </c>
       <c r="T46" t="n">
-        <v>1.86</v>
+        <v>2.08</v>
       </c>
       <c r="U46" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="V46" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="W46" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X46" t="n">
         <v>1.15</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="Z46" t="n">
-        <v>1.94</v>
+        <v>2.12</v>
       </c>
       <c r="AA46" t="n">
-        <v>3.34</v>
+        <v>3.07</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="AC46" t="n">
-        <v>7.3</v>
+        <v>6.38</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AE46" t="n">
         <v>1.02</v>
       </c>
       <c r="AF46" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7791,10 +7791,10 @@
         </is>
       </c>
       <c r="AJ46" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AK46" t="n">
-        <v>1.52</v>
+        <v>1.82</v>
       </c>
       <c r="AL46" t="n">
         <v>0</v>
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,64 +7880,64 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>2.1</v>
+        <v>1.77</v>
       </c>
       <c r="O47" t="n">
-        <v>2.8</v>
+        <v>2.95</v>
       </c>
       <c r="P47" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="V47" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X47" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.78</v>
+        <v>3.4</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AC47" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -7950,10 +7950,10 @@
         </is>
       </c>
       <c r="AJ47" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AK47" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AL47" t="n">
         <v>0</v>
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>4.08</v>
+        <v>4.1</v>
       </c>
       <c r="O49" t="n">
-        <v>3.48</v>
+        <v>3.51</v>
       </c>
       <c r="P49" t="n">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
       <c r="Q49" t="n">
         <v>4.66</v>
@@ -8219,10 +8219,10 @@
         <v>2.7</v>
       </c>
       <c r="U49" t="n">
-        <v>2.91</v>
+        <v>2.78</v>
       </c>
       <c r="V49" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W49" t="n">
         <v>1.06</v>
@@ -8246,7 +8246,7 @@
         <v>3.71</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AE49" t="n">
         <v>1.06</v>
@@ -8268,7 +8268,7 @@
         </is>
       </c>
       <c r="AJ49" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AK49" t="n">
         <v>1.2</v>
@@ -8369,19 +8369,19 @@
         <v>3.3</v>
       </c>
       <c r="R50" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S50" t="n">
         <v>1.34</v>
       </c>
       <c r="T50" t="n">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="U50" t="n">
-        <v>2.2</v>
+        <v>2.67</v>
       </c>
       <c r="V50" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="W50" t="n">
         <v>1.08</v>
@@ -8390,13 +8390,13 @@
         <v>1.05</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z50" t="n">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AB50" t="n">
         <v>1.83</v>
@@ -8516,7 +8516,7 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="O51" t="n">
         <v>2.89</v>
@@ -8525,16 +8525,16 @@
         <v>3.2</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.08</v>
+        <v>2.88</v>
       </c>
       <c r="R51" t="n">
         <v>1.91</v>
       </c>
       <c r="S51" t="n">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="T51" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="U51" t="n">
         <v>3.5</v>
@@ -8546,25 +8546,25 @@
         <v>1.04</v>
       </c>
       <c r="X51" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="Z51" t="n">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="AA51" t="n">
-        <v>2.5</v>
+        <v>2.61</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AC51" t="n">
-        <v>4.95</v>
+        <v>6.89</v>
       </c>
       <c r="AD51" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AE51" t="n">
         <v>1.04</v>
@@ -8589,7 +8589,7 @@
         <v>1.4</v>
       </c>
       <c r="AK51" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AL51" t="n">
         <v>0</v>
@@ -8849,16 +8849,16 @@
         <v>2.15</v>
       </c>
       <c r="S53" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T53" t="n">
-        <v>2.23</v>
+        <v>2.75</v>
       </c>
       <c r="U53" t="n">
         <v>2.83</v>
       </c>
       <c r="V53" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="W53" t="n">
         <v>1.04</v>
@@ -8882,7 +8882,7 @@
         <v>3.5</v>
       </c>
       <c r="AD53" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AE53" t="n">
         <v>1.08</v>
@@ -8907,7 +8907,7 @@
         <v>1.24</v>
       </c>
       <c r="AK53" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AL53" t="n">
         <v>0</v>

--- a/jogos_2026-07-11.xlsx
+++ b/jogos_2026-07-11.xlsx
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>APIA Leichhardt Tigers</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Sydney II</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="O5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="P5" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="V5" t="n">
         <v>1.64</v>
-      </c>
-      <c r="O5" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="P5" t="n">
-        <v>4.47</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R5" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="T5" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.45</v>
       </c>
       <c r="W5" t="n">
         <v>1.13</v>
       </c>
       <c r="X5" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.95</v>
+        <v>4.9</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.67</v>
+        <v>1.42</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.05</v>
+        <v>2.49</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.62</v>
+        <v>2.07</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.42</v>
+        <v>1.62</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.07</v>
+        <v>2.17</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.03</v>
+        <v>2.43</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>APIA Leichhardt Tigers</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sydney II</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,65 +1361,65 @@
         </is>
       </c>
       <c r="N6" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="O6" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="P6" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="V6" t="n">
         <v>1.45</v>
-      </c>
-      <c r="O6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="P6" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="R6" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="T6" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.64</v>
       </c>
       <c r="W6" t="n">
         <v>1.13</v>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE6" t="n">
         <v>1.12</v>
       </c>
-      <c r="Z6" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AC6" t="n">
+      <c r="AF6" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG6" t="n">
         <v>2.07</v>
       </c>
-      <c r="AD6" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>2.17</v>
-      </c>
       <c r="AH6" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.43</v>
+        <v>2.03</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>7.49</v>
+        <v>2.23</v>
       </c>
       <c r="O9" t="n">
-        <v>4.55</v>
+        <v>3.18</v>
       </c>
       <c r="P9" t="n">
-        <v>1.28</v>
+        <v>2.97</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.25</v>
+        <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>2.4</v>
+        <v>1.98</v>
       </c>
       <c r="S9" t="n">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="T9" t="n">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="U9" t="n">
-        <v>2.44</v>
+        <v>2.91</v>
       </c>
       <c r="V9" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="W9" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X9" t="n">
         <v>1.04</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.82</v>
+        <v>3.04</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.75</v>
+        <v>1.99</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.97</v>
+        <v>1.7</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.9</v>
+        <v>3.35</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.95</v>
+        <v>1.77</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>2.88</v>
+        <v>1.3</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.06</v>
+        <v>1.54</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.23</v>
+        <v>2.05</v>
       </c>
       <c r="O10" t="n">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="P10" t="n">
-        <v>2.97</v>
+        <v>3.17</v>
       </c>
       <c r="Q10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.99</v>
+        <v>2.15</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>5.3</v>
+        <v>2.05</v>
       </c>
       <c r="O11" t="n">
-        <v>3.72</v>
+        <v>3.2</v>
       </c>
       <c r="P11" t="n">
-        <v>1.55</v>
+        <v>3.35</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.5</v>
+        <v>2.49</v>
       </c>
       <c r="R11" t="n">
-        <v>2.01</v>
+        <v>2.14</v>
       </c>
       <c r="S11" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="T11" t="n">
-        <v>2.53</v>
+        <v>2.75</v>
       </c>
       <c r="U11" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="V11" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y11" t="n">
         <v>1.33</v>
       </c>
-      <c r="W11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.4</v>
-      </c>
       <c r="Z11" t="n">
-        <v>2.72</v>
+        <v>3</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.05</v>
+        <v>3.45</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.2</v>
+        <v>1.87</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.6</v>
+        <v>1.82</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>2.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.1</v>
+        <v>1.77</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,65 +2315,65 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.74</v>
+        <v>1.87</v>
       </c>
       <c r="O12" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P12" t="n">
-        <v>2.47</v>
+        <v>3.6</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.2</v>
+        <v>2.52</v>
       </c>
       <c r="R12" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S12" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="T12" t="n">
-        <v>2.81</v>
+        <v>2.66</v>
       </c>
       <c r="U12" t="n">
         <v>2.88</v>
       </c>
       <c r="V12" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="W12" t="n">
         <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.4</v>
+        <v>3.14</v>
       </c>
       <c r="AA12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AG12" t="n">
         <v>1.95</v>
       </c>
-      <c r="AB12" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AH12" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.48</v>
+        <v>1.83</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,65 +2474,65 @@
         </is>
       </c>
       <c r="N13" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="O13" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R13" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG13" t="n">
         <v>2.05</v>
       </c>
-      <c r="O13" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P13" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>0</v>
-      </c>
       <c r="AH13" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.87</v>
+        <v>5.3</v>
       </c>
       <c r="O14" t="n">
-        <v>3.25</v>
+        <v>3.72</v>
       </c>
       <c r="P14" t="n">
-        <v>3.6</v>
+        <v>1.55</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.52</v>
+        <v>6.5</v>
       </c>
       <c r="R14" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AA14" t="n">
         <v>2.2</v>
       </c>
-      <c r="S14" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="U14" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>2</v>
-      </c>
       <c r="AB14" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.5</v>
+        <v>4.05</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.79</v>
+        <v>2.2</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.83</v>
+        <v>1.1</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,80 +2792,80 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.05</v>
+        <v>7.49</v>
       </c>
       <c r="O15" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T15" t="n">
         <v>3.2</v>
       </c>
-      <c r="P15" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="R15" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.75</v>
-      </c>
       <c r="U15" t="n">
-        <v>3</v>
+        <v>2.44</v>
       </c>
       <c r="V15" t="n">
-        <v>1.32</v>
+        <v>1.43</v>
       </c>
       <c r="W15" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ15" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AK15" t="n">
         <v>1.06</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1.77</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.59</v>
+        <v>2.15</v>
       </c>
       <c r="O16" t="n">
-        <v>4.46</v>
+        <v>3.2</v>
       </c>
       <c r="P16" t="n">
-        <v>5.2</v>
+        <v>3.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.15</v>
+        <v>1.59</v>
       </c>
       <c r="O19" t="n">
-        <v>3.2</v>
+        <v>4.46</v>
       </c>
       <c r="P19" t="n">
-        <v>3.1</v>
+        <v>5.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.5</v>
+        <v>1.36</v>
       </c>
       <c r="O21" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="P21" t="n">
-        <v>2.4</v>
+        <v>7.5</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.36</v>
+        <v>2.5</v>
       </c>
       <c r="O22" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="P22" t="n">
-        <v>7.5</v>
+        <v>2.4</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.86</v>
+        <v>2.81</v>
       </c>
       <c r="R23" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="S23" t="n">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="T23" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="U23" t="n">
-        <v>2.64</v>
+        <v>1.99</v>
       </c>
       <c r="V23" t="n">
-        <v>1.44</v>
+        <v>1.75</v>
       </c>
       <c r="W23" t="n">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="X23" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.24</v>
+        <v>1.06</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.54</v>
+        <v>11.4</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.82</v>
+        <v>1.4</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.01</v>
+        <v>2.74</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.1</v>
+        <v>1.95</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.38</v>
+        <v>1.75</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.15</v>
+        <v>1.31</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.61</v>
+        <v>1.36</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.18</v>
+        <v>2.98</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.81</v>
+        <v>2.86</v>
       </c>
       <c r="R24" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="S24" t="n">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="T24" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="U24" t="n">
-        <v>1.99</v>
+        <v>2.64</v>
       </c>
       <c r="V24" t="n">
-        <v>1.75</v>
+        <v>1.44</v>
       </c>
       <c r="W24" t="n">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="X24" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.06</v>
+        <v>1.24</v>
       </c>
       <c r="Z24" t="n">
-        <v>11.4</v>
+        <v>4.54</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.4</v>
+        <v>1.82</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.74</v>
+        <v>2.01</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.95</v>
+        <v>3.1</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.75</v>
+        <v>1.38</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.31</v>
+        <v>1.15</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.36</v>
+        <v>1.61</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.98</v>
+        <v>2.18</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,64 +4541,64 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>2.75</v>
+        <v>1.27</v>
       </c>
       <c r="O26" t="n">
-        <v>3.01</v>
+        <v>5.1</v>
       </c>
       <c r="P26" t="n">
-        <v>2.7</v>
+        <v>7</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.3</v>
+        <v>1.76</v>
       </c>
       <c r="R26" t="n">
-        <v>2.08</v>
+        <v>2.68</v>
       </c>
       <c r="S26" t="n">
-        <v>1.48</v>
+        <v>1.28</v>
       </c>
       <c r="T26" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC26" t="n">
         <v>2.63</v>
       </c>
-      <c r="U26" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>3.9</v>
-      </c>
       <c r="AD26" t="n">
-        <v>1.21</v>
+        <v>1.44</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.41</v>
+        <v>3.2</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,80 +4700,80 @@
         </is>
       </c>
       <c r="N27" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O27" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="P27" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R27" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="S27" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U27" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ27" t="n">
         <v>1.27</v>
       </c>
-      <c r="O27" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="P27" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="R27" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="S27" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="T27" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U27" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X27" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ27" t="n">
-        <v>1.16</v>
-      </c>
       <c r="AK27" t="n">
-        <v>3.2</v>
+        <v>1.41</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,64 +4859,64 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>1.95</v>
+        <v>2.13</v>
       </c>
       <c r="O28" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="P28" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="AJ28" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,64 +5018,64 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>2.13</v>
+        <v>1.95</v>
       </c>
       <c r="O29" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="P29" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,64 +5336,64 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>2.9</v>
+        <v>1.89</v>
       </c>
       <c r="O31" t="n">
-        <v>3.5</v>
+        <v>2.95</v>
       </c>
       <c r="P31" t="n">
-        <v>2.19</v>
+        <v>4.1</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>5.42</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="AJ31" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,64 +5495,64 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>1.89</v>
+        <v>1.74</v>
       </c>
       <c r="O32" t="n">
-        <v>2.95</v>
+        <v>3.78</v>
       </c>
       <c r="P32" t="n">
-        <v>4.1</v>
+        <v>3.84</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK32" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,64 +5654,64 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1.74</v>
+        <v>2.9</v>
       </c>
       <c r="O33" t="n">
-        <v>3.78</v>
+        <v>3.5</v>
       </c>
       <c r="P33" t="n">
-        <v>3.84</v>
+        <v>2.19</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.26</v>
+        <v>3.4</v>
       </c>
       <c r="R33" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="S33" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="T33" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="U33" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="V33" t="n">
         <v>1.62</v>
       </c>
       <c r="W33" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="X33" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="Z33" t="n">
-        <v>5.3</v>
+        <v>5.42</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AF33" t="n">
         <v>1.44</v>
       </c>
       <c r="AG33" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>1.21</v>
+        <v>1.7</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.86</v>
+        <v>1.33</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,64 +6131,64 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1.65</v>
+        <v>1.32</v>
       </c>
       <c r="O36" t="n">
-        <v>3.75</v>
+        <v>4.8</v>
       </c>
       <c r="P36" t="n">
-        <v>4.58</v>
+        <v>7.8</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z36" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="AB36" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="AC36" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="AG36" t="n">
-        <v>2.1</v>
+        <v>1.78</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AK36" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,64 +6449,64 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1.32</v>
+        <v>1.65</v>
       </c>
       <c r="O38" t="n">
-        <v>4.8</v>
+        <v>3.75</v>
       </c>
       <c r="P38" t="n">
-        <v>7.8</v>
+        <v>4.58</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z38" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.78</v>
+        <v>2.1</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AK38" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,64 +6767,64 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1.97</v>
+        <v>2.15</v>
       </c>
       <c r="O40" t="n">
-        <v>2.93</v>
+        <v>2.5</v>
       </c>
       <c r="P40" t="n">
-        <v>3.99</v>
+        <v>3.9</v>
       </c>
       <c r="Q40" t="n">
         <v>2.9</v>
       </c>
       <c r="R40" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="S40" t="n">
-        <v>1.6</v>
+        <v>1.76</v>
       </c>
       <c r="T40" t="n">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="U40" t="n">
-        <v>3.88</v>
+        <v>4.65</v>
       </c>
       <c r="V40" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X40" t="n">
         <v>1.18</v>
       </c>
-      <c r="W40" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X40" t="n">
-        <v>1.14</v>
-      </c>
       <c r="Y40" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.75</v>
+        <v>3.28</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AC40" t="n">
-        <v>5.6</v>
+        <v>7.1</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="AE40" t="n">
         <v>1.02</v>
       </c>
       <c r="AF40" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="AJ40" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,64 +6926,64 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>2.8</v>
+        <v>1.83</v>
       </c>
       <c r="O41" t="n">
-        <v>2.7</v>
+        <v>2.87</v>
       </c>
       <c r="P41" t="n">
-        <v>2.81</v>
+        <v>4.96</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AA41" t="n">
-        <v>3.1</v>
+        <v>3.07</v>
       </c>
       <c r="AB41" t="n">
         <v>1.36</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>6.38</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -6996,10 +6996,10 @@
         </is>
       </c>
       <c r="AJ41" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK41" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL41" t="n">
         <v>0</v>
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,61 +7085,61 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="O42" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="P42" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="Q42" t="n">
         <v>2.9</v>
-      </c>
-      <c r="P42" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>2.63</v>
       </c>
       <c r="R42" t="n">
         <v>1.85</v>
       </c>
       <c r="S42" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="T42" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="U42" t="n">
-        <v>4</v>
+        <v>3.88</v>
       </c>
       <c r="V42" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W42" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X42" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.21</v>
+        <v>2.1</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="AB42" t="n">
         <v>1.36</v>
       </c>
       <c r="AC42" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF42" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AG42" t="n">
         <v>1.57</v>
@@ -7155,10 +7155,10 @@
         </is>
       </c>
       <c r="AJ42" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AK42" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AL42" t="n">
         <v>0</v>
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,64 +7244,64 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>2.02</v>
+        <v>1.72</v>
       </c>
       <c r="O43" t="n">
-        <v>2.78</v>
+        <v>2.98</v>
       </c>
       <c r="P43" t="n">
-        <v>3.7</v>
+        <v>4.9</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="R43" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="S43" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="T43" t="n">
-        <v>2.11</v>
+        <v>2.04</v>
       </c>
       <c r="U43" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="V43" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="W43" t="n">
         <v>1.03</v>
       </c>
       <c r="X43" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.59</v>
+        <v>1.75</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.8</v>
+        <v>3.34</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AC43" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF43" t="n">
-        <v>2.25</v>
+        <v>2.55</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.6</v>
+        <v>1.42</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7314,10 +7314,10 @@
         </is>
       </c>
       <c r="AJ43" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AK43" t="n">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AL43" t="n">
         <v>0</v>
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,64 +7403,64 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>1.72</v>
+        <v>2.02</v>
       </c>
       <c r="O44" t="n">
-        <v>2.98</v>
+        <v>2.78</v>
       </c>
       <c r="P44" t="n">
-        <v>4.9</v>
+        <v>3.7</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="R44" t="n">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="S44" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="T44" t="n">
-        <v>2.04</v>
+        <v>2.11</v>
       </c>
       <c r="U44" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="V44" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W44" t="n">
         <v>1.03</v>
       </c>
       <c r="X44" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.75</v>
+        <v>1.59</v>
       </c>
       <c r="Z44" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AA44" t="n">
-        <v>3.34</v>
+        <v>2.8</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AC44" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF44" t="n">
-        <v>2.55</v>
+        <v>2.25</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.42</v>
+        <v>1.6</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="AJ44" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AK44" t="n">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="AL44" t="n">
         <v>0</v>
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,64 +7562,64 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>2.15</v>
+        <v>1.99</v>
       </c>
       <c r="O45" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="P45" t="n">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.9</v>
+        <v>2.63</v>
       </c>
       <c r="R45" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="S45" t="n">
-        <v>1.76</v>
+        <v>1.61</v>
       </c>
       <c r="T45" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="U45" t="n">
-        <v>4.65</v>
+        <v>4</v>
       </c>
       <c r="V45" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="W45" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X45" t="n">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.02</v>
+        <v>2.21</v>
       </c>
       <c r="AA45" t="n">
-        <v>3.28</v>
+        <v>2.78</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AC45" t="n">
-        <v>7.1</v>
+        <v>5.9</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF45" t="n">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.43</v>
+        <v>1.57</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7632,10 +7632,10 @@
         </is>
       </c>
       <c r="AJ45" t="n">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="AK45" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AL45" t="n">
         <v>0</v>
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,64 +7721,64 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="O46" t="n">
-        <v>2.87</v>
+        <v>2.95</v>
       </c>
       <c r="P46" t="n">
-        <v>4.96</v>
+        <v>4.4</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>3.07</v>
+        <v>3.4</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AC46" t="n">
-        <v>6.38</v>
+        <v>0</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7791,10 +7791,10 @@
         </is>
       </c>
       <c r="AJ46" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AK46" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AL46" t="n">
         <v>0</v>
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>1.77</v>
+        <v>2.8</v>
       </c>
       <c r="O47" t="n">
-        <v>2.95</v>
+        <v>2.7</v>
       </c>
       <c r="P47" t="n">
-        <v>4.4</v>
+        <v>2.81</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -7919,10 +7919,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>

--- a/jogos_2026-07-11.xlsx
+++ b/jogos_2026-07-11.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,31 +725,31 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="O2" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="P2" t="n">
-        <v>2.4</v>
+        <v>2.57</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.97</v>
+        <v>2.7</v>
       </c>
       <c r="R2" t="n">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="S2" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="T2" t="n">
-        <v>3.14</v>
+        <v>2.92</v>
       </c>
       <c r="U2" t="n">
-        <v>2.44</v>
+        <v>2.63</v>
       </c>
       <c r="V2" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W2" t="n">
         <v>1.07</v>
@@ -758,31 +758,31 @@
         <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.05</v>
+        <v>3.58</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.62</v>
+        <v>2.78</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.29</v>
+        <v>2.17</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.71</v>
+        <v>2.45</v>
       </c>
       <c r="O3" t="n">
-        <v>3.44</v>
+        <v>3.6</v>
       </c>
       <c r="P3" t="n">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.37</v>
+        <v>2.97</v>
       </c>
       <c r="R3" t="n">
-        <v>2.21</v>
+        <v>2.18</v>
       </c>
       <c r="S3" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T3" t="n">
-        <v>3.12</v>
+        <v>3.14</v>
       </c>
       <c r="U3" t="n">
-        <v>2.28</v>
+        <v>2.44</v>
       </c>
       <c r="V3" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="W3" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X3" t="n">
         <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.98</v>
+        <v>4.05</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AB3" t="n">
         <v>2.1</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.52</v>
+        <v>2.62</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AF3" t="n">
         <v>1.53</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>1.22</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.35</v>
+        <v>2.71</v>
       </c>
       <c r="O4" t="n">
-        <v>3.35</v>
+        <v>3.44</v>
       </c>
       <c r="P4" t="n">
-        <v>2.57</v>
+        <v>2.26</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.7</v>
+        <v>3.37</v>
       </c>
       <c r="R4" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="S4" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="T4" t="n">
-        <v>2.92</v>
+        <v>3.12</v>
       </c>
       <c r="U4" t="n">
-        <v>2.63</v>
+        <v>2.28</v>
       </c>
       <c r="V4" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W4" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X4" t="n">
         <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.58</v>
+        <v>3.98</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.74</v>
+        <v>1.62</v>
       </c>
       <c r="AB4" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.78</v>
+        <v>2.52</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.17</v>
+        <v>2.32</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.46</v>
+        <v>1.37</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>APIA Leichhardt Tigers</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sydney II</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,65 +1202,65 @@
         </is>
       </c>
       <c r="N5" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="O5" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="P5" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="V5" t="n">
         <v>1.45</v>
-      </c>
-      <c r="O5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="P5" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="R5" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="T5" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.64</v>
       </c>
       <c r="W5" t="n">
         <v>1.13</v>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y5" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE5" t="n">
         <v>1.12</v>
       </c>
-      <c r="Z5" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AC5" t="n">
+      <c r="AF5" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG5" t="n">
         <v>2.07</v>
       </c>
-      <c r="AD5" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>2.17</v>
-      </c>
       <c r="AH5" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.43</v>
+        <v>2.03</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>APIA Leichhardt Tigers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Sydney II</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="O6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="P6" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="V6" t="n">
         <v>1.64</v>
-      </c>
-      <c r="O6" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="P6" t="n">
-        <v>4.47</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R6" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="T6" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.45</v>
       </c>
       <c r="W6" t="n">
         <v>1.13</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.95</v>
+        <v>4.9</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.67</v>
+        <v>1.42</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.05</v>
+        <v>2.49</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.62</v>
+        <v>2.07</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.42</v>
+        <v>1.62</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.07</v>
+        <v>2.17</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.03</v>
+        <v>2.43</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.23</v>
+        <v>1.87</v>
       </c>
       <c r="O9" t="n">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="P9" t="n">
-        <v>2.97</v>
+        <v>3.6</v>
       </c>
       <c r="Q9" t="n">
-        <v>3</v>
+        <v>2.52</v>
       </c>
       <c r="R9" t="n">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="S9" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="T9" t="n">
-        <v>2.75</v>
+        <v>2.66</v>
       </c>
       <c r="U9" t="n">
-        <v>2.91</v>
+        <v>2.88</v>
       </c>
       <c r="V9" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W9" t="n">
         <v>1.03</v>
       </c>
       <c r="X9" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.04</v>
+        <v>3.14</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>1.3</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.54</v>
+        <v>1.83</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,65 +1997,65 @@
         </is>
       </c>
       <c r="N10" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="O10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG10" t="n">
         <v>2.05</v>
       </c>
-      <c r="O10" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P10" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>0</v>
-      </c>
       <c r="AH10" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.05</v>
+        <v>5.3</v>
       </c>
       <c r="O11" t="n">
-        <v>3.2</v>
+        <v>3.72</v>
       </c>
       <c r="P11" t="n">
-        <v>3.35</v>
+        <v>1.55</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.49</v>
+        <v>6.5</v>
       </c>
       <c r="R11" t="n">
-        <v>2.14</v>
+        <v>2.01</v>
       </c>
       <c r="S11" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="T11" t="n">
-        <v>2.75</v>
+        <v>2.53</v>
       </c>
       <c r="U11" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="V11" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W11" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X11" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="Z11" t="n">
-        <v>3</v>
+        <v>2.72</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.45</v>
+        <v>4.05</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.87</v>
+        <v>2.2</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.82</v>
+        <v>1.6</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.25</v>
+        <v>2.3</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.77</v>
+        <v>1.1</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,80 +2315,80 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.87</v>
+        <v>7.49</v>
       </c>
       <c r="O12" t="n">
-        <v>3.25</v>
+        <v>4.55</v>
       </c>
       <c r="P12" t="n">
-        <v>3.6</v>
+        <v>1.28</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.52</v>
+        <v>6.25</v>
       </c>
       <c r="R12" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="S12" t="n">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="T12" t="n">
-        <v>2.66</v>
+        <v>3.2</v>
       </c>
       <c r="U12" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ12" t="n">
         <v>2.88</v>
       </c>
-      <c r="V12" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X12" t="n">
+      <c r="AK12" t="n">
         <v>1.06</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>1.83</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,80 +2474,80 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.74</v>
+        <v>2.05</v>
       </c>
       <c r="O13" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P13" t="n">
-        <v>2.47</v>
+        <v>3.35</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.2</v>
+        <v>2.49</v>
       </c>
       <c r="R13" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="S13" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="T13" t="n">
-        <v>2.81</v>
+        <v>2.75</v>
       </c>
       <c r="U13" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="V13" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="W13" t="n">
         <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ13" t="n">
         <v>1.25</v>
       </c>
-      <c r="Z13" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.48</v>
-      </c>
       <c r="AK13" t="n">
-        <v>1.48</v>
+        <v>1.77</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>5.3</v>
+        <v>2.05</v>
       </c>
       <c r="O14" t="n">
-        <v>3.72</v>
+        <v>3.2</v>
       </c>
       <c r="P14" t="n">
-        <v>1.55</v>
+        <v>3.17</v>
       </c>
       <c r="Q14" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>7.49</v>
+        <v>2.23</v>
       </c>
       <c r="O15" t="n">
-        <v>4.55</v>
+        <v>3.18</v>
       </c>
       <c r="P15" t="n">
-        <v>1.28</v>
+        <v>2.97</v>
       </c>
       <c r="Q15" t="n">
-        <v>6.25</v>
+        <v>3</v>
       </c>
       <c r="R15" t="n">
-        <v>2.4</v>
+        <v>1.98</v>
       </c>
       <c r="S15" t="n">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="T15" t="n">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="U15" t="n">
-        <v>2.44</v>
+        <v>2.91</v>
       </c>
       <c r="V15" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="W15" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X15" t="n">
         <v>1.04</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.82</v>
+        <v>3.04</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.75</v>
+        <v>1.99</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.97</v>
+        <v>1.7</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.9</v>
+        <v>3.35</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.95</v>
+        <v>1.77</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>2.88</v>
+        <v>1.3</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.06</v>
+        <v>1.54</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.15</v>
+        <v>3.18</v>
       </c>
       <c r="O16" t="n">
-        <v>3.2</v>
+        <v>3.48</v>
       </c>
       <c r="P16" t="n">
-        <v>3.1</v>
+        <v>2.25</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>3.18</v>
+        <v>2.15</v>
       </c>
       <c r="O17" t="n">
-        <v>3.48</v>
+        <v>3.2</v>
       </c>
       <c r="P17" t="n">
-        <v>2.25</v>
+        <v>3.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>4.46</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>4.46</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.81</v>
+        <v>2.86</v>
       </c>
       <c r="R23" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="S23" t="n">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="T23" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="U23" t="n">
-        <v>1.99</v>
+        <v>2.64</v>
       </c>
       <c r="V23" t="n">
-        <v>1.75</v>
+        <v>1.44</v>
       </c>
       <c r="W23" t="n">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="X23" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.06</v>
+        <v>1.24</v>
       </c>
       <c r="Z23" t="n">
-        <v>11.4</v>
+        <v>4.54</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.4</v>
+        <v>1.82</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.74</v>
+        <v>2.01</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.95</v>
+        <v>3.1</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.75</v>
+        <v>1.38</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.31</v>
+        <v>1.15</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.36</v>
+        <v>1.61</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.98</v>
+        <v>2.18</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.86</v>
+        <v>2.81</v>
       </c>
       <c r="R24" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="S24" t="n">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="T24" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="U24" t="n">
-        <v>2.64</v>
+        <v>1.99</v>
       </c>
       <c r="V24" t="n">
-        <v>1.44</v>
+        <v>1.75</v>
       </c>
       <c r="W24" t="n">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="X24" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.24</v>
+        <v>1.06</v>
       </c>
       <c r="Z24" t="n">
-        <v>4.54</v>
+        <v>11.4</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.82</v>
+        <v>1.4</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.01</v>
+        <v>2.74</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.1</v>
+        <v>1.95</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.38</v>
+        <v>1.75</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.15</v>
+        <v>1.31</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.61</v>
+        <v>1.36</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.18</v>
+        <v>2.98</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,64 +4859,64 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>2.13</v>
+        <v>1.95</v>
       </c>
       <c r="O28" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="P28" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,64 +5018,64 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>1.95</v>
+        <v>2.13</v>
       </c>
       <c r="O29" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="P29" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="AJ29" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,64 +5495,64 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>1.74</v>
+        <v>2.9</v>
       </c>
       <c r="O32" t="n">
-        <v>3.78</v>
+        <v>3.5</v>
       </c>
       <c r="P32" t="n">
-        <v>3.84</v>
+        <v>2.19</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.26</v>
+        <v>3.4</v>
       </c>
       <c r="R32" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="S32" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="T32" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="U32" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="V32" t="n">
         <v>1.62</v>
       </c>
       <c r="W32" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="X32" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="Z32" t="n">
-        <v>5.3</v>
+        <v>5.42</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AF32" t="n">
         <v>1.44</v>
       </c>
       <c r="AG32" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>1.21</v>
+        <v>1.7</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.86</v>
+        <v>1.33</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,64 +5654,64 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>2.9</v>
+        <v>1.74</v>
       </c>
       <c r="O33" t="n">
-        <v>3.5</v>
+        <v>3.78</v>
       </c>
       <c r="P33" t="n">
-        <v>2.19</v>
+        <v>3.84</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.4</v>
+        <v>2.26</v>
       </c>
       <c r="R33" t="n">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="S33" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="T33" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="U33" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="V33" t="n">
         <v>1.62</v>
       </c>
       <c r="W33" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="X33" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="Z33" t="n">
-        <v>5.42</v>
+        <v>5.3</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AF33" t="n">
         <v>1.44</v>
       </c>
       <c r="AG33" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>1.7</v>
+        <v>1.21</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.33</v>
+        <v>1.86</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,64 +6131,64 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1.32</v>
+        <v>1.67</v>
       </c>
       <c r="O36" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="P36" t="n">
-        <v>7.8</v>
+        <v>4.59</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z36" t="n">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AB36" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AC36" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AE36" t="n">
         <v>1.15</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.78</v>
+        <v>2.11</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AK36" t="n">
-        <v>2.7</v>
+        <v>2.15</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,65 +6290,65 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="O37" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="P37" t="n">
-        <v>4.59</v>
+        <v>4.58</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="R37" t="n">
         <v>2.3</v>
       </c>
       <c r="S37" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="T37" t="n">
-        <v>3.3</v>
+        <v>3.04</v>
       </c>
       <c r="U37" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="V37" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="W37" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X37" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y37" t="n">
         <v>1.2</v>
       </c>
       <c r="Z37" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="AA37" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF37" t="n">
         <v>1.67</v>
       </c>
-      <c r="AB37" t="n">
+      <c r="AG37" t="n">
         <v>2.1</v>
       </c>
-      <c r="AC37" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>2.11</v>
-      </c>
       <c r="AH37" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AK37" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,64 +6449,64 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1.65</v>
+        <v>1.32</v>
       </c>
       <c r="O38" t="n">
-        <v>3.75</v>
+        <v>4.8</v>
       </c>
       <c r="P38" t="n">
-        <v>4.58</v>
+        <v>7.8</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z38" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="AG38" t="n">
-        <v>2.1</v>
+        <v>1.78</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AK38" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,64 +6767,64 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="O40" t="n">
-        <v>2.5</v>
+        <v>2.78</v>
       </c>
       <c r="P40" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="R40" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="S40" t="n">
-        <v>1.76</v>
+        <v>1.64</v>
       </c>
       <c r="T40" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="U40" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X40" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="Z40" t="n">
         <v>2.2</v>
       </c>
-      <c r="U40" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="V40" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X40" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>2.02</v>
-      </c>
       <c r="AA40" t="n">
-        <v>3.28</v>
+        <v>2.8</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AC40" t="n">
-        <v>7.1</v>
+        <v>6</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF40" t="n">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.43</v>
+        <v>1.6</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="AJ40" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,64 +6926,64 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>1.83</v>
+        <v>2.15</v>
       </c>
       <c r="O41" t="n">
-        <v>2.87</v>
+        <v>2.5</v>
       </c>
       <c r="P41" t="n">
-        <v>4.96</v>
+        <v>3.9</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.45</v>
+        <v>2.9</v>
       </c>
       <c r="R41" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="S41" t="n">
-        <v>1.66</v>
+        <v>1.76</v>
       </c>
       <c r="T41" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="U41" t="n">
-        <v>4.2</v>
+        <v>4.65</v>
       </c>
       <c r="V41" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="W41" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X41" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="AA41" t="n">
-        <v>3.07</v>
+        <v>3.28</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AC41" t="n">
-        <v>6.38</v>
+        <v>7.1</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="AE41" t="n">
         <v>1.02</v>
       </c>
       <c r="AF41" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AG41" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -6996,10 +6996,10 @@
         </is>
       </c>
       <c r="AJ41" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AK41" t="n">
-        <v>1.82</v>
+        <v>1.55</v>
       </c>
       <c r="AL41" t="n">
         <v>0</v>
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,64 +7085,64 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>1.97</v>
+        <v>1.77</v>
       </c>
       <c r="O42" t="n">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="P42" t="n">
-        <v>3.99</v>
+        <v>4.4</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AC42" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7155,10 +7155,10 @@
         </is>
       </c>
       <c r="AJ42" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK42" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL42" t="n">
         <v>0</v>
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,64 +7244,64 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>1.72</v>
+        <v>2.8</v>
       </c>
       <c r="O43" t="n">
-        <v>2.98</v>
+        <v>2.7</v>
       </c>
       <c r="P43" t="n">
-        <v>4.9</v>
+        <v>2.81</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>3.34</v>
+        <v>3.1</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AC43" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF43" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7314,10 +7314,10 @@
         </is>
       </c>
       <c r="AJ43" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK43" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AL43" t="n">
         <v>0</v>
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,52 +7403,52 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="O44" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="P44" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="R44" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="S44" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="U44" t="n">
+        <v>4</v>
+      </c>
+      <c r="V44" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W44" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X44" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AA44" t="n">
         <v>2.78</v>
       </c>
-      <c r="P44" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R44" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="S44" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="T44" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="U44" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="V44" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="W44" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X44" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>2.8</v>
-      </c>
       <c r="AB44" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AC44" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AD44" t="n">
         <v>1.11</v>
@@ -7457,10 +7457,10 @@
         <v>1.03</v>
       </c>
       <c r="AF44" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7473,7 +7473,7 @@
         </is>
       </c>
       <c r="AJ44" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AK44" t="n">
         <v>1.65</v>
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,64 +7562,64 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>1.99</v>
+        <v>1.83</v>
       </c>
       <c r="O45" t="n">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="P45" t="n">
-        <v>3.65</v>
+        <v>4.96</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="R45" t="n">
         <v>1.85</v>
       </c>
       <c r="S45" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="T45" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="U45" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="V45" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="W45" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X45" t="n">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.21</v>
+        <v>2.12</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.78</v>
+        <v>3.07</v>
       </c>
       <c r="AB45" t="n">
         <v>1.36</v>
       </c>
       <c r="AC45" t="n">
-        <v>5.9</v>
+        <v>6.38</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF45" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7632,10 +7632,10 @@
         </is>
       </c>
       <c r="AJ45" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AK45" t="n">
-        <v>1.65</v>
+        <v>1.82</v>
       </c>
       <c r="AL45" t="n">
         <v>0</v>
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,64 +7721,64 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="O46" t="n">
-        <v>2.95</v>
+        <v>2.98</v>
       </c>
       <c r="P46" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA46" t="n">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7791,10 +7791,10 @@
         </is>
       </c>
       <c r="AJ46" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK46" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL46" t="n">
         <v>0</v>
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,64 +7880,64 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>2.8</v>
+        <v>1.97</v>
       </c>
       <c r="O47" t="n">
-        <v>2.7</v>
+        <v>2.93</v>
       </c>
       <c r="P47" t="n">
-        <v>2.81</v>
+        <v>3.99</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA47" t="n">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="AB47" t="n">
         <v>1.36</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -7950,10 +7950,10 @@
         </is>
       </c>
       <c r="AJ47" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK47" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL47" t="n">
         <v>0</v>

--- a/jogos_2026-07-11.xlsx
+++ b/jogos_2026-07-11.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.35</v>
+        <v>2.71</v>
       </c>
       <c r="O2" t="n">
-        <v>3.35</v>
+        <v>3.44</v>
       </c>
       <c r="P2" t="n">
-        <v>2.57</v>
+        <v>2.26</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.7</v>
+        <v>3.37</v>
       </c>
       <c r="R2" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="S2" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="T2" t="n">
-        <v>2.92</v>
+        <v>3.12</v>
       </c>
       <c r="U2" t="n">
-        <v>2.63</v>
+        <v>2.28</v>
       </c>
       <c r="V2" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W2" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X2" t="n">
         <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.58</v>
+        <v>3.98</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.74</v>
+        <v>1.62</v>
       </c>
       <c r="AB2" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.78</v>
+        <v>2.52</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.17</v>
+        <v>2.32</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.46</v>
+        <v>1.37</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,31 +884,31 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="O3" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="P3" t="n">
-        <v>2.4</v>
+        <v>2.57</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.97</v>
+        <v>2.7</v>
       </c>
       <c r="R3" t="n">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="S3" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="T3" t="n">
-        <v>3.14</v>
+        <v>2.92</v>
       </c>
       <c r="U3" t="n">
-        <v>2.44</v>
+        <v>2.63</v>
       </c>
       <c r="V3" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W3" t="n">
         <v>1.07</v>
@@ -917,31 +917,31 @@
         <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.05</v>
+        <v>3.58</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.62</v>
+        <v>2.78</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.29</v>
+        <v>2.17</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.71</v>
+        <v>2.45</v>
       </c>
       <c r="O4" t="n">
-        <v>3.44</v>
+        <v>3.6</v>
       </c>
       <c r="P4" t="n">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.37</v>
+        <v>2.97</v>
       </c>
       <c r="R4" t="n">
-        <v>2.21</v>
+        <v>2.18</v>
       </c>
       <c r="S4" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T4" t="n">
-        <v>3.12</v>
+        <v>3.14</v>
       </c>
       <c r="U4" t="n">
-        <v>2.28</v>
+        <v>2.44</v>
       </c>
       <c r="V4" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="W4" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X4" t="n">
         <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.98</v>
+        <v>4.05</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AB4" t="n">
         <v>2.1</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.52</v>
+        <v>2.62</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AF4" t="n">
         <v>1.53</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>1.22</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>APIA Leichhardt Tigers</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Sydney II</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="O5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="P5" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="V5" t="n">
         <v>1.64</v>
-      </c>
-      <c r="O5" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="P5" t="n">
-        <v>4.47</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R5" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="T5" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.45</v>
       </c>
       <c r="W5" t="n">
         <v>1.13</v>
       </c>
       <c r="X5" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.95</v>
+        <v>4.9</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.67</v>
+        <v>1.42</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.05</v>
+        <v>2.49</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.62</v>
+        <v>2.07</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.42</v>
+        <v>1.62</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.07</v>
+        <v>2.17</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.03</v>
+        <v>2.43</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>APIA Leichhardt Tigers</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sydney II</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,65 +1361,65 @@
         </is>
       </c>
       <c r="N6" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="O6" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="P6" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="V6" t="n">
         <v>1.45</v>
-      </c>
-      <c r="O6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="P6" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="R6" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="T6" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.64</v>
       </c>
       <c r="W6" t="n">
         <v>1.13</v>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE6" t="n">
         <v>1.12</v>
       </c>
-      <c r="Z6" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AC6" t="n">
+      <c r="AF6" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG6" t="n">
         <v>2.07</v>
       </c>
-      <c r="AD6" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>2.17</v>
-      </c>
       <c r="AH6" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.43</v>
+        <v>2.03</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,80 +1838,80 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.87</v>
+        <v>7.49</v>
       </c>
       <c r="O9" t="n">
-        <v>3.25</v>
+        <v>4.55</v>
       </c>
       <c r="P9" t="n">
-        <v>3.6</v>
+        <v>1.28</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.52</v>
+        <v>6.25</v>
       </c>
       <c r="R9" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="S9" t="n">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="T9" t="n">
-        <v>2.66</v>
+        <v>3.2</v>
       </c>
       <c r="U9" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9" t="n">
         <v>2.88</v>
       </c>
-      <c r="V9" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X9" t="n">
+      <c r="AK9" t="n">
         <v>1.06</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1.83</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>7.49</v>
+        <v>2.05</v>
       </c>
       <c r="O12" t="n">
-        <v>4.55</v>
+        <v>3.2</v>
       </c>
       <c r="P12" t="n">
-        <v>1.28</v>
+        <v>3.35</v>
       </c>
       <c r="Q12" t="n">
-        <v>6.25</v>
+        <v>2.49</v>
       </c>
       <c r="R12" t="n">
-        <v>2.4</v>
+        <v>2.14</v>
       </c>
       <c r="S12" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="T12" t="n">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="U12" t="n">
-        <v>2.44</v>
+        <v>3</v>
       </c>
       <c r="V12" t="n">
-        <v>1.43</v>
+        <v>1.32</v>
       </c>
       <c r="W12" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AD12" t="n">
         <v>1.22</v>
       </c>
-      <c r="Z12" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.35</v>
-      </c>
       <c r="AE12" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>2.88</v>
+        <v>1.25</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.06</v>
+        <v>1.77</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2480,58 +2480,58 @@
         <v>3.2</v>
       </c>
       <c r="P13" t="n">
-        <v>3.35</v>
+        <v>3.17</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.05</v>
+        <v>2.23</v>
       </c>
       <c r="O14" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="P14" t="n">
-        <v>3.17</v>
+        <v>2.97</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.15</v>
+        <v>1.99</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.23</v>
+        <v>1.87</v>
       </c>
       <c r="O15" t="n">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="P15" t="n">
-        <v>2.97</v>
+        <v>3.6</v>
       </c>
       <c r="Q15" t="n">
-        <v>3</v>
+        <v>2.52</v>
       </c>
       <c r="R15" t="n">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="S15" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="T15" t="n">
-        <v>2.75</v>
+        <v>2.66</v>
       </c>
       <c r="U15" t="n">
-        <v>2.91</v>
+        <v>2.88</v>
       </c>
       <c r="V15" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W15" t="n">
         <v>1.03</v>
       </c>
       <c r="X15" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.04</v>
+        <v>3.14</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2865,7 +2865,7 @@
         <v>1.3</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.54</v>
+        <v>1.83</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.52</v>
+        <v>1.59</v>
       </c>
       <c r="O18" t="n">
-        <v>4.2</v>
+        <v>4.46</v>
       </c>
       <c r="P18" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.59</v>
+        <v>2.15</v>
       </c>
       <c r="O20" t="n">
-        <v>4.46</v>
+        <v>3.2</v>
       </c>
       <c r="P20" t="n">
-        <v>5.2</v>
+        <v>3.1</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.36</v>
+        <v>2.5</v>
       </c>
       <c r="O21" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="P21" t="n">
-        <v>7.5</v>
+        <v>2.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.5</v>
+        <v>1.36</v>
       </c>
       <c r="O22" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="P22" t="n">
-        <v>2.4</v>
+        <v>7.5</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.86</v>
+        <v>2.81</v>
       </c>
       <c r="R23" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="S23" t="n">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="T23" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="U23" t="n">
-        <v>2.64</v>
+        <v>1.99</v>
       </c>
       <c r="V23" t="n">
-        <v>1.44</v>
+        <v>1.75</v>
       </c>
       <c r="W23" t="n">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="X23" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.24</v>
+        <v>1.06</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.54</v>
+        <v>11.4</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.82</v>
+        <v>1.4</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.01</v>
+        <v>2.74</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.1</v>
+        <v>1.95</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.38</v>
+        <v>1.75</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.15</v>
+        <v>1.31</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.61</v>
+        <v>1.36</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.18</v>
+        <v>2.98</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.81</v>
+        <v>2.86</v>
       </c>
       <c r="R24" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="S24" t="n">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="T24" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="U24" t="n">
-        <v>1.99</v>
+        <v>2.64</v>
       </c>
       <c r="V24" t="n">
-        <v>1.75</v>
+        <v>1.44</v>
       </c>
       <c r="W24" t="n">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="X24" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.06</v>
+        <v>1.24</v>
       </c>
       <c r="Z24" t="n">
-        <v>11.4</v>
+        <v>4.54</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.4</v>
+        <v>1.82</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.74</v>
+        <v>2.01</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.95</v>
+        <v>3.1</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.75</v>
+        <v>1.38</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.31</v>
+        <v>1.15</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.36</v>
+        <v>1.61</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.98</v>
+        <v>2.18</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,80 +4541,80 @@
         </is>
       </c>
       <c r="N26" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O26" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R26" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="S26" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U26" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ26" t="n">
         <v>1.27</v>
       </c>
-      <c r="O26" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="P26" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="R26" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="S26" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="T26" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U26" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ26" t="n">
-        <v>1.16</v>
-      </c>
       <c r="AK26" t="n">
-        <v>3.2</v>
+        <v>1.41</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,64 +4700,64 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>2.75</v>
+        <v>1.27</v>
       </c>
       <c r="O27" t="n">
-        <v>3.01</v>
+        <v>5.1</v>
       </c>
       <c r="P27" t="n">
-        <v>2.7</v>
+        <v>7</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.3</v>
+        <v>1.76</v>
       </c>
       <c r="R27" t="n">
-        <v>2.08</v>
+        <v>2.68</v>
       </c>
       <c r="S27" t="n">
-        <v>1.48</v>
+        <v>1.28</v>
       </c>
       <c r="T27" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC27" t="n">
         <v>2.63</v>
       </c>
-      <c r="U27" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X27" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>3.9</v>
-      </c>
       <c r="AD27" t="n">
-        <v>1.21</v>
+        <v>1.44</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.41</v>
+        <v>3.2</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,64 +5018,64 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>2.13</v>
+        <v>2.61</v>
       </c>
       <c r="O29" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="P29" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="Q29" t="n">
         <v>3.1</v>
       </c>
-      <c r="P29" t="n">
+      <c r="R29" t="n">
+        <v>2</v>
+      </c>
+      <c r="S29" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U29" t="n">
         <v>3.2</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,64 +5177,64 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>2.61</v>
+        <v>2.13</v>
       </c>
       <c r="O30" t="n">
-        <v>2.86</v>
+        <v>3.1</v>
       </c>
       <c r="P30" t="n">
-        <v>3.01</v>
+        <v>3.2</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,64 +5495,64 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>2.9</v>
+        <v>1.74</v>
       </c>
       <c r="O32" t="n">
-        <v>3.5</v>
+        <v>3.78</v>
       </c>
       <c r="P32" t="n">
-        <v>2.19</v>
+        <v>3.84</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.4</v>
+        <v>2.26</v>
       </c>
       <c r="R32" t="n">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="S32" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="T32" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="U32" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="V32" t="n">
         <v>1.62</v>
       </c>
       <c r="W32" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="X32" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="Z32" t="n">
-        <v>5.42</v>
+        <v>5.3</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AF32" t="n">
         <v>1.44</v>
       </c>
       <c r="AG32" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>1.7</v>
+        <v>1.21</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.33</v>
+        <v>1.86</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,64 +5654,64 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1.74</v>
+        <v>2.9</v>
       </c>
       <c r="O33" t="n">
-        <v>3.78</v>
+        <v>3.5</v>
       </c>
       <c r="P33" t="n">
-        <v>3.84</v>
+        <v>2.19</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.26</v>
+        <v>3.4</v>
       </c>
       <c r="R33" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="S33" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="T33" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="U33" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="V33" t="n">
         <v>1.62</v>
       </c>
       <c r="W33" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="X33" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="Z33" t="n">
-        <v>5.3</v>
+        <v>5.42</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AF33" t="n">
         <v>1.44</v>
       </c>
       <c r="AG33" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>1.21</v>
+        <v>1.7</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.86</v>
+        <v>1.33</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,65 +6131,65 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="O36" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="P36" t="n">
-        <v>4.59</v>
+        <v>4.58</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="R36" t="n">
         <v>2.3</v>
       </c>
       <c r="S36" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="T36" t="n">
-        <v>3.3</v>
+        <v>3.04</v>
       </c>
       <c r="U36" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="V36" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="W36" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X36" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y36" t="n">
         <v>1.2</v>
       </c>
       <c r="Z36" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="AA36" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF36" t="n">
         <v>1.67</v>
       </c>
-      <c r="AB36" t="n">
+      <c r="AG36" t="n">
         <v>2.1</v>
       </c>
-      <c r="AC36" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>2.11</v>
-      </c>
       <c r="AH36" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AK36" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,64 +6290,64 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="O37" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="P37" t="n">
-        <v>4.58</v>
+        <v>4.59</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="R37" t="n">
         <v>2.3</v>
       </c>
       <c r="S37" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T37" t="n">
-        <v>3.04</v>
+        <v>3.3</v>
       </c>
       <c r="U37" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="V37" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="W37" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X37" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y37" t="n">
         <v>1.2</v>
       </c>
       <c r="Z37" t="n">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AG37" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AK37" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6611,19 +6611,19 @@
         <v>2.86</v>
       </c>
       <c r="O39" t="n">
-        <v>2.9</v>
+        <v>3.08</v>
       </c>
       <c r="P39" t="n">
         <v>2.52</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="R39" t="n">
         <v>1.92</v>
       </c>
       <c r="S39" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="T39" t="n">
         <v>2.41</v>
@@ -6635,16 +6635,16 @@
         <v>1.28</v>
       </c>
       <c r="W39" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X39" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.89</v>
+        <v>2.66</v>
       </c>
       <c r="AA39" t="n">
         <v>2.25</v>
@@ -6656,10 +6656,10 @@
         <v>4.2</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF39" t="n">
         <v>1.89</v>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="AJ39" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK39" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,64 +6926,64 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>2.15</v>
+        <v>2.8</v>
       </c>
       <c r="O41" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="P41" t="n">
-        <v>3.9</v>
+        <v>2.81</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>3.28</v>
+        <v>3.1</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AC41" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AG41" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -6996,10 +6996,10 @@
         </is>
       </c>
       <c r="AJ41" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AK41" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AL41" t="n">
         <v>0</v>
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,64 +7085,64 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="O42" t="n">
-        <v>2.95</v>
+        <v>2.98</v>
       </c>
       <c r="P42" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA42" t="n">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7155,10 +7155,10 @@
         </is>
       </c>
       <c r="AJ42" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK42" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL42" t="n">
         <v>0</v>
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,64 +7244,64 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>2.8</v>
+        <v>1.83</v>
       </c>
       <c r="O43" t="n">
-        <v>2.7</v>
+        <v>2.87</v>
       </c>
       <c r="P43" t="n">
-        <v>2.81</v>
+        <v>4.96</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AA43" t="n">
-        <v>3.1</v>
+        <v>3.07</v>
       </c>
       <c r="AB43" t="n">
         <v>1.36</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>6.38</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7314,10 +7314,10 @@
         </is>
       </c>
       <c r="AJ43" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK43" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL43" t="n">
         <v>0</v>
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,52 +7562,52 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>1.83</v>
+        <v>1.97</v>
       </c>
       <c r="O45" t="n">
-        <v>2.87</v>
+        <v>2.93</v>
       </c>
       <c r="P45" t="n">
-        <v>4.96</v>
+        <v>3.99</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.45</v>
+        <v>2.9</v>
       </c>
       <c r="R45" t="n">
         <v>1.85</v>
       </c>
       <c r="S45" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="T45" t="n">
-        <v>2.08</v>
+        <v>2.13</v>
       </c>
       <c r="U45" t="n">
-        <v>4.2</v>
+        <v>3.88</v>
       </c>
       <c r="V45" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="W45" t="n">
         <v>1.03</v>
       </c>
       <c r="X45" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AA45" t="n">
-        <v>3.07</v>
+        <v>2.75</v>
       </c>
       <c r="AB45" t="n">
         <v>1.36</v>
       </c>
       <c r="AC45" t="n">
-        <v>6.38</v>
+        <v>5.6</v>
       </c>
       <c r="AD45" t="n">
         <v>1.1</v>
@@ -7616,10 +7616,10 @@
         <v>1.02</v>
       </c>
       <c r="AF45" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7632,10 +7632,10 @@
         </is>
       </c>
       <c r="AJ45" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="AK45" t="n">
-        <v>1.82</v>
+        <v>1.53</v>
       </c>
       <c r="AL45" t="n">
         <v>0</v>
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,64 +7721,64 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>1.72</v>
+        <v>2.15</v>
       </c>
       <c r="O46" t="n">
-        <v>2.98</v>
+        <v>2.5</v>
       </c>
       <c r="P46" t="n">
-        <v>4.9</v>
+        <v>3.9</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="R46" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="S46" t="n">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="T46" t="n">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="U46" t="n">
-        <v>4.2</v>
+        <v>4.65</v>
       </c>
       <c r="V46" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="W46" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X46" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Y46" t="n">
         <v>1.75</v>
       </c>
       <c r="Z46" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AA46" t="n">
-        <v>3.34</v>
+        <v>3.28</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AC46" t="n">
-        <v>7.5</v>
+        <v>7.1</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AE46" t="n">
         <v>1.02</v>
       </c>
       <c r="AF46" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7791,10 +7791,10 @@
         </is>
       </c>
       <c r="AJ46" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AK46" t="n">
-        <v>1.95</v>
+        <v>1.55</v>
       </c>
       <c r="AL46" t="n">
         <v>0</v>
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,64 +7880,64 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>1.97</v>
+        <v>1.77</v>
       </c>
       <c r="O47" t="n">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="P47" t="n">
-        <v>3.99</v>
+        <v>4.4</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="V47" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X47" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AC47" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -7950,10 +7950,10 @@
         </is>
       </c>
       <c r="AJ47" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK47" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL47" t="n">
         <v>0</v>
@@ -8198,19 +8198,19 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="O49" t="n">
-        <v>3.51</v>
+        <v>3.4</v>
       </c>
       <c r="P49" t="n">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="Q49" t="n">
-        <v>4.66</v>
+        <v>4.5</v>
       </c>
       <c r="R49" t="n">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="S49" t="n">
         <v>1.38</v>
@@ -8222,7 +8222,7 @@
         <v>2.78</v>
       </c>
       <c r="V49" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W49" t="n">
         <v>1.06</v>
@@ -8249,10 +8249,10 @@
         <v>1.29</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG49" t="n">
         <v>1.91</v>
@@ -8268,10 +8268,10 @@
         </is>
       </c>
       <c r="AJ49" t="n">
-        <v>1.26</v>
+        <v>1.83</v>
       </c>
       <c r="AK49" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AL49" t="n">
         <v>0</v>
@@ -8516,13 +8516,13 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="O51" t="n">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="P51" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="Q51" t="n">
         <v>2.88</v>
@@ -8540,25 +8540,25 @@
         <v>3.5</v>
       </c>
       <c r="V51" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="W51" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X51" t="n">
         <v>1.1</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="Z51" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="AA51" t="n">
-        <v>2.61</v>
+        <v>2.5</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AC51" t="n">
         <v>6.89</v>
@@ -8570,7 +8570,7 @@
         <v>1.04</v>
       </c>
       <c r="AF51" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AG51" t="n">
         <v>1.67</v>

--- a/jogos_2026-07-11.xlsx
+++ b/jogos_2026-07-11.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.71</v>
+        <v>2.37</v>
       </c>
       <c r="O2" t="n">
-        <v>3.44</v>
+        <v>3.34</v>
       </c>
       <c r="P2" t="n">
-        <v>2.26</v>
+        <v>2.55</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.37</v>
+        <v>2.88</v>
       </c>
       <c r="R2" t="n">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="S2" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="T2" t="n">
-        <v>3.12</v>
+        <v>2.92</v>
       </c>
       <c r="U2" t="n">
-        <v>2.28</v>
+        <v>2.63</v>
       </c>
       <c r="V2" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="W2" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X2" t="n">
         <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.98</v>
+        <v>3.58</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.62</v>
+        <v>1.74</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.52</v>
+        <v>2.78</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.32</v>
+        <v>2.17</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.37</v>
+        <v>1.52</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.35</v>
+        <v>2.71</v>
       </c>
       <c r="O3" t="n">
-        <v>3.35</v>
+        <v>3.44</v>
       </c>
       <c r="P3" t="n">
-        <v>2.57</v>
+        <v>2.26</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.7</v>
+        <v>3.37</v>
       </c>
       <c r="R3" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="S3" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="T3" t="n">
-        <v>2.92</v>
+        <v>3.12</v>
       </c>
       <c r="U3" t="n">
-        <v>2.63</v>
+        <v>2.39</v>
       </c>
       <c r="V3" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="W3" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X3" t="n">
         <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.58</v>
+        <v>3.98</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.74</v>
+        <v>1.64</v>
       </c>
       <c r="AB3" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.17</v>
+        <v>2.32</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.46</v>
+        <v>1.37</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1052,10 +1052,10 @@
         <v>2.4</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.97</v>
+        <v>2.95</v>
       </c>
       <c r="R4" t="n">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="S4" t="n">
         <v>1.29</v>
@@ -1064,13 +1064,13 @@
         <v>3.14</v>
       </c>
       <c r="U4" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="V4" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W4" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X4" t="n">
         <v>1.01</v>
@@ -1085,22 +1085,22 @@
         <v>1.66</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AF4" t="n">
         <v>1.53</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>1.22</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>APIA Leichhardt Tigers</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sydney II</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.45</v>
+        <v>1.65</v>
       </c>
       <c r="O5" t="n">
-        <v>4.2</v>
+        <v>3.72</v>
       </c>
       <c r="P5" t="n">
-        <v>5.7</v>
+        <v>4.41</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="R5" t="n">
-        <v>2.39</v>
+        <v>2.22</v>
       </c>
       <c r="S5" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="T5" t="n">
-        <v>3.48</v>
+        <v>3.04</v>
       </c>
       <c r="U5" t="n">
-        <v>1.98</v>
+        <v>2.46</v>
       </c>
       <c r="V5" t="n">
-        <v>1.64</v>
+        <v>1.44</v>
       </c>
       <c r="W5" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.9</v>
+        <v>3.95</v>
       </c>
       <c r="AA5" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AD5" t="n">
         <v>1.42</v>
       </c>
-      <c r="AB5" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AD5" t="n">
+      <c r="AE5" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF5" t="n">
         <v>1.62</v>
       </c>
-      <c r="AE5" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AG5" t="n">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.43</v>
+        <v>1.9</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>APIA Leichhardt Tigers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Sydney II</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.64</v>
+        <v>1.43</v>
       </c>
       <c r="O6" t="n">
-        <v>3.74</v>
+        <v>4.25</v>
       </c>
       <c r="P6" t="n">
-        <v>4.47</v>
+        <v>5.97</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.2</v>
+        <v>1.93</v>
       </c>
       <c r="R6" t="n">
-        <v>2.23</v>
+        <v>2.4</v>
       </c>
       <c r="S6" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="T6" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="U6" t="n">
-        <v>2.44</v>
+        <v>2.1</v>
       </c>
       <c r="V6" t="n">
-        <v>1.45</v>
+        <v>1.67</v>
       </c>
       <c r="W6" t="n">
         <v>1.13</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.95</v>
+        <v>5.15</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.67</v>
+        <v>1.42</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.62</v>
+        <v>2.07</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.42</v>
+        <v>1.62</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.12</v>
+        <v>1.23</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.07</v>
+        <v>2.24</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.03</v>
+        <v>2.46</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.33</v>
+        <v>2.44</v>
       </c>
       <c r="O7" t="n">
-        <v>3.28</v>
+        <v>3.35</v>
       </c>
       <c r="P7" t="n">
-        <v>2.64</v>
+        <v>2.63</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,80 +1838,80 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>7.49</v>
+        <v>1.86</v>
       </c>
       <c r="O9" t="n">
-        <v>4.55</v>
+        <v>3.08</v>
       </c>
       <c r="P9" t="n">
-        <v>1.28</v>
+        <v>3.18</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.25</v>
+        <v>2.3</v>
       </c>
       <c r="R9" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="S9" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9" t="n">
         <v>1.3</v>
       </c>
-      <c r="T9" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9" t="n">
-        <v>2.88</v>
-      </c>
       <c r="AK9" t="n">
-        <v>1.06</v>
+        <v>1.77</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.74</v>
+        <v>2.03</v>
       </c>
       <c r="O10" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P10" t="n">
-        <v>2.47</v>
+        <v>3.17</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
         <v>2.15</v>
       </c>
-      <c r="S10" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AB10" t="n">
-        <v>1.85</v>
+        <v>1.66</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,80 +2156,80 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>5.3</v>
+        <v>2.74</v>
       </c>
       <c r="O11" t="n">
-        <v>3.72</v>
+        <v>3.3</v>
       </c>
       <c r="P11" t="n">
-        <v>1.55</v>
+        <v>2.47</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.5</v>
+        <v>3.2</v>
       </c>
       <c r="R11" t="n">
-        <v>2.01</v>
+        <v>2.15</v>
       </c>
       <c r="S11" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="T11" t="n">
-        <v>2.53</v>
+        <v>3</v>
       </c>
       <c r="U11" t="n">
-        <v>2.96</v>
+        <v>2.81</v>
       </c>
       <c r="V11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ11" t="n">
         <v>1.33</v>
       </c>
-      <c r="W11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y11" t="n">
+      <c r="AK11" t="n">
         <v>1.4</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ11" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>1.1</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="O12" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB12" t="n">
         <v>2.05</v>
       </c>
-      <c r="O12" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P12" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="R12" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U12" t="n">
-        <v>3</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AC12" t="n">
-        <v>3.45</v>
+        <v>2.74</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.77</v>
+        <v>1.08</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2480,58 +2480,58 @@
         <v>3.2</v>
       </c>
       <c r="P13" t="n">
-        <v>3.17</v>
+        <v>3.35</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2642,19 +2642,19 @@
         <v>2.97</v>
       </c>
       <c r="Q14" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="R14" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="S14" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="T14" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="U14" t="n">
-        <v>2.91</v>
+        <v>3.04</v>
       </c>
       <c r="V14" t="n">
         <v>1.33</v>
@@ -2663,7 +2663,7 @@
         <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
         <v>1.29</v>
@@ -2675,22 +2675,22 @@
         <v>1.99</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="AD14" t="n">
         <v>1.27</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF14" t="n">
         <v>1.77</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AK14" t="n">
         <v>1.54</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.87</v>
+        <v>5.5</v>
       </c>
       <c r="O15" t="n">
-        <v>3.25</v>
+        <v>3.51</v>
       </c>
       <c r="P15" t="n">
-        <v>3.6</v>
+        <v>1.57</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.52</v>
+        <v>6.5</v>
       </c>
       <c r="R15" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="U15" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AA15" t="n">
         <v>2.2</v>
       </c>
-      <c r="S15" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="U15" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2</v>
-      </c>
       <c r="AB15" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.5</v>
+        <v>4.25</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.79</v>
+        <v>2.25</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.95</v>
+        <v>1.57</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.83</v>
+        <v>1.11</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.59</v>
+        <v>3.18</v>
       </c>
       <c r="O18" t="n">
-        <v>4.46</v>
+        <v>3.48</v>
       </c>
       <c r="P18" t="n">
-        <v>5.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.95</v>
+        <v>3.4</v>
       </c>
       <c r="R18" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="S18" t="n">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="T18" t="n">
-        <v>3.68</v>
+        <v>3.05</v>
       </c>
       <c r="U18" t="n">
-        <v>2.02</v>
+        <v>2.39</v>
       </c>
       <c r="V18" t="n">
-        <v>1.68</v>
+        <v>1.45</v>
       </c>
       <c r="W18" t="n">
-        <v>1.16</v>
+        <v>1.06</v>
       </c>
       <c r="X18" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.4</v>
+        <v>5.12</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.48</v>
+        <v>1.73</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.12</v>
+        <v>2.75</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.68</v>
+        <v>1.4</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.28</v>
+        <v>1.14</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.45</v>
+        <v>2.23</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.05</v>
+        <v>1.3</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.4</v>
+        <v>1.22</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.52</v>
+        <v>2.15</v>
       </c>
       <c r="O19" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="P19" t="n">
-        <v>5</v>
+        <v>3.1</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="O20" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="P20" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="R20" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AC20" t="n">
         <v>2.15</v>
       </c>
-      <c r="O20" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P20" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>0</v>
-      </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.5</v>
+        <v>1.36</v>
       </c>
       <c r="O21" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="P21" t="n">
-        <v>2.4</v>
+        <v>7.5</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.36</v>
+        <v>2.5</v>
       </c>
       <c r="O22" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="P22" t="n">
-        <v>7.5</v>
+        <v>2.37</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.81</v>
+        <v>2.86</v>
       </c>
       <c r="R23" t="n">
-        <v>2.38</v>
+        <v>2.08</v>
       </c>
       <c r="S23" t="n">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="T23" t="n">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="U23" t="n">
-        <v>1.99</v>
+        <v>2.54</v>
       </c>
       <c r="V23" t="n">
-        <v>1.75</v>
+        <v>1.44</v>
       </c>
       <c r="W23" t="n">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="X23" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.06</v>
+        <v>1.24</v>
       </c>
       <c r="Z23" t="n">
-        <v>11.4</v>
+        <v>3.94</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.4</v>
+        <v>1.82</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.74</v>
+        <v>2.01</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.95</v>
+        <v>2.88</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.75</v>
+        <v>1.38</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.31</v>
+        <v>1.11</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.36</v>
+        <v>1.61</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.98</v>
+        <v>2.18</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.86</v>
+        <v>2.63</v>
       </c>
       <c r="R24" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="S24" t="n">
-        <v>1.35</v>
+        <v>1.19</v>
       </c>
       <c r="T24" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="U24" t="n">
-        <v>2.64</v>
+        <v>1.99</v>
       </c>
       <c r="V24" t="n">
-        <v>1.44</v>
+        <v>1.75</v>
       </c>
       <c r="W24" t="n">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="X24" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.24</v>
+        <v>1.11</v>
       </c>
       <c r="Z24" t="n">
-        <v>4.54</v>
+        <v>6</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.82</v>
+        <v>1.4</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.01</v>
+        <v>2.87</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.1</v>
+        <v>1.95</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.38</v>
+        <v>1.75</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.15</v>
+        <v>1.31</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.61</v>
+        <v>1.33</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.18</v>
+        <v>2.9</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.57</v>
+        <v>1.42</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4382,28 +4382,28 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.52</v>
+        <v>2.75</v>
       </c>
       <c r="O25" t="n">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="P25" t="n">
         <v>2.45</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="R25" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="S25" t="n">
         <v>1.36</v>
       </c>
       <c r="T25" t="n">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="U25" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="V25" t="n">
         <v>1.43</v>
@@ -4412,7 +4412,7 @@
         <v>1.05</v>
       </c>
       <c r="X25" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y25" t="n">
         <v>1.22</v>
@@ -4421,7 +4421,7 @@
         <v>3.8</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AB25" t="n">
         <v>2</v>
@@ -4433,10 +4433,10 @@
         <v>1.36</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="AG25" t="n">
         <v>2.2</v>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,64 +4541,64 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>2.75</v>
+        <v>1.33</v>
       </c>
       <c r="O26" t="n">
-        <v>3.01</v>
+        <v>4.75</v>
       </c>
       <c r="P26" t="n">
-        <v>2.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.3</v>
+        <v>1.76</v>
       </c>
       <c r="R26" t="n">
-        <v>2.08</v>
+        <v>2.48</v>
       </c>
       <c r="S26" t="n">
-        <v>1.48</v>
+        <v>1.28</v>
       </c>
       <c r="T26" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC26" t="n">
         <v>2.63</v>
       </c>
-      <c r="U26" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>3.9</v>
-      </c>
       <c r="AD26" t="n">
-        <v>1.21</v>
+        <v>1.44</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.41</v>
+        <v>3.2</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,64 +4700,64 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.27</v>
+        <v>2.75</v>
       </c>
       <c r="O27" t="n">
-        <v>5.1</v>
+        <v>3.01</v>
       </c>
       <c r="P27" t="n">
-        <v>7</v>
+        <v>2.7</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.76</v>
+        <v>3.5</v>
       </c>
       <c r="R27" t="n">
-        <v>2.68</v>
+        <v>1.9</v>
       </c>
       <c r="S27" t="n">
-        <v>1.28</v>
+        <v>1.48</v>
       </c>
       <c r="T27" t="n">
-        <v>3.25</v>
+        <v>2.47</v>
       </c>
       <c r="U27" t="n">
-        <v>2.36</v>
+        <v>3.2</v>
       </c>
       <c r="V27" t="n">
-        <v>1.51</v>
+        <v>1.3</v>
       </c>
       <c r="W27" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="X27" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AE27" t="n">
         <v>1.03</v>
       </c>
-      <c r="Y27" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AF27" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>1.16</v>
+        <v>1.36</v>
       </c>
       <c r="AK27" t="n">
-        <v>3.2</v>
+        <v>1.41</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4859,7 +4859,7 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="O28" t="n">
         <v>3.4</v>
@@ -4868,25 +4868,25 @@
         <v>3.3</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="R28" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="S28" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T28" t="n">
         <v>3.15</v>
       </c>
       <c r="U28" t="n">
-        <v>2.63</v>
+        <v>2.53</v>
       </c>
       <c r="V28" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="W28" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X28" t="n">
         <v>1.04</v>
@@ -4895,25 +4895,25 @@
         <v>1.22</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.94</v>
+        <v>4</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="AD28" t="n">
         <v>1.36</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG28" t="n">
         <v>2.15</v>
@@ -4929,7 +4929,7 @@
         </is>
       </c>
       <c r="AJ28" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK28" t="n">
         <v>1.82</v>
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,64 +5018,64 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>2.61</v>
+        <v>2.13</v>
       </c>
       <c r="O29" t="n">
-        <v>2.86</v>
+        <v>3.3</v>
       </c>
       <c r="P29" t="n">
-        <v>3.01</v>
+        <v>3.25</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="AJ29" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,64 +5177,64 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>2.13</v>
+        <v>2.61</v>
       </c>
       <c r="O30" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="P30" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="Q30" t="n">
         <v>3.1</v>
       </c>
-      <c r="P30" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,64 +5336,64 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1.89</v>
+        <v>3.05</v>
       </c>
       <c r="O31" t="n">
-        <v>2.95</v>
+        <v>3.65</v>
       </c>
       <c r="P31" t="n">
-        <v>4.1</v>
+        <v>2.13</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>5.41</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="O32" t="n">
-        <v>3.78</v>
+        <v>3.7</v>
       </c>
       <c r="P32" t="n">
-        <v>3.84</v>
+        <v>3.6</v>
       </c>
       <c r="Q32" t="n">
         <v>2.26</v>
@@ -5522,7 +5522,7 @@
         <v>1.62</v>
       </c>
       <c r="W32" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X32" t="n">
         <v>1.01</v>
@@ -5534,7 +5534,7 @@
         <v>5.3</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="AB32" t="n">
         <v>2.5</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,64 +5654,64 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>2.9</v>
+        <v>1.92</v>
       </c>
       <c r="O33" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="P33" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="S33" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="U33" t="n">
         <v>3.5</v>
       </c>
-      <c r="P33" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R33" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="S33" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="T33" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U33" t="n">
-        <v>2.2</v>
-      </c>
       <c r="V33" t="n">
-        <v>1.62</v>
+        <v>1.25</v>
       </c>
       <c r="W33" t="n">
-        <v>1.15</v>
+        <v>1.04</v>
       </c>
       <c r="X33" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.18</v>
+        <v>1.5</v>
       </c>
       <c r="Z33" t="n">
-        <v>5.42</v>
+        <v>2.38</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.53</v>
+        <v>2.55</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.4</v>
+        <v>1.43</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.25</v>
+        <v>4.8</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.62</v>
+        <v>1.11</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.19</v>
+        <v>1.02</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.44</v>
+        <v>2.16</v>
       </c>
       <c r="AG33" t="n">
-        <v>2.5</v>
+        <v>1.59</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AK33" t="n">
         <v>1.7</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>1.33</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -5834,16 +5834,16 @@
         <v>3</v>
       </c>
       <c r="U34" t="n">
-        <v>2.85</v>
+        <v>2.5</v>
       </c>
       <c r="V34" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="W34" t="n">
         <v>1.08</v>
       </c>
       <c r="X34" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y34" t="n">
         <v>1.3</v>
@@ -5852,10 +5852,10 @@
         <v>3.1</v>
       </c>
       <c r="AA34" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="AC34" t="n">
         <v>3</v>
@@ -5867,10 +5867,10 @@
         <v>1.06</v>
       </c>
       <c r="AF34" t="n">
-        <v>2.15</v>
+        <v>1.78</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.64</v>
+        <v>1.82</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="AJ34" t="n">
-        <v>1.18</v>
+        <v>2.54</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -5972,64 +5972,64 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="O35" t="n">
         <v>4.2</v>
       </c>
       <c r="P35" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="Q35" t="n">
-        <v>5.36</v>
+        <v>5.23</v>
       </c>
       <c r="R35" t="n">
-        <v>2.68</v>
+        <v>2.39</v>
       </c>
       <c r="S35" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="T35" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="U35" t="n">
         <v>2.2</v>
       </c>
       <c r="V35" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W35" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="X35" t="n">
         <v>1.02</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="Z35" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AB35" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AG35" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6045,7 +6045,7 @@
         <v>1.18</v>
       </c>
       <c r="AK35" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,64 +6131,64 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="O36" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="P36" t="n">
-        <v>4.58</v>
+        <v>4.2</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="R36" t="n">
         <v>2.3</v>
       </c>
       <c r="S36" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T36" t="n">
-        <v>3.04</v>
+        <v>3.28</v>
       </c>
       <c r="U36" t="n">
-        <v>2.56</v>
+        <v>2.47</v>
       </c>
       <c r="V36" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="W36" t="n">
         <v>1.07</v>
       </c>
       <c r="X36" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="Z36" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AB36" t="n">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="AC36" t="n">
-        <v>2.75</v>
+        <v>2.61</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AF36" t="n">
         <v>1.67</v>
       </c>
       <c r="AG36" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AK36" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,64 +6290,64 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.67</v>
+        <v>1.32</v>
       </c>
       <c r="O37" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P37" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z37" t="n">
         <v>4</v>
       </c>
-      <c r="P37" t="n">
-        <v>4.59</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="R37" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="S37" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="T37" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U37" t="n">
+      <c r="AA37" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AC37" t="n">
         <v>2.5</v>
       </c>
-      <c r="V37" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X37" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>2.8</v>
-      </c>
       <c r="AD37" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AE37" t="n">
         <v>1.15</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="AG37" t="n">
-        <v>2.11</v>
+        <v>1.78</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AK37" t="n">
-        <v>2.15</v>
+        <v>2.7</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,64 +6449,64 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1.32</v>
+        <v>1.65</v>
       </c>
       <c r="O38" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="P38" t="n">
-        <v>7.8</v>
+        <v>4.52</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z38" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.78</v>
+        <v>2.05</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AK38" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6608,10 +6608,10 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>2.86</v>
+        <v>2.75</v>
       </c>
       <c r="O39" t="n">
-        <v>3.08</v>
+        <v>2.9</v>
       </c>
       <c r="P39" t="n">
         <v>2.52</v>
@@ -6635,7 +6635,7 @@
         <v>1.28</v>
       </c>
       <c r="W39" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X39" t="n">
         <v>1.08</v>
@@ -6665,7 +6665,7 @@
         <v>1.89</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,64 +6767,64 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>2.02</v>
+        <v>1.9</v>
       </c>
       <c r="O40" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="P40" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="R40" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="S40" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="T40" t="n">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="U40" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="V40" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="W40" t="n">
         <v>1.03</v>
       </c>
       <c r="X40" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.59</v>
+        <v>1.76</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AC40" t="n">
-        <v>6</v>
+        <v>7.1</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF40" t="n">
-        <v>2.25</v>
+        <v>2.67</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.6</v>
+        <v>1.41</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6840,7 +6840,7 @@
         <v>1.4</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="O41" t="n">
-        <v>2.7</v>
+        <v>2.95</v>
       </c>
       <c r="P41" t="n">
-        <v>2.81</v>
+        <v>3</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -6965,10 +6965,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -7085,58 +7085,58 @@
         </is>
       </c>
       <c r="N42" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="O42" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P42" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R42" t="n">
         <v>1.72</v>
       </c>
-      <c r="O42" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="P42" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="R42" t="n">
-        <v>1.85</v>
-      </c>
       <c r="S42" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="T42" t="n">
-        <v>2.04</v>
+        <v>1.97</v>
       </c>
       <c r="U42" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="V42" t="n">
         <v>1.2</v>
       </c>
       <c r="W42" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X42" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="Z42" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AA42" t="n">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AC42" t="n">
-        <v>7.5</v>
+        <v>6.75</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF42" t="n">
         <v>2.55</v>
@@ -7155,10 +7155,10 @@
         </is>
       </c>
       <c r="AJ42" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AK42" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AL42" t="n">
         <v>0</v>
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,64 +7244,64 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>1.83</v>
+        <v>1.99</v>
       </c>
       <c r="O43" t="n">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="P43" t="n">
-        <v>4.96</v>
+        <v>4.2</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="R43" t="n">
         <v>1.85</v>
       </c>
       <c r="S43" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="T43" t="n">
-        <v>2.08</v>
+        <v>2.25</v>
       </c>
       <c r="U43" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="V43" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="W43" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X43" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AE43" t="n">
         <v>1.03</v>
       </c>
-      <c r="X43" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>6.38</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AE43" t="n">
-        <v>1.02</v>
-      </c>
       <c r="AF43" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7314,10 +7314,10 @@
         </is>
       </c>
       <c r="AJ43" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="AK43" t="n">
-        <v>1.82</v>
+        <v>1.7</v>
       </c>
       <c r="AL43" t="n">
         <v>0</v>
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,64 +7403,64 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>1.99</v>
+        <v>1.8</v>
       </c>
       <c r="O44" t="n">
         <v>2.9</v>
       </c>
       <c r="P44" t="n">
-        <v>3.65</v>
+        <v>4.6</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.78</v>
+        <v>3.5</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AC44" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="AJ44" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AK44" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AL44" t="n">
         <v>0</v>
@@ -7577,7 +7577,7 @@
         <v>1.85</v>
       </c>
       <c r="S45" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="T45" t="n">
         <v>2.13</v>
@@ -7598,28 +7598,28 @@
         <v>1.57</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.1</v>
+        <v>2.21</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.75</v>
+        <v>3.02</v>
       </c>
       <c r="AB45" t="n">
         <v>1.36</v>
       </c>
       <c r="AC45" t="n">
-        <v>5.6</v>
+        <v>6.26</v>
       </c>
       <c r="AD45" t="n">
         <v>1.1</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF45" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7632,7 +7632,7 @@
         </is>
       </c>
       <c r="AJ45" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AK45" t="n">
         <v>1.53</v>
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,64 +7721,64 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="O46" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="P46" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="R46" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="S46" t="n">
-        <v>1.76</v>
+        <v>1.64</v>
       </c>
       <c r="T46" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="U46" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="V46" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W46" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X46" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Z46" t="n">
         <v>2.2</v>
       </c>
-      <c r="U46" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="V46" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="W46" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X46" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>2.02</v>
-      </c>
       <c r="AA46" t="n">
-        <v>3.28</v>
+        <v>2.8</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AC46" t="n">
-        <v>7.1</v>
+        <v>6</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF46" t="n">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.43</v>
+        <v>1.6</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7791,10 +7791,10 @@
         </is>
       </c>
       <c r="AJ46" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AK46" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AL46" t="n">
         <v>0</v>
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,64 +7880,64 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>1.77</v>
+        <v>2.15</v>
       </c>
       <c r="O47" t="n">
-        <v>2.95</v>
+        <v>2.45</v>
       </c>
       <c r="P47" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA47" t="n">
-        <v>3.4</v>
+        <v>3.51</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -7950,10 +7950,10 @@
         </is>
       </c>
       <c r="AJ47" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AK47" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL47" t="n">
         <v>0</v>
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>3.8</v>
+        <v>4.25</v>
       </c>
       <c r="O49" t="n">
-        <v>3.4</v>
+        <v>3.52</v>
       </c>
       <c r="P49" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="Q49" t="n">
         <v>4.5</v>
@@ -8213,16 +8213,16 @@
         <v>2.15</v>
       </c>
       <c r="S49" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="T49" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="U49" t="n">
         <v>2.78</v>
       </c>
       <c r="V49" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W49" t="n">
         <v>1.06</v>
@@ -8231,10 +8231,10 @@
         <v>1.05</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="Z49" t="n">
-        <v>3.71</v>
+        <v>3.25</v>
       </c>
       <c r="AA49" t="n">
         <v>1.91</v>
@@ -8243,13 +8243,13 @@
         <v>1.85</v>
       </c>
       <c r="AC49" t="n">
-        <v>3.71</v>
+        <v>3.62</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF49" t="n">
         <v>1.75</v>
@@ -8268,10 +8268,10 @@
         </is>
       </c>
       <c r="AJ49" t="n">
-        <v>1.83</v>
+        <v>1.26</v>
       </c>
       <c r="AK49" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AL49" t="n">
         <v>0</v>
@@ -8366,25 +8366,25 @@
         <v>2.22</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.3</v>
+        <v>3.64</v>
       </c>
       <c r="R50" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="S50" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T50" t="n">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="U50" t="n">
         <v>2.67</v>
       </c>
       <c r="V50" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W50" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X50" t="n">
         <v>1.05</v>
@@ -8393,19 +8393,19 @@
         <v>1.24</v>
       </c>
       <c r="Z50" t="n">
-        <v>3.34</v>
+        <v>2.75</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AB50" t="n">
         <v>1.83</v>
       </c>
       <c r="AC50" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AE50" t="n">
         <v>1.1</v>
@@ -8516,64 +8516,64 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="O51" t="n">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="P51" t="n">
         <v>3.1</v>
       </c>
       <c r="Q51" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="R51" t="n">
         <v>1.91</v>
       </c>
       <c r="S51" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="T51" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="U51" t="n">
         <v>3.5</v>
       </c>
       <c r="V51" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="W51" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X51" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Y51" t="n">
         <v>1.5</v>
       </c>
       <c r="Z51" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AA51" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AC51" t="n">
-        <v>6.89</v>
+        <v>6.71</v>
       </c>
       <c r="AD51" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF51" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AG51" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8586,10 +8586,10 @@
         </is>
       </c>
       <c r="AJ51" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AK51" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AL51" t="n">
         <v>0</v>
@@ -8843,10 +8843,10 @@
         <v>3.75</v>
       </c>
       <c r="Q53" t="n">
-        <v>2.38</v>
+        <v>2.51</v>
       </c>
       <c r="R53" t="n">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="S53" t="n">
         <v>1.36</v>
@@ -8861,13 +8861,13 @@
         <v>1.34</v>
       </c>
       <c r="W53" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X53" t="n">
         <v>1.05</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Z53" t="n">
         <v>3.1</v>
@@ -8882,7 +8882,7 @@
         <v>3.5</v>
       </c>
       <c r="AD53" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AE53" t="n">
         <v>1.08</v>
@@ -8904,7 +8904,7 @@
         </is>
       </c>
       <c r="AJ53" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AK53" t="n">
         <v>1.75</v>

--- a/jogos_2026-07-11.xlsx
+++ b/jogos_2026-07-11.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.37</v>
+        <v>2.45</v>
       </c>
       <c r="O2" t="n">
-        <v>3.34</v>
+        <v>3.6</v>
       </c>
       <c r="P2" t="n">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="R2" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="S2" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="T2" t="n">
-        <v>2.92</v>
+        <v>3.14</v>
       </c>
       <c r="U2" t="n">
-        <v>2.63</v>
+        <v>2.46</v>
       </c>
       <c r="V2" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W2" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X2" t="n">
         <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.58</v>
+        <v>4.05</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.74</v>
+        <v>1.66</v>
       </c>
       <c r="AB2" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.78</v>
+        <v>2.55</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.17</v>
+        <v>2.28</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.45</v>
+        <v>2.37</v>
       </c>
       <c r="O4" t="n">
-        <v>3.6</v>
+        <v>3.34</v>
       </c>
       <c r="P4" t="n">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="R4" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="S4" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="T4" t="n">
-        <v>3.14</v>
+        <v>2.92</v>
       </c>
       <c r="U4" t="n">
-        <v>2.46</v>
+        <v>2.63</v>
       </c>
       <c r="V4" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W4" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X4" t="n">
         <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.05</v>
+        <v>3.58</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.55</v>
+        <v>2.78</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.28</v>
+        <v>2.17</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>APIA Leichhardt Tigers</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Sydney II</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,80 +1202,80 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.65</v>
+        <v>1.43</v>
       </c>
       <c r="O5" t="n">
-        <v>3.72</v>
+        <v>4.25</v>
       </c>
       <c r="P5" t="n">
-        <v>4.41</v>
+        <v>5.97</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.21</v>
+        <v>1.93</v>
       </c>
       <c r="R5" t="n">
-        <v>2.22</v>
+        <v>2.4</v>
       </c>
       <c r="S5" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="T5" t="n">
-        <v>3.04</v>
+        <v>4</v>
       </c>
       <c r="U5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AK5" t="n">
         <v>2.46</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1.9</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>APIA Leichhardt Tigers</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sydney II</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,80 +1361,80 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.43</v>
+        <v>1.65</v>
       </c>
       <c r="O6" t="n">
-        <v>4.25</v>
+        <v>3.72</v>
       </c>
       <c r="P6" t="n">
-        <v>5.97</v>
+        <v>4.41</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.93</v>
+        <v>2.21</v>
       </c>
       <c r="R6" t="n">
-        <v>2.4</v>
+        <v>2.22</v>
       </c>
       <c r="S6" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6" t="n">
         <v>1.2</v>
       </c>
-      <c r="T6" t="n">
-        <v>4</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AK6" t="n">
-        <v>2.46</v>
+        <v>1.9</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.86</v>
+        <v>2.03</v>
       </c>
       <c r="O9" t="n">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="P9" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.03</v>
+        <v>2.23</v>
       </c>
       <c r="O10" t="n">
-        <v>3.25</v>
+        <v>3.18</v>
       </c>
       <c r="P10" t="n">
-        <v>3.17</v>
+        <v>2.97</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.15</v>
+        <v>1.99</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,80 +2156,80 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.74</v>
+        <v>5.5</v>
       </c>
       <c r="O11" t="n">
-        <v>3.3</v>
+        <v>3.51</v>
       </c>
       <c r="P11" t="n">
-        <v>2.47</v>
+        <v>1.57</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.2</v>
+        <v>6.5</v>
       </c>
       <c r="R11" t="n">
-        <v>2.15</v>
+        <v>2.01</v>
       </c>
       <c r="S11" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="T11" t="n">
-        <v>3</v>
+        <v>2.53</v>
       </c>
       <c r="U11" t="n">
-        <v>2.81</v>
+        <v>3.22</v>
       </c>
       <c r="V11" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="W11" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X11" t="n">
         <v>1.05</v>
       </c>
       <c r="Y11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ11" t="n">
         <v>1.29</v>
       </c>
-      <c r="Z11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AK11" t="n">
-        <v>1.4</v>
+        <v>1.11</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,65 +2315,65 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>6.1</v>
+        <v>2.74</v>
       </c>
       <c r="O12" t="n">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="P12" t="n">
-        <v>1.35</v>
+        <v>2.47</v>
       </c>
       <c r="Q12" t="n">
-        <v>6.95</v>
+        <v>3.2</v>
       </c>
       <c r="R12" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="S12" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T12" t="n">
-        <v>3.21</v>
+        <v>3</v>
       </c>
       <c r="U12" t="n">
-        <v>2.53</v>
+        <v>2.81</v>
       </c>
       <c r="V12" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="W12" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X12" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.78</v>
+        <v>3.4</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AB12" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG12" t="n">
         <v>2.05</v>
       </c>
-      <c r="AC12" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AH12" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.08</v>
+        <v>1.4</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.23</v>
+        <v>6.1</v>
       </c>
       <c r="O14" t="n">
-        <v>3.18</v>
+        <v>4.4</v>
       </c>
       <c r="P14" t="n">
-        <v>2.97</v>
+        <v>1.35</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.85</v>
+        <v>6.95</v>
       </c>
       <c r="R14" t="n">
-        <v>2.02</v>
+        <v>2.4</v>
       </c>
       <c r="S14" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="T14" t="n">
-        <v>2.62</v>
+        <v>3.21</v>
       </c>
       <c r="U14" t="n">
-        <v>3.04</v>
+        <v>2.53</v>
       </c>
       <c r="V14" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="W14" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X14" t="n">
         <v>1.03</v>
       </c>
-      <c r="X14" t="n">
-        <v>1.01</v>
-      </c>
       <c r="Y14" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.04</v>
+        <v>3.78</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.99</v>
+        <v>1.75</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.72</v>
+        <v>2.05</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.75</v>
+        <v>2.74</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.77</v>
+        <v>1.95</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.92</v>
+        <v>1.75</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.54</v>
+        <v>1.08</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,80 +2792,80 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>5.5</v>
+        <v>1.86</v>
       </c>
       <c r="O15" t="n">
-        <v>3.51</v>
+        <v>3.08</v>
       </c>
       <c r="P15" t="n">
-        <v>1.57</v>
+        <v>3.18</v>
       </c>
       <c r="Q15" t="n">
-        <v>6.5</v>
+        <v>2.3</v>
       </c>
       <c r="R15" t="n">
-        <v>2.01</v>
+        <v>2.2</v>
       </c>
       <c r="S15" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="T15" t="n">
-        <v>2.53</v>
+        <v>2.66</v>
       </c>
       <c r="U15" t="n">
-        <v>3.22</v>
+        <v>2.88</v>
       </c>
       <c r="V15" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ15" t="n">
         <v>1.3</v>
       </c>
-      <c r="W15" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AK15" t="n">
-        <v>1.11</v>
+        <v>1.77</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="O19" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="P19" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="R19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AC19" t="n">
         <v>2.15</v>
       </c>
-      <c r="O19" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P19" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>0</v>
-      </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.59</v>
+        <v>2.15</v>
       </c>
       <c r="O20" t="n">
-        <v>4.46</v>
+        <v>3.2</v>
       </c>
       <c r="P20" t="n">
-        <v>5.2</v>
+        <v>3.1</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.36</v>
+        <v>2.5</v>
       </c>
       <c r="O21" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="P21" t="n">
-        <v>7.5</v>
+        <v>2.37</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.5</v>
+        <v>1.36</v>
       </c>
       <c r="O22" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="P22" t="n">
-        <v>2.37</v>
+        <v>7.5</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,65 +4064,65 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.86</v>
+        <v>2.63</v>
       </c>
       <c r="R23" t="n">
-        <v>2.08</v>
+        <v>2.38</v>
       </c>
       <c r="S23" t="n">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="T23" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AG23" t="n">
         <v>2.9</v>
       </c>
-      <c r="U23" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>2.18</v>
-      </c>
       <c r="AH23" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.58</v>
+        <v>1.42</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.63</v>
+        <v>2.86</v>
       </c>
       <c r="R24" t="n">
-        <v>2.38</v>
+        <v>2.08</v>
       </c>
       <c r="S24" t="n">
-        <v>1.19</v>
+        <v>1.32</v>
       </c>
       <c r="T24" t="n">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
       <c r="U24" t="n">
-        <v>1.99</v>
+        <v>2.54</v>
       </c>
       <c r="V24" t="n">
-        <v>1.75</v>
+        <v>1.44</v>
       </c>
       <c r="W24" t="n">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="X24" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE24" t="n">
         <v>1.11</v>
       </c>
-      <c r="Z24" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AF24" t="n">
-        <v>1.33</v>
+        <v>1.61</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.9</v>
+        <v>2.18</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.42</v>
+        <v>1.58</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,64 +4541,64 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.33</v>
+        <v>2.75</v>
       </c>
       <c r="O26" t="n">
-        <v>4.75</v>
+        <v>3.01</v>
       </c>
       <c r="P26" t="n">
-        <v>8.699999999999999</v>
+        <v>2.7</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.76</v>
+        <v>3.5</v>
       </c>
       <c r="R26" t="n">
-        <v>2.48</v>
+        <v>1.9</v>
       </c>
       <c r="S26" t="n">
-        <v>1.28</v>
+        <v>1.48</v>
       </c>
       <c r="T26" t="n">
-        <v>3.25</v>
+        <v>2.47</v>
       </c>
       <c r="U26" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="V26" t="n">
-        <v>1.53</v>
+        <v>1.3</v>
       </c>
       <c r="W26" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="X26" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AE26" t="n">
         <v>1.03</v>
       </c>
-      <c r="Y26" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AF26" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>1.16</v>
+        <v>1.36</v>
       </c>
       <c r="AK26" t="n">
-        <v>3.2</v>
+        <v>1.41</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,80 +4700,80 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>2.75</v>
+        <v>1.33</v>
       </c>
       <c r="O27" t="n">
-        <v>3.01</v>
+        <v>4.75</v>
       </c>
       <c r="P27" t="n">
-        <v>2.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.5</v>
+        <v>1.76</v>
       </c>
       <c r="R27" t="n">
-        <v>1.9</v>
+        <v>2.48</v>
       </c>
       <c r="S27" t="n">
-        <v>1.48</v>
+        <v>1.28</v>
       </c>
       <c r="T27" t="n">
-        <v>2.47</v>
+        <v>3.25</v>
       </c>
       <c r="U27" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ27" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AK27" t="n">
         <v>3.2</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X27" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ27" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>1.41</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,55 +5336,55 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>3.05</v>
+        <v>1.75</v>
       </c>
       <c r="O31" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="P31" t="n">
-        <v>2.13</v>
+        <v>3.6</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.3</v>
+        <v>2.26</v>
       </c>
       <c r="R31" t="n">
-        <v>2.33</v>
+        <v>2.6</v>
       </c>
       <c r="S31" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="T31" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="U31" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="V31" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="W31" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X31" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="Z31" t="n">
-        <v>5.41</v>
+        <v>5.3</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.54</v>
+        <v>1.42</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.32</v>
+        <v>2.14</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="AE31" t="n">
         <v>1.22</v>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="AJ31" t="n">
-        <v>1.7</v>
+        <v>1.21</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.33</v>
+        <v>1.86</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,55 +5495,55 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>1.75</v>
+        <v>3.05</v>
       </c>
       <c r="O32" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="P32" t="n">
-        <v>3.6</v>
+        <v>2.13</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.26</v>
+        <v>3.3</v>
       </c>
       <c r="R32" t="n">
-        <v>2.6</v>
+        <v>2.33</v>
       </c>
       <c r="S32" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="T32" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="U32" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="V32" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="W32" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X32" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="Z32" t="n">
-        <v>5.3</v>
+        <v>5.41</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.14</v>
+        <v>2.32</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="AE32" t="n">
         <v>1.22</v>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>1.21</v>
+        <v>1.7</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.86</v>
+        <v>1.33</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,64 +6131,64 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="O36" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="P36" t="n">
-        <v>4.2</v>
+        <v>4.52</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="R36" t="n">
         <v>2.3</v>
       </c>
       <c r="S36" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="T36" t="n">
-        <v>3.28</v>
+        <v>3.02</v>
       </c>
       <c r="U36" t="n">
-        <v>2.47</v>
+        <v>2.57</v>
       </c>
       <c r="V36" t="n">
         <v>1.48</v>
       </c>
       <c r="W36" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X36" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="Z36" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AB36" t="n">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="AC36" t="n">
-        <v>2.61</v>
+        <v>2.8</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AF36" t="n">
         <v>1.67</v>
       </c>
       <c r="AG36" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AK36" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,64 +6290,64 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.32</v>
+        <v>1.66</v>
       </c>
       <c r="O37" t="n">
-        <v>4.8</v>
+        <v>3.8</v>
       </c>
       <c r="P37" t="n">
-        <v>7.8</v>
+        <v>4.2</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z37" t="n">
         <v>4</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.5</v>
+        <v>2.61</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.78</v>
+        <v>2.11</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AK37" t="n">
-        <v>2.7</v>
+        <v>2.15</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,64 +6449,64 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1.65</v>
+        <v>1.32</v>
       </c>
       <c r="O38" t="n">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="P38" t="n">
-        <v>4.52</v>
+        <v>7.8</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z38" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="AG38" t="n">
-        <v>2.05</v>
+        <v>1.78</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AK38" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,64 +6767,64 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="O40" t="n">
         <v>2.8</v>
       </c>
       <c r="P40" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="R40" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="S40" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="T40" t="n">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="U40" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="V40" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="W40" t="n">
         <v>1.03</v>
       </c>
       <c r="X40" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.76</v>
+        <v>1.62</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="AA40" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AC40" t="n">
-        <v>7.1</v>
+        <v>6</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF40" t="n">
-        <v>2.67</v>
+        <v>2.25</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.41</v>
+        <v>1.6</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6840,7 +6840,7 @@
         <v>1.4</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,64 +6926,64 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>2.85</v>
+        <v>1.99</v>
       </c>
       <c r="O41" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="P41" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AA41" t="n">
-        <v>3.4</v>
+        <v>2.78</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -6996,10 +6996,10 @@
         </is>
       </c>
       <c r="AJ41" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK41" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL41" t="n">
         <v>0</v>
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,10 +7244,10 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>1.99</v>
+        <v>1.9</v>
       </c>
       <c r="O43" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="P43" t="n">
         <v>4.2</v>
@@ -7256,68 +7256,68 @@
         <v>2.7</v>
       </c>
       <c r="R43" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="S43" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="T43" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="U43" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="V43" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="W43" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X43" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="AD43" t="n">
         <v>1.04</v>
       </c>
-      <c r="X43" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AB43" t="n">
+      <c r="AE43" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ43" t="n">
         <v>1.4</v>
       </c>
-      <c r="AC43" t="n">
-        <v>5.85</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AE43" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF43" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AG43" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AH43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ43" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AK43" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AL43" t="n">
         <v>0</v>
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,64 +7403,64 @@
         </is>
       </c>
       <c r="N44" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="O44" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="P44" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="R44" t="n">
         <v>1.8</v>
       </c>
-      <c r="O44" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="P44" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
-      <c r="R44" t="n">
-        <v>0</v>
-      </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA44" t="n">
-        <v>3.5</v>
+        <v>3.51</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="AJ44" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AK44" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL44" t="n">
         <v>0</v>
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,64 +7562,64 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>1.97</v>
+        <v>2.85</v>
       </c>
       <c r="O45" t="n">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="P45" t="n">
-        <v>3.99</v>
+        <v>3</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>3.02</v>
+        <v>3.4</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AC45" t="n">
-        <v>6.26</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7632,10 +7632,10 @@
         </is>
       </c>
       <c r="AJ45" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK45" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL45" t="n">
         <v>0</v>
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,64 +7721,64 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="O46" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="P46" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" t="n">
+        <v>0</v>
+      </c>
+      <c r="W46" t="n">
+        <v>0</v>
+      </c>
+      <c r="X46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA46" t="n">
         <v>3.5</v>
       </c>
-      <c r="Q46" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R46" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="S46" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="T46" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="U46" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="V46" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="W46" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X46" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>2.8</v>
-      </c>
       <c r="AB46" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AC46" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7791,10 +7791,10 @@
         </is>
       </c>
       <c r="AJ46" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AK46" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AL46" t="n">
         <v>0</v>
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,64 +7880,64 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>2.15</v>
+        <v>1.97</v>
       </c>
       <c r="O47" t="n">
-        <v>2.45</v>
+        <v>2.93</v>
       </c>
       <c r="P47" t="n">
-        <v>3.9</v>
+        <v>3.99</v>
       </c>
       <c r="Q47" t="n">
         <v>2.9</v>
       </c>
       <c r="R47" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="S47" t="n">
-        <v>1.76</v>
+        <v>1.63</v>
       </c>
       <c r="T47" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="U47" t="n">
-        <v>4.65</v>
+        <v>3.88</v>
       </c>
       <c r="V47" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="W47" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X47" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.95</v>
+        <v>2.21</v>
       </c>
       <c r="AA47" t="n">
-        <v>3.51</v>
+        <v>3.02</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AC47" t="n">
-        <v>7.1</v>
+        <v>6.26</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF47" t="n">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="AG47" t="n">
-        <v>1.44</v>
+        <v>1.54</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -7950,10 +7950,10 @@
         </is>
       </c>
       <c r="AJ47" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AK47" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AL47" t="n">
         <v>0</v>

--- a/jogos_2026-07-11.xlsx
+++ b/jogos_2026-07-11.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.45</v>
+        <v>2.37</v>
       </c>
       <c r="O2" t="n">
-        <v>3.6</v>
+        <v>3.34</v>
       </c>
       <c r="P2" t="n">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="R2" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="S2" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="T2" t="n">
-        <v>3.14</v>
+        <v>2.92</v>
       </c>
       <c r="U2" t="n">
-        <v>2.46</v>
+        <v>2.63</v>
       </c>
       <c r="V2" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W2" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X2" t="n">
         <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.05</v>
+        <v>3.58</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.55</v>
+        <v>2.78</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.28</v>
+        <v>2.17</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.37</v>
+        <v>2.45</v>
       </c>
       <c r="O4" t="n">
-        <v>3.34</v>
+        <v>3.6</v>
       </c>
       <c r="P4" t="n">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="R4" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="S4" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="T4" t="n">
-        <v>2.92</v>
+        <v>3.14</v>
       </c>
       <c r="U4" t="n">
-        <v>2.63</v>
+        <v>2.46</v>
       </c>
       <c r="V4" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W4" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X4" t="n">
         <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.58</v>
+        <v>4.05</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.74</v>
+        <v>1.66</v>
       </c>
       <c r="AB4" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.78</v>
+        <v>2.55</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.17</v>
+        <v>2.28</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="O9" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P9" t="n">
-        <v>3.17</v>
+        <v>3.35</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,80 +1997,80 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.23</v>
+        <v>5.5</v>
       </c>
       <c r="O10" t="n">
-        <v>3.18</v>
+        <v>3.51</v>
       </c>
       <c r="P10" t="n">
-        <v>2.97</v>
+        <v>1.57</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.85</v>
+        <v>6.5</v>
       </c>
       <c r="R10" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="S10" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y10" t="n">
         <v>1.4</v>
       </c>
-      <c r="T10" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U10" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y10" t="n">
+      <c r="Z10" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ10" t="n">
         <v>1.29</v>
       </c>
-      <c r="Z10" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AK10" t="n">
-        <v>1.54</v>
+        <v>1.11</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>5.5</v>
+        <v>6.1</v>
       </c>
       <c r="O11" t="n">
-        <v>3.51</v>
+        <v>4.4</v>
       </c>
       <c r="P11" t="n">
-        <v>1.57</v>
+        <v>1.35</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.5</v>
+        <v>6.95</v>
       </c>
       <c r="R11" t="n">
-        <v>2.01</v>
+        <v>2.4</v>
       </c>
       <c r="S11" t="n">
-        <v>1.46</v>
+        <v>1.32</v>
       </c>
       <c r="T11" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="U11" t="n">
         <v>2.53</v>
       </c>
-      <c r="U11" t="n">
-        <v>3.22</v>
-      </c>
       <c r="V11" t="n">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="W11" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X11" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.72</v>
+        <v>3.78</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.65</v>
+        <v>2.05</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.25</v>
+        <v>2.74</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.02</v>
+        <v>1.14</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.74</v>
+        <v>2.03</v>
       </c>
       <c r="O12" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P12" t="n">
-        <v>2.47</v>
+        <v>3.17</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
         <v>2.15</v>
       </c>
-      <c r="S12" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="T12" t="n">
-        <v>3</v>
-      </c>
-      <c r="U12" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AB12" t="n">
-        <v>1.85</v>
+        <v>1.66</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,80 +2474,80 @@
         </is>
       </c>
       <c r="N13" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="O13" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R13" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG13" t="n">
         <v>2.05</v>
       </c>
-      <c r="O13" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P13" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="R13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="U13" t="n">
-        <v>3</v>
-      </c>
-      <c r="V13" t="n">
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ13" t="n">
         <v>1.33</v>
       </c>
-      <c r="W13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AK13" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,65 +2633,65 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>6.1</v>
+        <v>1.86</v>
       </c>
       <c r="O14" t="n">
-        <v>4.4</v>
+        <v>3.08</v>
       </c>
       <c r="P14" t="n">
-        <v>1.35</v>
+        <v>3.18</v>
       </c>
       <c r="Q14" t="n">
-        <v>6.95</v>
+        <v>2.3</v>
       </c>
       <c r="R14" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="S14" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="T14" t="n">
-        <v>3.21</v>
+        <v>2.66</v>
       </c>
       <c r="U14" t="n">
-        <v>2.53</v>
+        <v>2.88</v>
       </c>
       <c r="V14" t="n">
-        <v>1.43</v>
+        <v>1.34</v>
       </c>
       <c r="W14" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.78</v>
+        <v>3.14</v>
       </c>
       <c r="AA14" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AF14" t="n">
         <v>1.75</v>
       </c>
-      <c r="AB14" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AF14" t="n">
+      <c r="AG14" t="n">
         <v>1.95</v>
       </c>
-      <c r="AG14" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AH14" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.08</v>
+        <v>1.77</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.86</v>
+        <v>2.23</v>
       </c>
       <c r="O15" t="n">
-        <v>3.08</v>
+        <v>3.18</v>
       </c>
       <c r="P15" t="n">
-        <v>3.18</v>
+        <v>2.97</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.3</v>
+        <v>2.85</v>
       </c>
       <c r="R15" t="n">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="S15" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T15" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="U15" t="n">
-        <v>2.88</v>
+        <v>3.04</v>
       </c>
       <c r="V15" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W15" t="n">
         <v>1.03</v>
       </c>
       <c r="X15" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AD15" t="n">
         <v>1.27</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.24</v>
       </c>
       <c r="AE15" t="n">
         <v>1.05</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.77</v>
+        <v>1.54</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.52</v>
+        <v>3.18</v>
       </c>
       <c r="O16" t="n">
-        <v>4.2</v>
+        <v>3.48</v>
       </c>
       <c r="P16" t="n">
-        <v>5</v>
+        <v>2.25</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>5.12</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>3.18</v>
+        <v>2.15</v>
       </c>
       <c r="O18" t="n">
-        <v>3.48</v>
+        <v>3.2</v>
       </c>
       <c r="P18" t="n">
-        <v>2.25</v>
+        <v>3.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.12</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.15</v>
+        <v>1.52</v>
       </c>
       <c r="O20" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="P20" t="n">
-        <v>3.1</v>
+        <v>5</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.63</v>
+        <v>2.86</v>
       </c>
       <c r="R23" t="n">
-        <v>2.38</v>
+        <v>2.08</v>
       </c>
       <c r="S23" t="n">
-        <v>1.19</v>
+        <v>1.32</v>
       </c>
       <c r="T23" t="n">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
       <c r="U23" t="n">
-        <v>1.99</v>
+        <v>2.54</v>
       </c>
       <c r="V23" t="n">
-        <v>1.75</v>
+        <v>1.44</v>
       </c>
       <c r="W23" t="n">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="X23" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE23" t="n">
         <v>1.11</v>
       </c>
-      <c r="Z23" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AF23" t="n">
-        <v>1.33</v>
+        <v>1.61</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.9</v>
+        <v>2.18</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.42</v>
+        <v>1.58</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,65 +4223,65 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.86</v>
+        <v>2.63</v>
       </c>
       <c r="R24" t="n">
-        <v>2.08</v>
+        <v>2.38</v>
       </c>
       <c r="S24" t="n">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="T24" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AG24" t="n">
         <v>2.9</v>
       </c>
-      <c r="U24" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>2.18</v>
-      </c>
       <c r="AH24" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.58</v>
+        <v>1.42</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,64 +4382,64 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.75</v>
+        <v>1.33</v>
       </c>
       <c r="O25" t="n">
-        <v>3.5</v>
+        <v>4.75</v>
       </c>
       <c r="P25" t="n">
-        <v>2.45</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.45</v>
+        <v>1.76</v>
       </c>
       <c r="R25" t="n">
-        <v>2.07</v>
+        <v>2.48</v>
       </c>
       <c r="S25" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="T25" t="n">
-        <v>2.89</v>
+        <v>3.25</v>
       </c>
       <c r="U25" t="n">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="V25" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="W25" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X25" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.8</v>
+        <v>4.33</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AB25" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.88</v>
+        <v>2.63</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.59</v>
+        <v>1.85</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.4</v>
+        <v>3.2</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,65 +4700,65 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.33</v>
+        <v>2.52</v>
       </c>
       <c r="O27" t="n">
-        <v>4.75</v>
+        <v>3.34</v>
       </c>
       <c r="P27" t="n">
-        <v>8.699999999999999</v>
+        <v>2.45</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.76</v>
+        <v>3.45</v>
       </c>
       <c r="R27" t="n">
-        <v>2.48</v>
+        <v>2.07</v>
       </c>
       <c r="S27" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="T27" t="n">
-        <v>3.25</v>
+        <v>2.89</v>
       </c>
       <c r="U27" t="n">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="V27" t="n">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="W27" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X27" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z27" t="n">
-        <v>4.33</v>
+        <v>3.8</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AB27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AG27" t="n">
         <v>2.2</v>
       </c>
-      <c r="AC27" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AH27" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="AK27" t="n">
-        <v>3.2</v>
+        <v>1.4</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,64 +4859,64 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>1.94</v>
+        <v>2.61</v>
       </c>
       <c r="O28" t="n">
-        <v>3.4</v>
+        <v>2.86</v>
       </c>
       <c r="P28" t="n">
-        <v>3.3</v>
+        <v>3.01</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.45</v>
+        <v>3.1</v>
       </c>
       <c r="R28" t="n">
-        <v>2.27</v>
+        <v>2</v>
       </c>
       <c r="S28" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="T28" t="n">
-        <v>3.15</v>
+        <v>2.75</v>
       </c>
       <c r="U28" t="n">
-        <v>2.53</v>
+        <v>3.1</v>
       </c>
       <c r="V28" t="n">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="W28" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X28" t="n">
         <v>1.04</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="Z28" t="n">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.73</v>
+        <v>2.24</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.05</v>
+        <v>1.71</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.8</v>
+        <v>3.55</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.14</v>
+        <v>1.03</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.62</v>
+        <v>1.77</v>
       </c>
       <c r="AG28" t="n">
-        <v>2.15</v>
+        <v>1.83</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>1.22</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.82</v>
+        <v>1.52</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,64 +5018,64 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>2.13</v>
+        <v>1.94</v>
       </c>
       <c r="O29" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P29" t="n">
         <v>3.3</v>
       </c>
-      <c r="P29" t="n">
-        <v>3.25</v>
-      </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,64 +5177,64 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>2.61</v>
+        <v>2.13</v>
       </c>
       <c r="O30" t="n">
-        <v>2.86</v>
+        <v>3.3</v>
       </c>
       <c r="P30" t="n">
-        <v>3.01</v>
+        <v>3.25</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.83</v>
+        <v>0</v